--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2167" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2173" uniqueCount="120">
   <si>
     <t xml:space="preserve">MÊS</t>
   </si>
@@ -280,6 +280,12 @@
   </si>
   <si>
     <t xml:space="preserve">Florianópolis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">novembro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bh</t>
   </si>
   <si>
     <t xml:space="preserve">MAIO</t>
@@ -3670,7 +3676,27 @@
       <c r="D125" s="5"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D126" s="5"/>
+      <c r="A126" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B126" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D127" s="5"/>
@@ -4142,7 +4168,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>18</v>
@@ -4151,24 +4177,24 @@
         <v>55</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>4</v>
@@ -4177,24 +4203,24 @@
         <v>55</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="H3" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>2</v>
@@ -4203,7 +4229,7 @@
         <v>77</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>78</v>
@@ -4213,12 +4239,12 @@
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>23</v>
@@ -4227,24 +4253,24 @@
         <v>79</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>24</v>
@@ -4253,24 +4279,24 @@
         <v>79</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="H6" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>23</v>
@@ -4279,7 +4305,7 @@
         <v>72</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>73</v>
@@ -4289,12 +4315,12 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>24</v>
@@ -4303,7 +4329,7 @@
         <v>72</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>73</v>
@@ -4313,12 +4339,12 @@
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>24</v>
@@ -4327,24 +4353,24 @@
         <v>74</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>23</v>
@@ -4353,24 +4379,24 @@
         <v>74</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>23</v>
@@ -4379,24 +4405,24 @@
         <v>75</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>24</v>
@@ -4405,24 +4431,24 @@
         <v>75</v>
       </c>
       <c r="D12" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="H12" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>9</v>
@@ -4431,7 +4457,7 @@
         <v>58</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>59</v>
@@ -4441,12 +4467,12 @@
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>10</v>
@@ -4455,7 +4481,7 @@
         <v>58</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>59</v>
@@ -4465,12 +4491,12 @@
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>23</v>
@@ -4479,24 +4505,24 @@
         <v>60</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>24</v>
@@ -4505,24 +4531,24 @@
         <v>60</v>
       </c>
       <c r="D16" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="H16" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>23</v>
@@ -4531,7 +4557,7 @@
         <v>68</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>69</v>
@@ -4541,12 +4567,12 @@
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>24</v>
@@ -4555,7 +4581,7 @@
         <v>68</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>69</v>
@@ -4565,12 +4591,12 @@
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>24</v>
@@ -4579,24 +4605,24 @@
         <v>70</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>69</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>23</v>
@@ -4605,24 +4631,24 @@
         <v>70</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>69</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>23</v>
@@ -4631,24 +4657,24 @@
         <v>71</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>24</v>
@@ -4657,24 +4683,24 @@
         <v>71</v>
       </c>
       <c r="D22" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="H22" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>2</v>
@@ -4683,7 +4709,7 @@
         <v>81</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>82</v>
@@ -4693,12 +4719,12 @@
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>23</v>
@@ -4707,24 +4733,24 @@
         <v>80</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>24</v>
@@ -4733,24 +4759,24 @@
         <v>80</v>
       </c>
       <c r="D25" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="H25" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>23</v>
@@ -4759,7 +4785,7 @@
         <v>63</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>64</v>
@@ -4769,12 +4795,12 @@
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>24</v>
@@ -4783,7 +4809,7 @@
         <v>63</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>64</v>
@@ -4793,12 +4819,12 @@
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>23</v>
@@ -4807,24 +4833,24 @@
         <v>65</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>64</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>24</v>
@@ -4833,24 +4859,24 @@
         <v>65</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>64</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>23</v>
@@ -4859,24 +4885,24 @@
         <v>66</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>24</v>
@@ -4885,24 +4911,24 @@
         <v>66</v>
       </c>
       <c r="D31" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="H31" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>9</v>
@@ -4911,7 +4937,7 @@
         <v>50</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>51</v>
@@ -4921,12 +4947,12 @@
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>10</v>
@@ -4935,7 +4961,7 @@
         <v>50</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>51</v>
@@ -4945,12 +4971,12 @@
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B34" s="5" t="n">
         <v>23</v>
@@ -4959,24 +4985,24 @@
         <v>53</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B35" s="5" t="n">
         <v>24</v>
@@ -4985,24 +5011,24 @@
         <v>53</v>
       </c>
       <c r="D35" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="H35" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>23</v>
@@ -5011,24 +5037,24 @@
         <v>83</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B37" s="5" t="n">
         <v>24</v>
@@ -5037,24 +5063,24 @@
         <v>83</v>
       </c>
       <c r="D37" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G37" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="H37" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>23</v>
@@ -5063,24 +5089,24 @@
         <v>61</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>24</v>
@@ -5089,24 +5115,24 @@
         <v>61</v>
       </c>
       <c r="D39" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G39" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="H39" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>16</v>
@@ -5115,7 +5141,7 @@
         <v>21</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>17</v>
@@ -5130,7 +5156,7 @@
     </row>
     <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>17</v>
@@ -5139,7 +5165,7 @@
         <v>21</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>17</v>
@@ -5154,7 +5180,7 @@
     </row>
     <row r="42" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>17</v>
@@ -5163,16 +5189,16 @@
         <v>22</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>14</v>
@@ -5180,7 +5206,7 @@
     </row>
     <row r="43" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>16</v>
@@ -5189,16 +5215,16 @@
         <v>22</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>14</v>
@@ -5206,7 +5232,7 @@
     </row>
     <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B44" s="5" t="n">
         <v>23</v>
@@ -5215,16 +5241,16 @@
         <v>27</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>14</v>
@@ -5232,7 +5258,7 @@
     </row>
     <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B45" s="5" t="n">
         <v>24</v>
@@ -5241,16 +5267,16 @@
         <v>27</v>
       </c>
       <c r="D45" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G45" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>88</v>
       </c>
       <c r="H45" s="5" t="s">
         <v>14</v>
@@ -5258,7 +5284,7 @@
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B46" s="5" t="n">
         <v>18</v>
@@ -5267,16 +5293,16 @@
         <v>9</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>14</v>
@@ -5284,7 +5310,7 @@
     </row>
     <row r="47" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B47" s="5" t="n">
         <v>4</v>
@@ -5293,16 +5319,16 @@
         <v>9</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>14</v>
@@ -5310,7 +5336,7 @@
     </row>
     <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B48" s="5" t="n">
         <v>18</v>
@@ -5319,13 +5345,13 @@
         <v>25</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5" t="s">
@@ -5334,7 +5360,7 @@
     </row>
     <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B49" s="5" t="n">
         <v>4</v>
@@ -5343,7 +5369,7 @@
         <v>15</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>17</v>
@@ -5358,7 +5384,7 @@
     </row>
     <row r="50" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B50" s="5" t="n">
         <v>4</v>
@@ -5367,16 +5393,16 @@
         <v>19</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>14</v>
@@ -5384,7 +5410,7 @@
     </row>
     <row r="51" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B51" s="5" t="n">
         <v>18</v>
@@ -5393,16 +5419,16 @@
         <v>19</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>14</v>
@@ -5467,7 +5493,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>1</v>
@@ -5476,24 +5502,24 @@
         <v>55</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>15</v>
@@ -5502,24 +5528,24 @@
         <v>55</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="G3" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>6</v>
@@ -5538,12 +5564,12 @@
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>27</v>
@@ -5558,18 +5584,18 @@
         <v>11</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>28</v>
@@ -5584,18 +5610,18 @@
         <v>11</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>27</v>
@@ -5614,12 +5640,12 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>28</v>
@@ -5638,12 +5664,12 @@
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>27</v>
@@ -5658,18 +5684,18 @@
         <v>73</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>28</v>
@@ -5684,18 +5710,18 @@
         <v>73</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>27</v>
@@ -5710,18 +5736,18 @@
         <v>11</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>28</v>
@@ -5736,18 +5762,18 @@
         <v>11</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>13</v>
@@ -5766,12 +5792,12 @@
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>14</v>
@@ -5790,12 +5816,12 @@
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>27</v>
@@ -5810,18 +5836,18 @@
         <v>11</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>28</v>
@@ -5836,18 +5862,18 @@
         <v>11</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>27</v>
@@ -5866,12 +5892,12 @@
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>28</v>
@@ -5890,12 +5916,12 @@
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>28</v>
@@ -5910,18 +5936,18 @@
         <v>69</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>27</v>
@@ -5936,18 +5962,18 @@
         <v>69</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>27</v>
@@ -5962,18 +5988,18 @@
         <v>11</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>28</v>
@@ -5988,18 +6014,18 @@
         <v>11</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>6</v>
@@ -6018,12 +6044,12 @@
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>27</v>
@@ -6038,18 +6064,18 @@
         <v>11</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>28</v>
@@ -6064,18 +6090,18 @@
         <v>11</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>27</v>
@@ -6094,12 +6120,12 @@
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>28</v>
@@ -6118,12 +6144,12 @@
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>28</v>
@@ -6138,18 +6164,18 @@
         <v>64</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>27</v>
@@ -6164,18 +6190,18 @@
         <v>64</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>27</v>
@@ -6190,18 +6216,18 @@
         <v>11</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>28</v>
@@ -6216,18 +6242,18 @@
         <v>11</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>13</v>
@@ -6246,12 +6272,12 @@
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>14</v>
@@ -6270,12 +6296,12 @@
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B34" s="5" t="n">
         <v>27</v>
@@ -6290,18 +6316,18 @@
         <v>11</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B35" s="5" t="n">
         <v>28</v>
@@ -6316,18 +6342,18 @@
         <v>11</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>27</v>
@@ -6342,18 +6368,18 @@
         <v>11</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B37" s="5" t="n">
         <v>28</v>
@@ -6368,18 +6394,18 @@
         <v>11</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>27</v>
@@ -6394,18 +6420,18 @@
         <v>11</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>28</v>
@@ -6420,18 +6446,18 @@
         <v>11</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>20</v>
@@ -6455,7 +6481,7 @@
     </row>
     <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>21</v>
@@ -6479,7 +6505,7 @@
     </row>
     <row r="42" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>21</v>
@@ -6494,10 +6520,10 @@
         <v>17</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>14</v>
@@ -6505,7 +6531,7 @@
     </row>
     <row r="43" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>20</v>
@@ -6520,10 +6546,10 @@
         <v>17</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>14</v>
@@ -6531,7 +6557,7 @@
     </row>
     <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B44" s="5" t="n">
         <v>27</v>
@@ -6546,10 +6572,10 @@
         <v>11</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>14</v>
@@ -6557,7 +6583,7 @@
     </row>
     <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B45" s="5" t="n">
         <v>28</v>
@@ -6572,10 +6598,10 @@
         <v>11</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H45" s="5" t="s">
         <v>14</v>
@@ -6583,7 +6609,7 @@
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B46" s="5" t="n">
         <v>1</v>
@@ -6592,16 +6618,16 @@
         <v>9</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>14</v>
@@ -6609,7 +6635,7 @@
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B47" s="5" t="n">
         <v>15</v>
@@ -6618,16 +6644,16 @@
         <v>9</v>
       </c>
       <c r="D47" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E47" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="G47" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>14</v>
@@ -6635,7 +6661,7 @@
     </row>
     <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B48" s="5" t="n">
         <v>15</v>
@@ -6644,7 +6670,7 @@
         <v>25</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>17</v>
@@ -6659,7 +6685,7 @@
     </row>
     <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B49" s="5" t="n">
         <v>1</v>
@@ -6668,7 +6694,7 @@
         <v>15</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>17</v>
@@ -6683,7 +6709,7 @@
     </row>
     <row r="50" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B50" s="5" t="n">
         <v>15</v>
@@ -6692,16 +6718,16 @@
         <v>19</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>14</v>
@@ -6709,7 +6735,7 @@
     </row>
     <row r="51" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B51" s="5" t="n">
         <v>1</v>
@@ -6718,16 +6744,16 @@
         <v>19</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>14</v>
@@ -6792,7 +6818,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>6</v>
@@ -6813,12 +6839,12 @@
         <v>13</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>20</v>
@@ -6839,12 +6865,12 @@
         <v>13</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>4</v>
@@ -6863,12 +6889,12 @@
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>25</v>
@@ -6887,12 +6913,12 @@
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>26</v>
@@ -6911,12 +6937,12 @@
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>25</v>
@@ -6935,12 +6961,12 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>26</v>
@@ -6959,12 +6985,12 @@
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>26</v>
@@ -6985,12 +7011,12 @@
         <v>13</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>25</v>
@@ -7011,12 +7037,12 @@
         <v>13</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>25</v>
@@ -7035,12 +7061,12 @@
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>26</v>
@@ -7059,12 +7085,12 @@
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>11</v>
@@ -7083,12 +7109,12 @@
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>12</v>
@@ -7107,12 +7133,12 @@
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>25</v>
@@ -7131,12 +7157,12 @@
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>26</v>
@@ -7155,12 +7181,12 @@
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>25</v>
@@ -7179,12 +7205,12 @@
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>26</v>
@@ -7203,12 +7229,12 @@
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>26</v>
@@ -7229,12 +7255,12 @@
         <v>13</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>25</v>
@@ -7255,12 +7281,12 @@
         <v>13</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>25</v>
@@ -7279,12 +7305,12 @@
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>26</v>
@@ -7303,12 +7329,12 @@
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>4</v>
@@ -7327,12 +7353,12 @@
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>25</v>
@@ -7351,12 +7377,12 @@
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>26</v>
@@ -7375,12 +7401,12 @@
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>25</v>
@@ -7399,12 +7425,12 @@
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>26</v>
@@ -7423,12 +7449,12 @@
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>26</v>
@@ -7449,12 +7475,12 @@
         <v>13</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>25</v>
@@ -7475,12 +7501,12 @@
         <v>13</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>25</v>
@@ -7499,12 +7525,12 @@
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>26</v>
@@ -7523,12 +7549,12 @@
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>11</v>
@@ -7547,12 +7573,12 @@
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>12</v>
@@ -7571,12 +7597,12 @@
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B34" s="5" t="n">
         <v>25</v>
@@ -7595,12 +7621,12 @@
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B35" s="5" t="n">
         <v>26</v>
@@ -7619,12 +7645,12 @@
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>25</v>
@@ -7643,12 +7669,12 @@
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B37" s="5" t="n">
         <v>26</v>
@@ -7667,12 +7693,12 @@
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>25</v>
@@ -7691,12 +7717,12 @@
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>26</v>
@@ -7715,12 +7741,12 @@
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>18</v>
@@ -7744,7 +7770,7 @@
     </row>
     <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>19</v>
@@ -7768,7 +7794,7 @@
     </row>
     <row r="42" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>19</v>
@@ -7794,7 +7820,7 @@
     </row>
     <row r="43" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>18</v>
@@ -7820,7 +7846,7 @@
     </row>
     <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B44" s="5" t="n">
         <v>25</v>
@@ -7844,7 +7870,7 @@
     </row>
     <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B45" s="5" t="n">
         <v>26</v>
@@ -7868,7 +7894,7 @@
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B46" s="5" t="n">
         <v>6</v>
@@ -7894,7 +7920,7 @@
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B47" s="5" t="n">
         <v>20</v>
@@ -7920,7 +7946,7 @@
     </row>
     <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B48" s="5" t="n">
         <v>20</v>
@@ -7944,7 +7970,7 @@
     </row>
     <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B49" s="5" t="n">
         <v>6</v>
@@ -7968,7 +7994,7 @@
     </row>
     <row r="50" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B50" s="5" t="n">
         <v>20</v>
@@ -7994,7 +8020,7 @@
     </row>
     <row r="51" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B51" s="5" t="n">
         <v>6</v>
@@ -8077,7 +8103,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>3</v>
@@ -8096,12 +8122,12 @@
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>17</v>
@@ -8120,12 +8146,12 @@
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>1</v>
@@ -8146,12 +8172,12 @@
         <v>36</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>2</v>
@@ -8172,12 +8198,12 @@
         <v>36</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>23</v>
@@ -8198,12 +8224,12 @@
         <v>36</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>22</v>
@@ -8224,12 +8250,12 @@
         <v>36</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>22</v>
@@ -8250,12 +8276,12 @@
         <v>36</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>23</v>
@@ -8276,12 +8302,12 @@
         <v>36</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>8</v>
@@ -8302,12 +8328,12 @@
         <v>36</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>9</v>
@@ -8328,12 +8354,12 @@
         <v>36</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>23</v>
@@ -8354,12 +8380,12 @@
         <v>36</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>22</v>
@@ -8380,12 +8406,12 @@
         <v>36</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>1</v>
@@ -8406,12 +8432,12 @@
         <v>36</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>2</v>
@@ -8432,12 +8458,12 @@
         <v>36</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>23</v>
@@ -8458,12 +8484,12 @@
         <v>36</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>22</v>
@@ -8484,12 +8510,12 @@
         <v>36</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>8</v>
@@ -8510,12 +8536,12 @@
         <v>36</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>9</v>
@@ -8536,12 +8562,12 @@
         <v>36</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>1</v>
@@ -8562,12 +8588,12 @@
         <v>36</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>2</v>
@@ -8588,12 +8614,12 @@
         <v>36</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>15</v>
@@ -8614,12 +8640,12 @@
         <v>36</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>16</v>
@@ -8640,12 +8666,12 @@
         <v>36</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>16</v>
@@ -8671,7 +8697,7 @@
     </row>
     <row r="25" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>15</v>
@@ -8697,7 +8723,7 @@
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>15</v>
@@ -8723,7 +8749,7 @@
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>16</v>
@@ -8749,7 +8775,7 @@
     </row>
     <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>3</v>
@@ -8773,7 +8799,7 @@
     </row>
     <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>17</v>
@@ -8797,7 +8823,7 @@
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>17</v>
@@ -8821,7 +8847,7 @@
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>3</v>
@@ -8845,7 +8871,7 @@
     </row>
     <row r="32" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>17</v>
@@ -8871,7 +8897,7 @@
     </row>
     <row r="33" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>3</v>
@@ -8952,7 +8978,7 @@
     </row>
     <row r="2" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>27</v>
@@ -8973,12 +8999,12 @@
         <v>44</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>26</v>
@@ -8999,12 +9025,12 @@
         <v>44</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>27</v>
@@ -9023,12 +9049,12 @@
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>26</v>
@@ -9047,12 +9073,12 @@
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>13</v>
@@ -9071,12 +9097,12 @@
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>12</v>
@@ -9095,12 +9121,12 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>27</v>
@@ -9121,12 +9147,12 @@
         <v>44</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>26</v>
@@ -9147,12 +9173,12 @@
         <v>44</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>6</v>
@@ -9171,12 +9197,12 @@
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>6</v>
@@ -9195,12 +9221,12 @@
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>6</v>
@@ -9219,12 +9245,12 @@
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>5</v>
@@ -9243,12 +9269,12 @@
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>5</v>
@@ -9267,12 +9293,12 @@
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>5</v>
@@ -9291,12 +9317,12 @@
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>27</v>
@@ -9317,12 +9343,12 @@
         <v>44</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>26</v>
@@ -9343,12 +9369,12 @@
         <v>44</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>13</v>
@@ -9367,12 +9393,12 @@
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>12</v>
@@ -9391,12 +9417,12 @@
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>7</v>
@@ -9417,12 +9443,12 @@
         <v>44</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>21</v>
@@ -9443,12 +9469,12 @@
         <v>44</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>20</v>
@@ -9467,12 +9493,12 @@
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>19</v>
@@ -9491,12 +9517,12 @@
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>20</v>
@@ -9522,7 +9548,7 @@
     </row>
     <row r="25" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>19</v>
@@ -9548,7 +9574,7 @@
     </row>
     <row r="26" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>20</v>
@@ -9572,7 +9598,7 @@
     </row>
     <row r="27" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>19</v>
@@ -9596,7 +9622,7 @@
     </row>
     <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>7</v>
@@ -9622,7 +9648,7 @@
     </row>
     <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>21</v>
@@ -9648,7 +9674,7 @@
     </row>
     <row r="30" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>21</v>
@@ -9674,7 +9700,7 @@
     </row>
     <row r="31" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>7</v>

--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2173" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2167" uniqueCount="118">
   <si>
     <t xml:space="preserve">MÊS</t>
   </si>
@@ -280,12 +280,6 @@
   </si>
   <si>
     <t xml:space="preserve">Florianópolis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">novembro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bh</t>
   </si>
   <si>
     <t xml:space="preserve">MAIO</t>
@@ -3676,27 +3670,10 @@
       <c r="D125" s="5"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B126" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H126" s="1" t="s">
-        <v>86</v>
-      </c>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="4"/>
+      <c r="E126" s="3"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D127" s="5"/>
@@ -4168,7 +4145,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>18</v>
@@ -4177,24 +4154,24 @@
         <v>55</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>4</v>
@@ -4203,24 +4180,24 @@
         <v>55</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>2</v>
@@ -4229,7 +4206,7 @@
         <v>77</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>78</v>
@@ -4239,12 +4216,12 @@
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>23</v>
@@ -4253,24 +4230,24 @@
         <v>79</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="H5" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>24</v>
@@ -4279,24 +4256,24 @@
         <v>79</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>23</v>
@@ -4305,7 +4282,7 @@
         <v>72</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>73</v>
@@ -4315,12 +4292,12 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>24</v>
@@ -4329,7 +4306,7 @@
         <v>72</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>73</v>
@@ -4339,12 +4316,12 @@
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>24</v>
@@ -4353,24 +4330,24 @@
         <v>74</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>23</v>
@@ -4379,24 +4356,24 @@
         <v>74</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>23</v>
@@ -4405,24 +4382,24 @@
         <v>75</v>
       </c>
       <c r="D11" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="H11" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>24</v>
@@ -4431,24 +4408,24 @@
         <v>75</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>9</v>
@@ -4457,7 +4434,7 @@
         <v>58</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>59</v>
@@ -4467,12 +4444,12 @@
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>10</v>
@@ -4481,7 +4458,7 @@
         <v>58</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>59</v>
@@ -4491,12 +4468,12 @@
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>23</v>
@@ -4505,24 +4482,24 @@
         <v>60</v>
       </c>
       <c r="D15" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="H15" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>24</v>
@@ -4531,24 +4508,24 @@
         <v>60</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>23</v>
@@ -4557,7 +4534,7 @@
         <v>68</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>69</v>
@@ -4567,12 +4544,12 @@
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>24</v>
@@ -4581,7 +4558,7 @@
         <v>68</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>69</v>
@@ -4591,12 +4568,12 @@
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>24</v>
@@ -4605,24 +4582,24 @@
         <v>70</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>69</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>23</v>
@@ -4631,24 +4608,24 @@
         <v>70</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>69</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>23</v>
@@ -4657,24 +4634,24 @@
         <v>71</v>
       </c>
       <c r="D21" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="H21" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>24</v>
@@ -4683,24 +4660,24 @@
         <v>71</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>2</v>
@@ -4709,7 +4686,7 @@
         <v>81</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>82</v>
@@ -4719,12 +4696,12 @@
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>23</v>
@@ -4733,24 +4710,24 @@
         <v>80</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="H24" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>24</v>
@@ -4759,24 +4736,24 @@
         <v>80</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>23</v>
@@ -4785,7 +4762,7 @@
         <v>63</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>64</v>
@@ -4795,12 +4772,12 @@
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>24</v>
@@ -4809,7 +4786,7 @@
         <v>63</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>64</v>
@@ -4819,12 +4796,12 @@
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>23</v>
@@ -4833,24 +4810,24 @@
         <v>65</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>64</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>24</v>
@@ -4859,24 +4836,24 @@
         <v>65</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>64</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>23</v>
@@ -4885,24 +4862,24 @@
         <v>66</v>
       </c>
       <c r="D30" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="H30" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>24</v>
@@ -4911,24 +4888,24 @@
         <v>66</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>9</v>
@@ -4937,7 +4914,7 @@
         <v>50</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>51</v>
@@ -4947,12 +4924,12 @@
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>10</v>
@@ -4961,7 +4938,7 @@
         <v>50</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>51</v>
@@ -4971,12 +4948,12 @@
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B34" s="5" t="n">
         <v>23</v>
@@ -4985,24 +4962,24 @@
         <v>53</v>
       </c>
       <c r="D34" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G34" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="H34" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B35" s="5" t="n">
         <v>24</v>
@@ -5011,24 +4988,24 @@
         <v>53</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>23</v>
@@ -5037,24 +5014,24 @@
         <v>83</v>
       </c>
       <c r="D36" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G36" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E36" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="H36" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B37" s="5" t="n">
         <v>24</v>
@@ -5063,24 +5040,24 @@
         <v>83</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>23</v>
@@ -5089,24 +5066,24 @@
         <v>61</v>
       </c>
       <c r="D38" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G38" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="H38" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>24</v>
@@ -5115,24 +5092,24 @@
         <v>61</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>16</v>
@@ -5141,7 +5118,7 @@
         <v>21</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>17</v>
@@ -5156,7 +5133,7 @@
     </row>
     <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>17</v>
@@ -5165,7 +5142,7 @@
         <v>21</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>17</v>
@@ -5180,7 +5157,7 @@
     </row>
     <row r="42" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>17</v>
@@ -5189,16 +5166,16 @@
         <v>22</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>14</v>
@@ -5206,7 +5183,7 @@
     </row>
     <row r="43" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>16</v>
@@ -5215,16 +5192,16 @@
         <v>22</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>14</v>
@@ -5232,7 +5209,7 @@
     </row>
     <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B44" s="5" t="n">
         <v>23</v>
@@ -5241,16 +5218,16 @@
         <v>27</v>
       </c>
       <c r="D44" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G44" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>90</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>14</v>
@@ -5258,7 +5235,7 @@
     </row>
     <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B45" s="5" t="n">
         <v>24</v>
@@ -5267,16 +5244,16 @@
         <v>27</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H45" s="5" t="s">
         <v>14</v>
@@ -5284,7 +5261,7 @@
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B46" s="5" t="n">
         <v>18</v>
@@ -5293,16 +5270,16 @@
         <v>9</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>14</v>
@@ -5310,7 +5287,7 @@
     </row>
     <row r="47" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B47" s="5" t="n">
         <v>4</v>
@@ -5319,16 +5296,16 @@
         <v>9</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>14</v>
@@ -5336,7 +5313,7 @@
     </row>
     <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B48" s="5" t="n">
         <v>18</v>
@@ -5345,13 +5322,13 @@
         <v>25</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5" t="s">
@@ -5360,7 +5337,7 @@
     </row>
     <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B49" s="5" t="n">
         <v>4</v>
@@ -5369,7 +5346,7 @@
         <v>15</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>17</v>
@@ -5384,7 +5361,7 @@
     </row>
     <row r="50" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B50" s="5" t="n">
         <v>4</v>
@@ -5393,16 +5370,16 @@
         <v>19</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>14</v>
@@ -5410,7 +5387,7 @@
     </row>
     <row r="51" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B51" s="5" t="n">
         <v>18</v>
@@ -5419,16 +5396,16 @@
         <v>19</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>14</v>
@@ -5493,7 +5470,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>1</v>
@@ -5502,24 +5479,24 @@
         <v>55</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>15</v>
@@ -5528,24 +5505,24 @@
         <v>55</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>6</v>
@@ -5564,12 +5541,12 @@
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>27</v>
@@ -5584,18 +5561,18 @@
         <v>11</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>28</v>
@@ -5610,18 +5587,18 @@
         <v>11</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>27</v>
@@ -5640,12 +5617,12 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>28</v>
@@ -5664,12 +5641,12 @@
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>27</v>
@@ -5684,18 +5661,18 @@
         <v>73</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>28</v>
@@ -5710,18 +5687,18 @@
         <v>73</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>27</v>
@@ -5736,18 +5713,18 @@
         <v>11</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>28</v>
@@ -5762,18 +5739,18 @@
         <v>11</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>13</v>
@@ -5792,12 +5769,12 @@
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>14</v>
@@ -5816,12 +5793,12 @@
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>27</v>
@@ -5836,18 +5813,18 @@
         <v>11</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>28</v>
@@ -5862,18 +5839,18 @@
         <v>11</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>27</v>
@@ -5892,12 +5869,12 @@
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>28</v>
@@ -5916,12 +5893,12 @@
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>28</v>
@@ -5936,18 +5913,18 @@
         <v>69</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>27</v>
@@ -5962,18 +5939,18 @@
         <v>69</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>27</v>
@@ -5988,18 +5965,18 @@
         <v>11</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>28</v>
@@ -6014,18 +5991,18 @@
         <v>11</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>6</v>
@@ -6044,12 +6021,12 @@
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>27</v>
@@ -6064,18 +6041,18 @@
         <v>11</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>28</v>
@@ -6090,18 +6067,18 @@
         <v>11</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>27</v>
@@ -6120,12 +6097,12 @@
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>28</v>
@@ -6144,12 +6121,12 @@
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>28</v>
@@ -6164,18 +6141,18 @@
         <v>64</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>27</v>
@@ -6190,18 +6167,18 @@
         <v>64</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>27</v>
@@ -6216,18 +6193,18 @@
         <v>11</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>28</v>
@@ -6242,18 +6219,18 @@
         <v>11</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>13</v>
@@ -6272,12 +6249,12 @@
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>14</v>
@@ -6296,12 +6273,12 @@
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B34" s="5" t="n">
         <v>27</v>
@@ -6316,18 +6293,18 @@
         <v>11</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B35" s="5" t="n">
         <v>28</v>
@@ -6342,18 +6319,18 @@
         <v>11</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>27</v>
@@ -6368,18 +6345,18 @@
         <v>11</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B37" s="5" t="n">
         <v>28</v>
@@ -6394,18 +6371,18 @@
         <v>11</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>27</v>
@@ -6420,18 +6397,18 @@
         <v>11</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>28</v>
@@ -6446,18 +6423,18 @@
         <v>11</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>20</v>
@@ -6481,7 +6458,7 @@
     </row>
     <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>21</v>
@@ -6505,7 +6482,7 @@
     </row>
     <row r="42" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>21</v>
@@ -6520,10 +6497,10 @@
         <v>17</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>14</v>
@@ -6531,7 +6508,7 @@
     </row>
     <row r="43" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>20</v>
@@ -6546,10 +6523,10 @@
         <v>17</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>14</v>
@@ -6557,7 +6534,7 @@
     </row>
     <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B44" s="5" t="n">
         <v>27</v>
@@ -6572,10 +6549,10 @@
         <v>11</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>14</v>
@@ -6583,7 +6560,7 @@
     </row>
     <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B45" s="5" t="n">
         <v>28</v>
@@ -6598,10 +6575,10 @@
         <v>11</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H45" s="5" t="s">
         <v>14</v>
@@ -6609,7 +6586,7 @@
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B46" s="5" t="n">
         <v>1</v>
@@ -6618,16 +6595,16 @@
         <v>9</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>14</v>
@@ -6635,7 +6612,7 @@
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B47" s="5" t="n">
         <v>15</v>
@@ -6644,16 +6621,16 @@
         <v>9</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>14</v>
@@ -6661,7 +6638,7 @@
     </row>
     <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B48" s="5" t="n">
         <v>15</v>
@@ -6670,7 +6647,7 @@
         <v>25</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>17</v>
@@ -6685,7 +6662,7 @@
     </row>
     <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B49" s="5" t="n">
         <v>1</v>
@@ -6694,7 +6671,7 @@
         <v>15</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>17</v>
@@ -6709,7 +6686,7 @@
     </row>
     <row r="50" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B50" s="5" t="n">
         <v>15</v>
@@ -6718,16 +6695,16 @@
         <v>19</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>14</v>
@@ -6735,7 +6712,7 @@
     </row>
     <row r="51" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B51" s="5" t="n">
         <v>1</v>
@@ -6744,16 +6721,16 @@
         <v>19</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>14</v>
@@ -6818,7 +6795,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>6</v>
@@ -6839,12 +6816,12 @@
         <v>13</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>20</v>
@@ -6865,12 +6842,12 @@
         <v>13</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>4</v>
@@ -6889,12 +6866,12 @@
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>25</v>
@@ -6913,12 +6890,12 @@
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>26</v>
@@ -6937,12 +6914,12 @@
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>25</v>
@@ -6961,12 +6938,12 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>26</v>
@@ -6985,12 +6962,12 @@
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>26</v>
@@ -7011,12 +6988,12 @@
         <v>13</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>25</v>
@@ -7037,12 +7014,12 @@
         <v>13</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>25</v>
@@ -7061,12 +7038,12 @@
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>26</v>
@@ -7085,12 +7062,12 @@
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>11</v>
@@ -7109,12 +7086,12 @@
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>12</v>
@@ -7133,12 +7110,12 @@
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>25</v>
@@ -7157,12 +7134,12 @@
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>26</v>
@@ -7181,12 +7158,12 @@
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>25</v>
@@ -7205,12 +7182,12 @@
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>26</v>
@@ -7229,12 +7206,12 @@
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>26</v>
@@ -7255,12 +7232,12 @@
         <v>13</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>25</v>
@@ -7281,12 +7258,12 @@
         <v>13</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>25</v>
@@ -7305,12 +7282,12 @@
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>26</v>
@@ -7329,12 +7306,12 @@
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>4</v>
@@ -7353,12 +7330,12 @@
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>25</v>
@@ -7377,12 +7354,12 @@
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>26</v>
@@ -7401,12 +7378,12 @@
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>25</v>
@@ -7425,12 +7402,12 @@
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>26</v>
@@ -7449,12 +7426,12 @@
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>26</v>
@@ -7475,12 +7452,12 @@
         <v>13</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>25</v>
@@ -7501,12 +7478,12 @@
         <v>13</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>25</v>
@@ -7525,12 +7502,12 @@
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>26</v>
@@ -7549,12 +7526,12 @@
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>11</v>
@@ -7573,12 +7550,12 @@
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>12</v>
@@ -7597,12 +7574,12 @@
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B34" s="5" t="n">
         <v>25</v>
@@ -7621,12 +7598,12 @@
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B35" s="5" t="n">
         <v>26</v>
@@ -7645,12 +7622,12 @@
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>25</v>
@@ -7669,12 +7646,12 @@
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B37" s="5" t="n">
         <v>26</v>
@@ -7693,12 +7670,12 @@
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>25</v>
@@ -7717,12 +7694,12 @@
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>26</v>
@@ -7741,12 +7718,12 @@
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>18</v>
@@ -7770,7 +7747,7 @@
     </row>
     <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>19</v>
@@ -7794,7 +7771,7 @@
     </row>
     <row r="42" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>19</v>
@@ -7820,7 +7797,7 @@
     </row>
     <row r="43" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>18</v>
@@ -7846,7 +7823,7 @@
     </row>
     <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B44" s="5" t="n">
         <v>25</v>
@@ -7870,7 +7847,7 @@
     </row>
     <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B45" s="5" t="n">
         <v>26</v>
@@ -7894,7 +7871,7 @@
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B46" s="5" t="n">
         <v>6</v>
@@ -7920,7 +7897,7 @@
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B47" s="5" t="n">
         <v>20</v>
@@ -7946,7 +7923,7 @@
     </row>
     <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B48" s="5" t="n">
         <v>20</v>
@@ -7970,7 +7947,7 @@
     </row>
     <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B49" s="5" t="n">
         <v>6</v>
@@ -7994,7 +7971,7 @@
     </row>
     <row r="50" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B50" s="5" t="n">
         <v>20</v>
@@ -8020,7 +7997,7 @@
     </row>
     <row r="51" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B51" s="5" t="n">
         <v>6</v>
@@ -8103,7 +8080,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>3</v>
@@ -8122,12 +8099,12 @@
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>17</v>
@@ -8146,12 +8123,12 @@
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>1</v>
@@ -8172,12 +8149,12 @@
         <v>36</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>2</v>
@@ -8198,12 +8175,12 @@
         <v>36</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>23</v>
@@ -8224,12 +8201,12 @@
         <v>36</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>22</v>
@@ -8250,12 +8227,12 @@
         <v>36</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>22</v>
@@ -8276,12 +8253,12 @@
         <v>36</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>23</v>
@@ -8302,12 +8279,12 @@
         <v>36</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>8</v>
@@ -8328,12 +8305,12 @@
         <v>36</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>9</v>
@@ -8354,12 +8331,12 @@
         <v>36</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>23</v>
@@ -8380,12 +8357,12 @@
         <v>36</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>22</v>
@@ -8406,12 +8383,12 @@
         <v>36</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>1</v>
@@ -8432,12 +8409,12 @@
         <v>36</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>2</v>
@@ -8458,12 +8435,12 @@
         <v>36</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>23</v>
@@ -8484,12 +8461,12 @@
         <v>36</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>22</v>
@@ -8510,12 +8487,12 @@
         <v>36</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>8</v>
@@ -8536,12 +8513,12 @@
         <v>36</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>9</v>
@@ -8562,12 +8539,12 @@
         <v>36</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>1</v>
@@ -8588,12 +8565,12 @@
         <v>36</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>2</v>
@@ -8614,12 +8591,12 @@
         <v>36</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>15</v>
@@ -8640,12 +8617,12 @@
         <v>36</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>16</v>
@@ -8666,12 +8643,12 @@
         <v>36</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>16</v>
@@ -8697,7 +8674,7 @@
     </row>
     <row r="25" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>15</v>
@@ -8723,7 +8700,7 @@
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>15</v>
@@ -8749,7 +8726,7 @@
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>16</v>
@@ -8775,7 +8752,7 @@
     </row>
     <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>3</v>
@@ -8799,7 +8776,7 @@
     </row>
     <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>17</v>
@@ -8823,7 +8800,7 @@
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>17</v>
@@ -8847,7 +8824,7 @@
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>3</v>
@@ -8871,7 +8848,7 @@
     </row>
     <row r="32" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>17</v>
@@ -8897,7 +8874,7 @@
     </row>
     <row r="33" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>3</v>
@@ -8978,7 +8955,7 @@
     </row>
     <row r="2" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>27</v>
@@ -8999,12 +8976,12 @@
         <v>44</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>26</v>
@@ -9025,12 +9002,12 @@
         <v>44</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>27</v>
@@ -9049,12 +9026,12 @@
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>26</v>
@@ -9073,12 +9050,12 @@
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>13</v>
@@ -9097,12 +9074,12 @@
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>12</v>
@@ -9121,12 +9098,12 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>27</v>
@@ -9147,12 +9124,12 @@
         <v>44</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>26</v>
@@ -9173,12 +9150,12 @@
         <v>44</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>6</v>
@@ -9197,12 +9174,12 @@
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>6</v>
@@ -9221,12 +9198,12 @@
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>6</v>
@@ -9245,12 +9222,12 @@
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>5</v>
@@ -9269,12 +9246,12 @@
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>5</v>
@@ -9293,12 +9270,12 @@
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>5</v>
@@ -9317,12 +9294,12 @@
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>27</v>
@@ -9343,12 +9320,12 @@
         <v>44</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>26</v>
@@ -9369,12 +9346,12 @@
         <v>44</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>13</v>
@@ -9393,12 +9370,12 @@
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>12</v>
@@ -9417,12 +9394,12 @@
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>7</v>
@@ -9443,12 +9420,12 @@
         <v>44</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>21</v>
@@ -9469,12 +9446,12 @@
         <v>44</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>20</v>
@@ -9493,12 +9470,12 @@
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>19</v>
@@ -9517,12 +9494,12 @@
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>20</v>
@@ -9548,7 +9525,7 @@
     </row>
     <row r="25" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>19</v>
@@ -9574,7 +9551,7 @@
     </row>
     <row r="26" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>20</v>
@@ -9598,7 +9575,7 @@
     </row>
     <row r="27" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>19</v>
@@ -9622,7 +9599,7 @@
     </row>
     <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>7</v>
@@ -9648,7 +9625,7 @@
     </row>
     <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>21</v>
@@ -9674,7 +9651,7 @@
     </row>
     <row r="30" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>21</v>
@@ -9700,7 +9677,7 @@
     </row>
     <row r="31" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>7</v>

--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2167" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2167" uniqueCount="119">
   <si>
     <t xml:space="preserve">MÊS</t>
   </si>
@@ -60,232 +60,235 @@
     <t xml:space="preserve">Farmacologia dos Injetáveis Corporais e Faciais</t>
   </si>
   <si>
+    <t xml:space="preserve">Aulas síncronas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/08/2026 a 11/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/08/2026 a 25/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SÃO PAULO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU SP 2a.f 100325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prática Clínica - Preenchimento Facial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paulista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prática Clinica        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU SP 2a.f. 010925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procedimento Injetável Estético: Toxina Botulinica - Teoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU SP 220225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU SP 230825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procedimento Injetável Estético: Biostimulador - Teoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procedimento Injetável Estético: Biostimulador - Prática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU SP 2a.f 100324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procedimento Injetável Estético: Toxina Botulinica - Prática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU SP 280226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eletroterapia Aplicada a Estética - Teoria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Após aula prática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tricologia e Terapia Capilares Avançadas - Teoria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agosto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prática Clínica - Fios de Sustentação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procedimento Injetável Estético: Bioestimulador - Teoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eletroterapia Aplicada a Estética - Prática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/09/2029 a 08/09/2026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/09/2026 a 22/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procedimento Injetável Estético: Preenchimento Facial - Teoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tricologia e Terapia Capilares Avançadas - Prática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procedimento Injetável Estético: Preenchimento Facial - Prática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procedimento Injetável Estético: Bioestimulador - Prática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setembro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paulista </t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/10/2026 a 06/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/10/2026 a 20/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procedimentos Intradérmicos e Intramusculares - Teoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avaliação após término da disciplina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procedimento Injetável Estético: Fios de Sustentação - Teoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procedimentos Intradérmicos e Intramusculares - Prática I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procedimento Injetável Estético: Fios de Sustentação - Prática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU RP 220225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ribeirão Preto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prática Clinica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU RP 280226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/09/2026 a 08/09/2026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU 2a.f 020326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santo André</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU SAN 2a.f 020326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU CAMP 220225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campinas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU CAMP 280226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU SJC 280226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">São José dos Campos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU RJ 220225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rio de Janeiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU RJ 230825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU RJ 280226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eletroterapia Aplicada a Estética - Teoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU CE 220225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fortaleza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU CE 230825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU CE 280226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU BH 220225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belo Horizonte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU BH 230825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU BH 280226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tricologia e Terapia Capilares Avançadas - Prática </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU BA 220225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salvador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU BA 280226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU PR 280226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU PR 220225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curitiba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROINSU SC 280226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florianópolis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciencia Estética</t>
+  </si>
+  <si>
     <t xml:space="preserve">Transmissão</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/08/2026 a 11/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/08/2026 a 25/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SÃO PAULO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU SP 2a.f 100325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prática Clínica - Preenchimento Facial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paulista</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prática Clinica        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU SP 2a.f. 010925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procedimento Injetável Estético: Toxina Botulinica - Teoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU SP 220225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU SP 230825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procedimento Injetável Estético: Biostimulador - Teoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procedimento Injetável Estético: Biostimulador - Prática</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU SP 2a.f 100324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procedimento Injetável Estético: Toxina Botulinica - Prática</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU SP 280226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eletroterapia Aplicada a Estética - Teoria </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Após aula prática</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tricologia e Terapia Capilares Avançadas - Teoria </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agosto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prática Clínica - Fios de Sustentação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procedimento Injetável Estético: Bioestimulador - Teoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eletroterapia Aplicada a Estética - Prática</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/09/2029 a 08/09/2026 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/09/2026 a 22/09/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procedimento Injetável Estético: Preenchimento Facial - Teoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tricologia e Terapia Capilares Avançadas - Prática</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procedimento Injetável Estético: Preenchimento Facial - Prática</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procedimento Injetável Estético: Bioestimulador - Prática</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Setembro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paulista </t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/10/2026 a 06/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/10/2026 a 20/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procedimentos Intradérmicos e Intramusculares - Teoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avaliação após término da disciplina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procedimento Injetável Estético: Fios de Sustentação - Teoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procedimentos Intradérmicos e Intramusculares - Prática I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procedimento Injetável Estético: Fios de Sustentação - Prática</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU RP 220225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ribeirão Preto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prática Clinica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU RP 280226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/09/2026 a 08/09/2026 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU 2a.f 020326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santo André</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU SAN 2a.f 020326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU CAMP 220225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campinas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU CAMP 280226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU SJC 280226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">São José dos Campos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU RJ 220225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rio de Janeiro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU RJ 230825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU RJ 280226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eletroterapia Aplicada a Estética - Teoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU CE 220225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fortaleza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU CE 230825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU CE 280226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU BH 220225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belo Horizonte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU BH 230825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU BH 280226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tricologia e Terapia Capilares Avançadas - Prática </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU BA 220225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salvador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU BA 280226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU PR 280226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU PR 220225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curitiba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROINSU SC 280226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florianópolis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ciencia Estética</t>
   </si>
   <si>
     <t xml:space="preserve">05/06/2026 a 09/06/2026</t>
@@ -4157,16 +4160,16 @@
         <v>86</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4180,19 +4183,19 @@
         <v>55</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4206,7 +4209,7 @@
         <v>77</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>78</v>
@@ -4216,7 +4219,7 @@
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4233,16 +4236,16 @@
         <v>86</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4256,19 +4259,19 @@
         <v>79</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4282,7 +4285,7 @@
         <v>72</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>73</v>
@@ -4292,7 +4295,7 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4306,7 +4309,7 @@
         <v>72</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>73</v>
@@ -4316,7 +4319,7 @@
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4330,19 +4333,19 @@
         <v>74</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4356,19 +4359,19 @@
         <v>74</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4385,16 +4388,16 @@
         <v>86</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4408,19 +4411,19 @@
         <v>75</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4434,7 +4437,7 @@
         <v>58</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>59</v>
@@ -4444,7 +4447,7 @@
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4458,7 +4461,7 @@
         <v>58</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>59</v>
@@ -4468,7 +4471,7 @@
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4485,16 +4488,16 @@
         <v>86</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4508,19 +4511,19 @@
         <v>60</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4534,7 +4537,7 @@
         <v>68</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>69</v>
@@ -4544,7 +4547,7 @@
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4558,7 +4561,7 @@
         <v>68</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>69</v>
@@ -4568,7 +4571,7 @@
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4582,19 +4585,19 @@
         <v>70</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>69</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4608,19 +4611,19 @@
         <v>70</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>69</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4637,16 +4640,16 @@
         <v>86</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4660,19 +4663,19 @@
         <v>71</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4686,7 +4689,7 @@
         <v>81</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>82</v>
@@ -4696,7 +4699,7 @@
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4713,16 +4716,16 @@
         <v>86</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4736,19 +4739,19 @@
         <v>80</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4762,7 +4765,7 @@
         <v>63</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>64</v>
@@ -4772,7 +4775,7 @@
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4786,7 +4789,7 @@
         <v>63</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>64</v>
@@ -4796,7 +4799,7 @@
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4810,19 +4813,19 @@
         <v>65</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>64</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4836,19 +4839,19 @@
         <v>65</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>64</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4865,16 +4868,16 @@
         <v>86</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4888,19 +4891,19 @@
         <v>66</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4914,7 +4917,7 @@
         <v>50</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>51</v>
@@ -4924,7 +4927,7 @@
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4938,7 +4941,7 @@
         <v>50</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>51</v>
@@ -4948,7 +4951,7 @@
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4965,16 +4968,16 @@
         <v>86</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4988,19 +4991,19 @@
         <v>53</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5017,16 +5020,16 @@
         <v>86</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5040,19 +5043,19 @@
         <v>83</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5069,16 +5072,16 @@
         <v>86</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5092,19 +5095,19 @@
         <v>61</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5118,7 +5121,7 @@
         <v>21</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>17</v>
@@ -5142,7 +5145,7 @@
         <v>21</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>17</v>
@@ -5166,16 +5169,16 @@
         <v>22</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>14</v>
@@ -5192,16 +5195,16 @@
         <v>22</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>14</v>
@@ -5221,13 +5224,13 @@
         <v>86</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>14</v>
@@ -5244,16 +5247,16 @@
         <v>27</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H45" s="5" t="s">
         <v>14</v>
@@ -5270,16 +5273,16 @@
         <v>9</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>14</v>
@@ -5296,16 +5299,16 @@
         <v>9</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>14</v>
@@ -5322,13 +5325,13 @@
         <v>25</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5" t="s">
@@ -5346,7 +5349,7 @@
         <v>15</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>17</v>
@@ -5370,16 +5373,16 @@
         <v>19</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>14</v>
@@ -5396,16 +5399,16 @@
         <v>19</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>14</v>
@@ -5470,7 +5473,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>1</v>
@@ -5479,24 +5482,24 @@
         <v>55</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>15</v>
@@ -5505,24 +5508,24 @@
         <v>55</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>112</v>
-      </c>
       <c r="H3" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>6</v>
@@ -5541,12 +5544,12 @@
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>27</v>
@@ -5558,21 +5561,21 @@
         <v>10</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>28</v>
@@ -5584,21 +5587,21 @@
         <v>10</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>27</v>
@@ -5617,12 +5620,12 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>28</v>
@@ -5641,12 +5644,12 @@
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>27</v>
@@ -5661,18 +5664,18 @@
         <v>73</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>28</v>
@@ -5687,18 +5690,18 @@
         <v>73</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>27</v>
@@ -5710,21 +5713,21 @@
         <v>10</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>28</v>
@@ -5736,21 +5739,21 @@
         <v>10</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>13</v>
@@ -5769,12 +5772,12 @@
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>14</v>
@@ -5793,12 +5796,12 @@
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>27</v>
@@ -5810,21 +5813,21 @@
         <v>10</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>28</v>
@@ -5836,21 +5839,21 @@
         <v>10</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>27</v>
@@ -5869,12 +5872,12 @@
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>28</v>
@@ -5893,12 +5896,12 @@
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>28</v>
@@ -5913,18 +5916,18 @@
         <v>69</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>27</v>
@@ -5939,18 +5942,18 @@
         <v>69</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>27</v>
@@ -5962,21 +5965,21 @@
         <v>10</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>28</v>
@@ -5988,21 +5991,21 @@
         <v>10</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>6</v>
@@ -6021,12 +6024,12 @@
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>27</v>
@@ -6038,21 +6041,21 @@
         <v>10</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>28</v>
@@ -6064,21 +6067,21 @@
         <v>10</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>27</v>
@@ -6097,12 +6100,12 @@
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>28</v>
@@ -6121,12 +6124,12 @@
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>28</v>
@@ -6141,18 +6144,18 @@
         <v>64</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>27</v>
@@ -6167,18 +6170,18 @@
         <v>64</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>27</v>
@@ -6190,21 +6193,21 @@
         <v>10</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>28</v>
@@ -6216,21 +6219,21 @@
         <v>10</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>13</v>
@@ -6249,12 +6252,12 @@
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>14</v>
@@ -6273,12 +6276,12 @@
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B34" s="5" t="n">
         <v>27</v>
@@ -6290,21 +6293,21 @@
         <v>10</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B35" s="5" t="n">
         <v>28</v>
@@ -6316,21 +6319,21 @@
         <v>10</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>27</v>
@@ -6342,21 +6345,21 @@
         <v>10</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B37" s="5" t="n">
         <v>28</v>
@@ -6368,21 +6371,21 @@
         <v>10</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>27</v>
@@ -6394,21 +6397,21 @@
         <v>10</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>28</v>
@@ -6420,21 +6423,21 @@
         <v>10</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>20</v>
@@ -6458,7 +6461,7 @@
     </row>
     <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>21</v>
@@ -6482,7 +6485,7 @@
     </row>
     <row r="42" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>21</v>
@@ -6497,10 +6500,10 @@
         <v>17</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>14</v>
@@ -6508,7 +6511,7 @@
     </row>
     <row r="43" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>20</v>
@@ -6523,10 +6526,10 @@
         <v>17</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>14</v>
@@ -6534,7 +6537,7 @@
     </row>
     <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B44" s="5" t="n">
         <v>27</v>
@@ -6546,13 +6549,13 @@
         <v>10</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>14</v>
@@ -6560,7 +6563,7 @@
     </row>
     <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B45" s="5" t="n">
         <v>28</v>
@@ -6572,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H45" s="5" t="s">
         <v>14</v>
@@ -6586,7 +6589,7 @@
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B46" s="5" t="n">
         <v>1</v>
@@ -6598,13 +6601,13 @@
         <v>86</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>14</v>
@@ -6612,7 +6615,7 @@
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B47" s="5" t="n">
         <v>15</v>
@@ -6621,16 +6624,16 @@
         <v>9</v>
       </c>
       <c r="D47" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G47" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>14</v>
@@ -6638,7 +6641,7 @@
     </row>
     <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B48" s="5" t="n">
         <v>15</v>
@@ -6647,7 +6650,7 @@
         <v>25</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>17</v>
@@ -6662,7 +6665,7 @@
     </row>
     <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B49" s="5" t="n">
         <v>1</v>
@@ -6671,7 +6674,7 @@
         <v>15</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>17</v>
@@ -6686,7 +6689,7 @@
     </row>
     <row r="50" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B50" s="5" t="n">
         <v>15</v>
@@ -6695,16 +6698,16 @@
         <v>19</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>14</v>
@@ -6712,7 +6715,7 @@
     </row>
     <row r="51" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B51" s="5" t="n">
         <v>1</v>
@@ -6721,16 +6724,16 @@
         <v>19</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>14</v>
@@ -6795,7 +6798,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>6</v>
@@ -6807,7 +6810,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>12</v>
@@ -6816,12 +6819,12 @@
         <v>13</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>20</v>
@@ -6833,7 +6836,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>12</v>
@@ -6842,12 +6845,12 @@
         <v>13</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>4</v>
@@ -6866,12 +6869,12 @@
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>25</v>
@@ -6883,19 +6886,19 @@
         <v>67</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>26</v>
@@ -6907,19 +6910,19 @@
         <v>30</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>25</v>
@@ -6938,12 +6941,12 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>26</v>
@@ -6962,12 +6965,12 @@
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>26</v>
@@ -6988,12 +6991,12 @@
         <v>13</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>25</v>
@@ -7014,12 +7017,12 @@
         <v>13</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>25</v>
@@ -7031,19 +7034,19 @@
         <v>67</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>26</v>
@@ -7055,19 +7058,19 @@
         <v>30</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>11</v>
@@ -7086,12 +7089,12 @@
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>12</v>
@@ -7110,12 +7113,12 @@
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>25</v>
@@ -7127,19 +7130,19 @@
         <v>28</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>26</v>
@@ -7151,19 +7154,19 @@
         <v>30</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>25</v>
@@ -7182,12 +7185,12 @@
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>26</v>
@@ -7206,12 +7209,12 @@
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>26</v>
@@ -7232,12 +7235,12 @@
         <v>13</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>25</v>
@@ -7258,12 +7261,12 @@
         <v>13</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>25</v>
@@ -7275,19 +7278,19 @@
         <v>67</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>26</v>
@@ -7299,19 +7302,19 @@
         <v>30</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>4</v>
@@ -7330,12 +7333,12 @@
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>25</v>
@@ -7347,19 +7350,19 @@
         <v>67</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>26</v>
@@ -7371,19 +7374,19 @@
         <v>30</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>25</v>
@@ -7402,12 +7405,12 @@
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>26</v>
@@ -7426,12 +7429,12 @@
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>26</v>
@@ -7452,12 +7455,12 @@
         <v>13</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>25</v>
@@ -7478,12 +7481,12 @@
         <v>13</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>25</v>
@@ -7495,19 +7498,19 @@
         <v>67</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>26</v>
@@ -7519,19 +7522,19 @@
         <v>30</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>11</v>
@@ -7550,12 +7553,12 @@
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>12</v>
@@ -7574,12 +7577,12 @@
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B34" s="5" t="n">
         <v>25</v>
@@ -7591,19 +7594,19 @@
         <v>28</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B35" s="5" t="n">
         <v>26</v>
@@ -7615,19 +7618,19 @@
         <v>30</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>25</v>
@@ -7639,19 +7642,19 @@
         <v>67</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B37" s="5" t="n">
         <v>26</v>
@@ -7663,19 +7666,19 @@
         <v>30</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>25</v>
@@ -7687,19 +7690,19 @@
         <v>28</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>26</v>
@@ -7711,19 +7714,19 @@
         <v>30</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>18</v>
@@ -7747,7 +7750,7 @@
     </row>
     <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>19</v>
@@ -7771,7 +7774,7 @@
     </row>
     <row r="42" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>19</v>
@@ -7797,7 +7800,7 @@
     </row>
     <row r="43" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>18</v>
@@ -7823,7 +7826,7 @@
     </row>
     <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B44" s="5" t="n">
         <v>25</v>
@@ -7835,7 +7838,7 @@
         <v>28</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>29</v>
@@ -7847,7 +7850,7 @@
     </row>
     <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B45" s="5" t="n">
         <v>26</v>
@@ -7859,7 +7862,7 @@
         <v>30</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>29</v>
@@ -7871,7 +7874,7 @@
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B46" s="5" t="n">
         <v>6</v>
@@ -7883,7 +7886,7 @@
         <v>10</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>12</v>
@@ -7897,7 +7900,7 @@
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B47" s="5" t="n">
         <v>20</v>
@@ -7909,7 +7912,7 @@
         <v>10</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>12</v>
@@ -7923,7 +7926,7 @@
     </row>
     <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B48" s="5" t="n">
         <v>20</v>
@@ -7947,7 +7950,7 @@
     </row>
     <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B49" s="5" t="n">
         <v>6</v>
@@ -7971,7 +7974,7 @@
     </row>
     <row r="50" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B50" s="5" t="n">
         <v>20</v>
@@ -7997,7 +8000,7 @@
     </row>
     <row r="51" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B51" s="5" t="n">
         <v>6</v>
@@ -8080,7 +8083,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>3</v>
@@ -8092,19 +8095,19 @@
         <v>28</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>17</v>
@@ -8116,19 +8119,19 @@
         <v>30</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>1</v>
@@ -8149,12 +8152,12 @@
         <v>36</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>2</v>
@@ -8175,12 +8178,12 @@
         <v>36</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>23</v>
@@ -8201,12 +8204,12 @@
         <v>36</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>22</v>
@@ -8227,12 +8230,12 @@
         <v>36</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>22</v>
@@ -8253,12 +8256,12 @@
         <v>36</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>23</v>
@@ -8279,12 +8282,12 @@
         <v>36</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>8</v>
@@ -8305,12 +8308,12 @@
         <v>36</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>9</v>
@@ -8331,12 +8334,12 @@
         <v>36</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>23</v>
@@ -8357,12 +8360,12 @@
         <v>36</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>22</v>
@@ -8383,12 +8386,12 @@
         <v>36</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>1</v>
@@ -8409,12 +8412,12 @@
         <v>36</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>2</v>
@@ -8435,12 +8438,12 @@
         <v>36</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>23</v>
@@ -8461,12 +8464,12 @@
         <v>36</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>22</v>
@@ -8487,12 +8490,12 @@
         <v>36</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>8</v>
@@ -8513,12 +8516,12 @@
         <v>36</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>9</v>
@@ -8539,12 +8542,12 @@
         <v>36</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>1</v>
@@ -8565,12 +8568,12 @@
         <v>36</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>2</v>
@@ -8591,12 +8594,12 @@
         <v>36</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>15</v>
@@ -8617,12 +8620,12 @@
         <v>36</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>16</v>
@@ -8643,12 +8646,12 @@
         <v>36</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>16</v>
@@ -8674,7 +8677,7 @@
     </row>
     <row r="25" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>15</v>
@@ -8700,7 +8703,7 @@
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>15</v>
@@ -8726,7 +8729,7 @@
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>16</v>
@@ -8752,7 +8755,7 @@
     </row>
     <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>3</v>
@@ -8764,7 +8767,7 @@
         <v>28</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>29</v>
@@ -8776,7 +8779,7 @@
     </row>
     <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>17</v>
@@ -8788,7 +8791,7 @@
         <v>30</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>29</v>
@@ -8800,7 +8803,7 @@
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>17</v>
@@ -8824,7 +8827,7 @@
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>3</v>
@@ -8848,7 +8851,7 @@
     </row>
     <row r="32" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>17</v>
@@ -8874,7 +8877,7 @@
     </row>
     <row r="33" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>3</v>
@@ -8955,7 +8958,7 @@
     </row>
     <row r="2" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>27</v>
@@ -8976,12 +8979,12 @@
         <v>44</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>26</v>
@@ -9002,12 +9005,12 @@
         <v>44</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>27</v>
@@ -9026,12 +9029,12 @@
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>26</v>
@@ -9050,12 +9053,12 @@
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>13</v>
@@ -9074,12 +9077,12 @@
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>12</v>
@@ -9098,12 +9101,12 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>27</v>
@@ -9124,12 +9127,12 @@
         <v>44</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>26</v>
@@ -9150,12 +9153,12 @@
         <v>44</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>6</v>
@@ -9174,12 +9177,12 @@
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>6</v>
@@ -9198,12 +9201,12 @@
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>6</v>
@@ -9222,12 +9225,12 @@
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>5</v>
@@ -9246,12 +9249,12 @@
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>5</v>
@@ -9270,12 +9273,12 @@
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>5</v>
@@ -9294,12 +9297,12 @@
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>27</v>
@@ -9320,12 +9323,12 @@
         <v>44</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>26</v>
@@ -9346,12 +9349,12 @@
         <v>44</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>13</v>
@@ -9370,12 +9373,12 @@
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>12</v>
@@ -9394,12 +9397,12 @@
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>7</v>
@@ -9420,12 +9423,12 @@
         <v>44</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>21</v>
@@ -9446,12 +9449,12 @@
         <v>44</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>20</v>
@@ -9470,12 +9473,12 @@
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>19</v>
@@ -9494,12 +9497,12 @@
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>20</v>
@@ -9525,7 +9528,7 @@
     </row>
     <row r="25" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>19</v>
@@ -9551,7 +9554,7 @@
     </row>
     <row r="26" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>20</v>
@@ -9575,7 +9578,7 @@
     </row>
     <row r="27" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>19</v>
@@ -9599,7 +9602,7 @@
     </row>
     <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>7</v>
@@ -9625,7 +9628,7 @@
     </row>
     <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>21</v>
@@ -9651,7 +9654,7 @@
     </row>
     <row r="30" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>21</v>
@@ -9677,7 +9680,7 @@
     </row>
     <row r="31" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>7</v>

--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -3670,7 +3670,10 @@
       <c r="D124" s="5"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D125" s="5"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="4"/>
+      <c r="E125" s="3"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B126" s="3"/>

--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="98">
   <si>
     <t>DIA</t>
   </si>
@@ -3499,7 +3499,6 @@
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
       <c r="D138" s="5"/>
@@ -3509,7 +3508,9 @@
       <c r="H138" s="2"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="2"/>
+      <c r="A139" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B139" s="10">
         <v>5.0</v>
       </c>
@@ -3533,7 +3534,9 @@
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="2"/>
+      <c r="A140" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B140" s="10">
         <v>6.0</v>
       </c>
@@ -3557,7 +3560,6 @@
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
       <c r="D141" s="5"/>
@@ -3567,7 +3569,9 @@
       <c r="H141" s="2"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="2"/>
+      <c r="A142" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B142" s="10">
         <v>5.0</v>
       </c>
@@ -3591,7 +3595,9 @@
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="2"/>
+      <c r="A143" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B143" s="10">
         <v>6.0</v>
       </c>
@@ -3615,7 +3621,6 @@
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
       <c r="D144" s="5"/>
@@ -3625,7 +3630,9 @@
       <c r="H144" s="2"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="2"/>
+      <c r="A145" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B145" s="10">
         <v>5.0</v>
       </c>
@@ -3649,7 +3656,9 @@
       </c>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="2"/>
+      <c r="A146" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B146" s="10">
         <v>6.0</v>
       </c>
@@ -3673,7 +3682,6 @@
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
       <c r="D147" s="5"/>
@@ -3683,7 +3691,9 @@
       <c r="H147" s="2"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="2"/>
+      <c r="A148" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B148" s="10">
         <v>12.0</v>
       </c>
@@ -3707,7 +3717,9 @@
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="2"/>
+      <c r="A149" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B149" s="10">
         <v>13.0</v>
       </c>
@@ -3731,7 +3743,6 @@
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
       <c r="D150" s="5"/>
@@ -3741,7 +3752,9 @@
       <c r="H150" s="2"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="2"/>
+      <c r="A151" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B151" s="10">
         <v>12.0</v>
       </c>
@@ -3765,7 +3778,9 @@
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="2"/>
+      <c r="A152" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B152" s="10">
         <v>13.0</v>
       </c>
@@ -3788,8 +3803,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="2"/>
+    <row r="153" ht="15.0" customHeight="1">
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
       <c r="D153" s="5"/>
@@ -3799,7 +3813,9 @@
       <c r="H153" s="2"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="2"/>
+      <c r="A154" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B154" s="10">
         <v>19.0</v>
       </c>
@@ -3823,7 +3839,9 @@
       </c>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="2"/>
+      <c r="A155" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B155" s="10">
         <v>20.0</v>
       </c>
@@ -3847,7 +3865,6 @@
       </c>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
       <c r="D156" s="5"/>
@@ -3857,7 +3874,9 @@
       <c r="H156" s="2"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="2"/>
+      <c r="A157" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B157" s="10">
         <v>19.0</v>
       </c>
@@ -3881,7 +3900,9 @@
       </c>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="2"/>
+      <c r="A158" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B158" s="10">
         <v>20.0</v>
       </c>
@@ -3905,7 +3926,9 @@
       </c>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="2"/>
+      <c r="A159" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B159" s="10">
         <v>19.0</v>
       </c>
@@ -3929,7 +3952,9 @@
       </c>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="2"/>
+      <c r="A160" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B160" s="10">
         <v>20.0</v>
       </c>
@@ -3953,7 +3978,6 @@
       </c>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
       <c r="D161" s="5"/>
@@ -3963,7 +3987,9 @@
       <c r="H161" s="2"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="2"/>
+      <c r="A162" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B162" s="10">
         <v>26.0</v>
       </c>
@@ -3987,7 +4013,9 @@
       </c>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="2"/>
+      <c r="A163" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B163" s="10">
         <v>27.0</v>
       </c>
@@ -4011,7 +4039,6 @@
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
       <c r="D164" s="5"/>
@@ -4021,7 +4048,9 @@
       <c r="H164" s="2"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="2"/>
+      <c r="A165" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B165" s="10">
         <v>26.0</v>
       </c>
@@ -4045,7 +4074,9 @@
       </c>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="2"/>
+      <c r="A166" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B166" s="10">
         <v>27.0</v>
       </c>
@@ -4069,7 +4100,9 @@
       </c>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="2"/>
+      <c r="A167" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B167" s="10">
         <v>26.0</v>
       </c>
@@ -4093,7 +4126,9 @@
       </c>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="2"/>
+      <c r="A168" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B168" s="10">
         <v>27.0</v>
       </c>
@@ -4117,7 +4152,6 @@
       </c>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
       <c r="D169" s="5"/>
@@ -4127,7 +4161,9 @@
       <c r="H169" s="2"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="2"/>
+      <c r="A170" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B170" s="10">
         <v>26.0</v>
       </c>
@@ -4151,7 +4187,9 @@
       </c>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="2"/>
+      <c r="A171" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B171" s="10">
         <v>27.0</v>
       </c>
@@ -4175,7 +4213,6 @@
       </c>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
       <c r="D172" s="5"/>
@@ -4185,7 +4222,9 @@
       <c r="H172" s="2"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="2"/>
+      <c r="A173" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B173" s="7">
         <v>22.0</v>
       </c>
@@ -4209,7 +4248,9 @@
       </c>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="2"/>
+      <c r="A174" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B174" s="7">
         <v>23.0</v>
       </c>
@@ -4233,7 +4274,6 @@
       </c>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
       <c r="D175" s="5"/>
@@ -4243,7 +4283,9 @@
       <c r="H175" s="2"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="2"/>
+      <c r="A176" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B176" s="7">
         <v>22.0</v>
       </c>
@@ -4267,7 +4309,9 @@
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="2"/>
+      <c r="A177" s="7" t="s">
+        <v>86</v>
+      </c>
       <c r="B177" s="7">
         <v>23.0</v>
       </c>

--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="98">
   <si>
     <t xml:space="preserve">MÊS</t>
   </si>
@@ -281,9 +281,6 @@
   </si>
   <si>
     <t xml:space="preserve">PROINSU SAN 2a.f 020326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">setembro</t>
   </si>
   <si>
     <t xml:space="preserve">PROINSU 2a.f. 010925</t>
@@ -3506,7 +3503,7 @@
     </row>
     <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B134" s="9" t="n">
         <v>7</v>
@@ -3532,7 +3529,7 @@
     </row>
     <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B135" s="9" t="n">
         <v>21</v>
@@ -3558,13 +3555,13 @@
     </row>
     <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B136" s="9" t="n">
         <v>7</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D136" s="10" t="s">
         <v>37</v>
@@ -3584,13 +3581,13 @@
     </row>
     <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B137" s="9" t="n">
         <v>21</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D137" s="10" t="s">
         <v>39</v>
@@ -3619,7 +3616,7 @@
     </row>
     <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B139" s="3" t="n">
         <v>5</v>
@@ -3628,7 +3625,7 @@
         <v>75</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E139" s="8" t="s">
         <v>74</v>
@@ -3637,7 +3634,7 @@
         <v>29</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H139" s="8" t="s">
         <v>74</v>
@@ -3645,7 +3642,7 @@
     </row>
     <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B140" s="3" t="n">
         <v>6</v>
@@ -3654,7 +3651,7 @@
         <v>75</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E140" s="8" t="s">
         <v>74</v>
@@ -3663,7 +3660,7 @@
         <v>29</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H140" s="8" t="s">
         <v>74</v>
@@ -3680,7 +3677,7 @@
     </row>
     <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B142" s="3" t="n">
         <v>5</v>
@@ -3689,7 +3686,7 @@
         <v>78</v>
       </c>
       <c r="D142" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E142" s="8" t="s">
         <v>77</v>
@@ -3698,7 +3695,7 @@
         <v>29</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H142" s="8" t="s">
         <v>77</v>
@@ -3706,7 +3703,7 @@
     </row>
     <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B143" s="3" t="n">
         <v>6</v>
@@ -3715,7 +3712,7 @@
         <v>78</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E143" s="8" t="s">
         <v>77</v>
@@ -3724,7 +3721,7 @@
         <v>29</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H143" s="8" t="s">
         <v>77</v>
@@ -3741,16 +3738,16 @@
     </row>
     <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B145" s="3" t="n">
         <v>5</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E145" s="8" t="s">
         <v>80</v>
@@ -3759,7 +3756,7 @@
         <v>29</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H145" s="8" t="s">
         <v>80</v>
@@ -3767,16 +3764,16 @@
     </row>
     <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B146" s="3" t="n">
         <v>6</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E146" s="8" t="s">
         <v>80</v>
@@ -3785,7 +3782,7 @@
         <v>29</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H146" s="8" t="s">
         <v>80</v>
@@ -3802,7 +3799,7 @@
     </row>
     <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B148" s="3" t="n">
         <v>12</v>
@@ -3811,7 +3808,7 @@
         <v>50</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>49</v>
@@ -3820,7 +3817,7 @@
         <v>29</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H148" s="8" t="s">
         <v>29</v>
@@ -3828,7 +3825,7 @@
     </row>
     <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B149" s="3" t="n">
         <v>13</v>
@@ -3837,7 +3834,7 @@
         <v>50</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E149" s="8" t="s">
         <v>49</v>
@@ -3846,7 +3843,7 @@
         <v>29</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H149" s="8" t="s">
         <v>29</v>
@@ -3863,7 +3860,7 @@
     </row>
     <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B151" s="3" t="n">
         <v>12</v>
@@ -3872,7 +3869,7 @@
         <v>44</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E151" s="8" t="s">
         <v>42</v>
@@ -3881,7 +3878,7 @@
         <v>29</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H151" s="8" t="s">
         <v>42</v>
@@ -3889,7 +3886,7 @@
     </row>
     <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B152" s="3" t="n">
         <v>13</v>
@@ -3898,7 +3895,7 @@
         <v>44</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E152" s="8" t="s">
         <v>42</v>
@@ -3907,7 +3904,7 @@
         <v>29</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H152" s="8" t="s">
         <v>42</v>
@@ -3924,7 +3921,7 @@
     </row>
     <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B154" s="3" t="n">
         <v>19</v>
@@ -3933,7 +3930,7 @@
         <v>51</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E154" s="8" t="s">
         <v>52</v>
@@ -3942,7 +3939,7 @@
         <v>29</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H154" s="8" t="s">
         <v>52</v>
@@ -3950,7 +3947,7 @@
     </row>
     <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B155" s="3" t="n">
         <v>20</v>
@@ -3959,7 +3956,7 @@
         <v>51</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E155" s="8" t="s">
         <v>52</v>
@@ -3968,7 +3965,7 @@
         <v>29</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H155" s="8" t="s">
         <v>52</v>
@@ -3985,7 +3982,7 @@
     </row>
     <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B157" s="3" t="n">
         <v>19</v>
@@ -3994,7 +3991,7 @@
         <v>27</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>17</v>
@@ -4003,7 +4000,7 @@
         <v>29</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H157" s="8" t="s">
         <v>17</v>
@@ -4011,7 +4008,7 @@
     </row>
     <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B158" s="3" t="n">
         <v>20</v>
@@ -4020,7 +4017,7 @@
         <v>27</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E158" s="9" t="s">
         <v>17</v>
@@ -4029,7 +4026,7 @@
         <v>29</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H158" s="8" t="s">
         <v>17</v>
@@ -4037,7 +4034,7 @@
     </row>
     <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B159" s="3" t="n">
         <v>19</v>
@@ -4046,7 +4043,7 @@
         <v>22</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E159" s="8" t="s">
         <v>17</v>
@@ -4063,7 +4060,7 @@
     </row>
     <row r="160" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B160" s="3" t="n">
         <v>20</v>
@@ -4072,7 +4069,7 @@
         <v>22</v>
       </c>
       <c r="D160" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E160" s="8" t="s">
         <v>17</v>
@@ -4098,7 +4095,7 @@
     </row>
     <row r="162" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B162" s="3" t="n">
         <v>26</v>
@@ -4124,7 +4121,7 @@
     </row>
     <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B163" s="3" t="n">
         <v>27</v>
@@ -4159,7 +4156,7 @@
     </row>
     <row r="165" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B165" s="3" t="n">
         <v>26</v>
@@ -4168,7 +4165,7 @@
         <v>67</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E165" s="8" t="s">
         <v>65</v>
@@ -4177,7 +4174,7 @@
         <v>29</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H165" s="8" t="s">
         <v>65</v>
@@ -4185,7 +4182,7 @@
     </row>
     <row r="166" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B166" s="3" t="n">
         <v>27</v>
@@ -4194,7 +4191,7 @@
         <v>67</v>
       </c>
       <c r="D166" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E166" s="8" t="s">
         <v>65</v>
@@ -4203,7 +4200,7 @@
         <v>29</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H166" s="8" t="s">
         <v>65</v>
@@ -4211,7 +4208,7 @@
     </row>
     <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B167" s="3" t="n">
         <v>26</v>
@@ -4220,7 +4217,7 @@
         <v>66</v>
       </c>
       <c r="D167" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E167" s="8" t="s">
         <v>65</v>
@@ -4237,7 +4234,7 @@
     </row>
     <row r="168" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B168" s="3" t="n">
         <v>27</v>
@@ -4272,7 +4269,7 @@
     </row>
     <row r="170" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B170" s="3" t="n">
         <v>26</v>
@@ -4298,7 +4295,7 @@
     </row>
     <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B171" s="3" t="n">
         <v>27</v>
@@ -4333,22 +4330,22 @@
     </row>
     <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B173" s="8" t="n">
         <v>22</v>
       </c>
       <c r="C173" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D173" s="8" t="s">
         <v>95</v>
-      </c>
-      <c r="D173" s="8" t="s">
-        <v>96</v>
       </c>
       <c r="E173" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F173" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G173" s="14" t="s">
         <v>36</v>
@@ -4359,7 +4356,7 @@
     </row>
     <row r="174" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B174" s="8" t="n">
         <v>23</v>
@@ -4368,13 +4365,13 @@
         <v>81</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E174" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F174" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G174" s="14" t="s">
         <v>36</v>
@@ -4394,7 +4391,7 @@
     </row>
     <row r="176" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B176" s="8" t="n">
         <v>22</v>
@@ -4403,13 +4400,13 @@
         <v>84</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E176" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F176" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G176" s="14" t="s">
         <v>36</v>
@@ -4420,7 +4417,7 @@
     </row>
     <row r="177" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B177" s="8" t="n">
         <v>23</v>
@@ -4429,13 +4426,13 @@
         <v>84</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E177" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F177" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G177" s="14" t="s">
         <v>36</v>

--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="124">
+  <si>
+    <t>MÊS</t>
+  </si>
   <si>
     <t>DIA</t>
   </si>
@@ -580,7 +583,7 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -858,27 +861,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -901,28 +906,28 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="6">
         <v>6.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
@@ -945,26 +950,26 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="6">
         <v>6.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
@@ -987,28 +992,28 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="6">
         <v>6.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -1031,26 +1036,26 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="6">
         <v>18.0</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -1073,28 +1078,28 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="6">
         <v>18.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -1117,26 +1122,26 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="6">
         <v>19.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -1159,28 +1164,28 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="6">
         <v>19.0</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -1203,28 +1208,28 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="6">
         <v>20.0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -1247,26 +1252,26 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" s="6">
         <v>20.0</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
@@ -1289,28 +1294,28 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" s="6">
         <v>20.0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
@@ -1333,26 +1338,26 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" s="6">
         <v>25.0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
@@ -1375,26 +1380,26 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" s="6">
         <v>26.0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
@@ -1417,26 +1422,26 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="6">
         <v>3.0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
@@ -1459,28 +1464,28 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" s="6">
         <v>3.0</v>
       </c>
       <c r="C15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="8" t="s">
         <v>14</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>13</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
@@ -1503,26 +1508,26 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" s="6">
         <v>3.0</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
@@ -1545,28 +1550,28 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" s="6">
         <v>15.0</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
@@ -1589,28 +1594,28 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" s="6">
         <v>15.0</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>35</v>
-      </c>
       <c r="H18" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
@@ -1633,28 +1638,28 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" s="6">
         <v>16.0</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
@@ -1677,28 +1682,28 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" s="6">
         <v>16.0</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
@@ -1721,26 +1726,26 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" s="6">
         <v>17.0</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
@@ -1763,28 +1768,28 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" s="6">
         <v>17.0</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
@@ -1807,28 +1812,28 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="6">
         <v>17.0</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
@@ -2103,26 +2108,26 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B33" s="6">
         <v>11.0</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G33" s="8"/>
       <c r="H33" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I33" s="8"/>
       <c r="J33" s="8"/>
@@ -2145,26 +2150,26 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B34" s="6">
         <v>12.0</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G34" s="8"/>
       <c r="H34" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I34" s="8"/>
       <c r="J34" s="8"/>
@@ -2187,26 +2192,26 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B35" s="6">
         <v>25.0</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I35" s="8"/>
       <c r="J35" s="8"/>
@@ -2229,26 +2234,26 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B36" s="6">
         <v>26.0</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D36" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
@@ -2271,28 +2276,28 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B37" s="6">
         <v>8.0</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
@@ -2315,28 +2320,28 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B38" s="6">
         <v>9.0</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
@@ -2443,28 +2448,28 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B42" s="6">
         <v>6.0</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I42" s="8"/>
       <c r="J42" s="8"/>
@@ -2487,28 +2492,28 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B43" s="6">
         <v>20.0</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
@@ -2531,26 +2536,26 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B44" s="6">
         <v>3.0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G44" s="8"/>
       <c r="H44" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I44" s="8"/>
       <c r="J44" s="8"/>
@@ -2573,26 +2578,26 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B45" s="6">
         <v>17.0</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D45" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="G45" s="8"/>
       <c r="H45" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
@@ -2699,26 +2704,26 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B49" s="6">
         <v>11.0</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G49" s="8"/>
       <c r="H49" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
@@ -2741,26 +2746,26 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B50" s="6">
         <v>12.0</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G50" s="8"/>
       <c r="H50" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I50" s="8"/>
       <c r="J50" s="8"/>
@@ -2783,26 +2788,26 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B51" s="6">
         <v>25.0</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G51" s="8"/>
       <c r="H51" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I51" s="8"/>
       <c r="J51" s="8"/>
@@ -2825,26 +2830,26 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B52" s="6">
         <v>26.0</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D52" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="G52" s="8"/>
       <c r="H52" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I52" s="8"/>
       <c r="J52" s="8"/>
@@ -2867,28 +2872,28 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B53" s="6">
         <v>8.0</v>
       </c>
       <c r="C53" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D53" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>48</v>
-      </c>
       <c r="F53" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
@@ -2911,28 +2916,28 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B54" s="6">
         <v>9.0</v>
       </c>
       <c r="C54" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D54" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>48</v>
-      </c>
       <c r="F54" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I54" s="8"/>
       <c r="J54" s="8"/>
@@ -3039,26 +3044,26 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B58" s="6">
         <v>25.0</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G58" s="8"/>
       <c r="H58" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I58" s="8"/>
       <c r="J58" s="8"/>
@@ -3081,26 +3086,26 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B59" s="6">
         <v>26.0</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D59" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="G59" s="8"/>
       <c r="H59" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I59" s="8"/>
       <c r="J59" s="8"/>
@@ -3123,28 +3128,28 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B60" s="6">
         <v>15.0</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I60" s="8"/>
       <c r="J60" s="8"/>
@@ -3167,28 +3172,28 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B61" s="6">
         <v>16.0</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I61" s="8"/>
       <c r="J61" s="8"/>
@@ -3295,22 +3300,22 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B65" s="6">
         <v>25.0</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G65" s="8"/>
       <c r="H65" s="8"/>
@@ -3335,28 +3340,28 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B66" s="6">
         <v>25.0</v>
       </c>
       <c r="C66" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D66" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E66" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="F66" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
@@ -3379,26 +3384,26 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B67" s="6">
         <v>26.0</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G67" s="8"/>
       <c r="H67" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I67" s="8"/>
       <c r="J67" s="8"/>
@@ -3421,28 +3426,28 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B68" s="6">
         <v>26.0</v>
       </c>
       <c r="C68" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E68" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D68" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="F68" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
@@ -3465,26 +3470,26 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B69" s="6">
         <v>25.0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G69" s="6"/>
       <c r="H69" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I69" s="8"/>
       <c r="J69" s="8"/>
@@ -3507,26 +3512,26 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B70" s="6">
         <v>26.0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D70" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="G70" s="6"/>
       <c r="H70" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I70" s="8"/>
       <c r="J70" s="8"/>
@@ -3549,28 +3554,28 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B71" s="6">
         <v>22.0</v>
       </c>
       <c r="C71" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E71" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D71" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="F71" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I71" s="8"/>
       <c r="J71" s="8"/>
@@ -3593,28 +3598,28 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B72" s="6">
         <v>23.0</v>
       </c>
       <c r="C72" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E72" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D72" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="F72" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I72" s="8"/>
       <c r="J72" s="8"/>
@@ -3721,26 +3726,26 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B76" s="6">
         <v>25.0</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G76" s="8"/>
       <c r="H76" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I76" s="8"/>
       <c r="J76" s="8"/>
@@ -3763,28 +3768,28 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B77" s="6">
         <v>25.0</v>
       </c>
       <c r="C77" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E77" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D77" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="F77" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I77" s="8"/>
       <c r="J77" s="8"/>
@@ -3807,26 +3812,26 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B78" s="6">
         <v>26.0</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G78" s="8"/>
       <c r="H78" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I78" s="8"/>
       <c r="J78" s="8"/>
@@ -3849,28 +3854,28 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B79" s="6">
         <v>26.0</v>
       </c>
       <c r="C79" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E79" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D79" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="F79" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I79" s="8"/>
       <c r="J79" s="8"/>
@@ -3893,26 +3898,26 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B80" s="6">
         <v>25.0</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G80" s="8"/>
       <c r="H80" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I80" s="8"/>
       <c r="J80" s="8"/>
@@ -3935,26 +3940,26 @@
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B81" s="6">
         <v>26.0</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D81" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="G81" s="8"/>
       <c r="H81" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I81" s="8"/>
       <c r="J81" s="8"/>
@@ -3977,28 +3982,28 @@
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B82" s="6">
         <v>22.0</v>
       </c>
       <c r="C82" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E82" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D82" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="F82" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I82" s="8"/>
       <c r="J82" s="8"/>
@@ -4021,28 +4026,28 @@
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B83" s="6">
         <v>23.0</v>
       </c>
       <c r="C83" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E83" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D83" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="F83" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I83" s="8"/>
       <c r="J83" s="8"/>
@@ -4149,26 +4154,26 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B87" s="6">
         <v>25.0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G87" s="8"/>
       <c r="H87" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I87" s="8"/>
       <c r="J87" s="8"/>
@@ -4191,28 +4196,28 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B88" s="6">
         <v>25.0</v>
       </c>
       <c r="C88" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E88" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D88" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E88" s="6" t="s">
-        <v>64</v>
-      </c>
       <c r="F88" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I88" s="8"/>
       <c r="J88" s="8"/>
@@ -4235,26 +4240,26 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B89" s="6">
         <v>26.0</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G89" s="8"/>
       <c r="H89" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I89" s="8"/>
       <c r="J89" s="8"/>
@@ -4277,28 +4282,28 @@
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B90" s="6">
         <v>26.0</v>
       </c>
       <c r="C90" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E90" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D90" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E90" s="6" t="s">
-        <v>64</v>
-      </c>
       <c r="F90" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I90" s="8"/>
       <c r="J90" s="8"/>
@@ -4321,26 +4326,26 @@
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B91" s="6">
         <v>25.0</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G91" s="8"/>
       <c r="H91" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I91" s="8"/>
       <c r="J91" s="8"/>
@@ -4363,26 +4368,26 @@
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B92" s="6">
         <v>26.0</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D92" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F92" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="G92" s="8"/>
       <c r="H92" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I92" s="8"/>
       <c r="J92" s="8"/>
@@ -4405,28 +4410,28 @@
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B93" s="6">
         <v>22.0</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I93" s="8"/>
       <c r="J93" s="8"/>
@@ -4449,28 +4454,28 @@
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B94" s="6">
         <v>22.0</v>
       </c>
       <c r="C94" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E94" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D94" s="7" t="s">
+      <c r="F94" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G94" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E94" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G94" s="6" t="s">
-        <v>35</v>
-      </c>
       <c r="H94" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I94" s="8"/>
       <c r="J94" s="8"/>
@@ -4493,28 +4498,28 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B95" s="6">
         <v>23.0</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I95" s="8"/>
       <c r="J95" s="8"/>
@@ -4537,28 +4542,28 @@
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B96" s="6">
         <v>23.0</v>
       </c>
       <c r="C96" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E96" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D96" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>64</v>
-      </c>
       <c r="F96" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I96" s="8"/>
       <c r="J96" s="8"/>
@@ -4609,28 +4614,28 @@
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B98" s="6">
         <v>26.0</v>
       </c>
       <c r="C98" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E98" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D98" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>64</v>
-      </c>
       <c r="F98" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I98" s="8"/>
       <c r="J98" s="8"/>
@@ -4653,26 +4658,26 @@
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B99" s="6">
         <v>27.0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G99" s="8"/>
       <c r="H99" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I99" s="8"/>
       <c r="J99" s="8"/>
@@ -4695,28 +4700,28 @@
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B100" s="6">
         <v>27.0</v>
       </c>
       <c r="C100" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E100" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D100" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>64</v>
-      </c>
       <c r="F100" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I100" s="8"/>
       <c r="J100" s="8"/>
@@ -4767,28 +4772,28 @@
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B102" s="6">
         <v>4.0</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G102" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>73</v>
       </c>
       <c r="I102" s="8"/>
       <c r="J102" s="8"/>
@@ -4811,28 +4816,28 @@
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B103" s="6">
         <v>25.0</v>
       </c>
       <c r="C103" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G103" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D103" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E103" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F103" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G103" s="8" t="s">
+      <c r="H103" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>73</v>
       </c>
       <c r="I103" s="8"/>
       <c r="J103" s="8"/>
@@ -4855,28 +4860,28 @@
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B104" s="6">
         <v>26.0</v>
       </c>
       <c r="C104" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G104" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D104" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E104" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F104" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G104" s="8" t="s">
+      <c r="H104" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>73</v>
       </c>
       <c r="I104" s="8"/>
       <c r="J104" s="8"/>
@@ -4899,28 +4904,28 @@
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B105" s="6">
         <v>1.0</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I105" s="8"/>
       <c r="J105" s="8"/>
@@ -4943,28 +4948,28 @@
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B106" s="6">
         <v>2.0</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I106" s="8"/>
       <c r="J106" s="8"/>
@@ -5071,28 +5076,28 @@
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B110" s="6">
         <v>4.0</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I110" s="8"/>
       <c r="J110" s="8"/>
@@ -5115,28 +5120,28 @@
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B111" s="6">
         <v>25.0</v>
       </c>
       <c r="C111" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H111" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="D111" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E111" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F111" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G111" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H111" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I111" s="8"/>
       <c r="J111" s="8"/>
@@ -5159,28 +5164,28 @@
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B112" s="6">
         <v>26.0</v>
       </c>
       <c r="C112" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E112" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G112" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="D112" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E112" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F112" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G112" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I112" s="8"/>
       <c r="J112" s="8"/>
@@ -5203,28 +5208,28 @@
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B113" s="6">
         <v>1.0</v>
       </c>
       <c r="C113" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E113" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D113" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E113" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="F113" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I113" s="8"/>
       <c r="J113" s="8"/>
@@ -5247,28 +5252,28 @@
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B114" s="6">
         <v>2.0</v>
       </c>
       <c r="C114" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E114" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D114" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E114" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="F114" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I114" s="8"/>
       <c r="J114" s="8"/>
@@ -5375,28 +5380,28 @@
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B118" s="6">
         <v>25.0</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H118" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I118" s="8"/>
       <c r="J118" s="8"/>
@@ -5419,28 +5424,28 @@
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B119" s="6">
         <v>26.0</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H119" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I119" s="8"/>
       <c r="J119" s="8"/>
@@ -5463,28 +5468,28 @@
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B120" s="6">
         <v>1.0</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H120" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I120" s="8"/>
       <c r="J120" s="8"/>
@@ -5507,28 +5512,28 @@
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B121" s="6">
         <v>2.0</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H121" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I121" s="8"/>
       <c r="J121" s="8"/>
@@ -5635,28 +5640,28 @@
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B125" s="6">
         <v>22.0</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G125" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H125" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I125" s="8"/>
       <c r="J125" s="8"/>
@@ -5679,28 +5684,28 @@
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B126" s="6">
         <v>23.0</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I126" s="8"/>
       <c r="J126" s="8"/>
@@ -5751,28 +5756,28 @@
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B128" s="6">
         <v>22.0</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H128" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I128" s="8"/>
       <c r="J128" s="8"/>
@@ -5795,28 +5800,28 @@
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B129" s="6">
         <v>23.0</v>
       </c>
       <c r="C129" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D129" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D129" s="6" t="s">
-        <v>83</v>
-      </c>
       <c r="E129" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G129" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H129" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I129" s="8"/>
       <c r="J129" s="8"/>
@@ -5867,28 +5872,28 @@
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B131" s="12">
         <v>7.0</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E131" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F131" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G131" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H131" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I131" s="8"/>
       <c r="J131" s="8"/>
@@ -5911,28 +5916,28 @@
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B132" s="12">
         <v>21.0</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E132" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F132" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G132" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H132" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I132" s="8"/>
       <c r="J132" s="8"/>
@@ -5983,28 +5988,28 @@
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B134" s="12">
         <v>7.0</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E134" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F134" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G134" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H134" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I134" s="8"/>
       <c r="J134" s="8"/>
@@ -6027,28 +6032,28 @@
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B135" s="12">
         <v>21.0</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D135" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E135" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F135" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G135" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H135" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I135" s="8"/>
       <c r="J135" s="8"/>
@@ -6071,28 +6076,28 @@
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B136" s="12">
         <v>7.0</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D136" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E136" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F136" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G136" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H136" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I136" s="8"/>
       <c r="J136" s="8"/>
@@ -6115,28 +6120,28 @@
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B137" s="12">
         <v>21.0</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D137" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E137" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F137" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G137" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H137" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I137" s="8"/>
       <c r="J137" s="8"/>
@@ -6187,28 +6192,28 @@
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B139" s="8">
         <v>5.0</v>
       </c>
       <c r="C139" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G139" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D139" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E139" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F139" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G139" s="8" t="s">
+      <c r="H139" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="H139" s="8" t="s">
-        <v>73</v>
       </c>
       <c r="I139" s="8"/>
       <c r="J139" s="8"/>
@@ -6231,28 +6236,28 @@
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B140" s="8">
         <v>6.0</v>
       </c>
       <c r="C140" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G140" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D140" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E140" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F140" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G140" s="8" t="s">
+      <c r="H140" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="H140" s="8" t="s">
-        <v>73</v>
       </c>
       <c r="I140" s="8"/>
       <c r="J140" s="8"/>
@@ -6303,28 +6308,28 @@
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B142" s="8">
         <v>5.0</v>
       </c>
       <c r="C142" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E142" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D142" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E142" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="F142" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G142" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H142" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I142" s="8"/>
       <c r="J142" s="8"/>
@@ -6347,28 +6352,28 @@
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B143" s="8">
         <v>6.0</v>
       </c>
       <c r="C143" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E143" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D143" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E143" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="F143" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H143" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I143" s="8"/>
       <c r="J143" s="8"/>
@@ -6419,28 +6424,28 @@
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B145" s="8">
         <v>5.0</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H145" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I145" s="8"/>
       <c r="J145" s="8"/>
@@ -6463,28 +6468,28 @@
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B146" s="8">
         <v>6.0</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G146" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H146" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I146" s="8"/>
       <c r="J146" s="8"/>
@@ -6535,28 +6540,28 @@
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B148" s="8">
         <v>12.0</v>
       </c>
       <c r="C148" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D148" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E148" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D148" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="E148" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="F148" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G148" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H148" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I148" s="8"/>
       <c r="J148" s="8"/>
@@ -6579,28 +6584,28 @@
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B149" s="8">
         <v>13.0</v>
       </c>
       <c r="C149" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D149" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E149" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D149" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E149" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="F149" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G149" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H149" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I149" s="8"/>
       <c r="J149" s="8"/>
@@ -6651,28 +6656,28 @@
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B151" s="8">
         <v>12.0</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H151" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I151" s="8"/>
       <c r="J151" s="8"/>
@@ -6695,28 +6700,28 @@
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B152" s="8">
         <v>13.0</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G152" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H152" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I152" s="8"/>
       <c r="J152" s="8"/>
@@ -6767,28 +6772,28 @@
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B154" s="8">
         <v>19.0</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H154" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I154" s="8"/>
       <c r="J154" s="8"/>
@@ -6811,28 +6816,28 @@
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B155" s="8">
         <v>20.0</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H155" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I155" s="8"/>
       <c r="J155" s="8"/>
@@ -6883,28 +6888,28 @@
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B157" s="8">
         <v>19.0</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E157" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H157" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I157" s="8"/>
       <c r="J157" s="8"/>
@@ -6927,28 +6932,28 @@
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B158" s="8">
         <v>20.0</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E158" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H158" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I158" s="8"/>
       <c r="J158" s="8"/>
@@ -6971,28 +6976,28 @@
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B159" s="8">
         <v>19.0</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E159" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H159" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I159" s="8"/>
       <c r="J159" s="8"/>
@@ -7015,28 +7020,28 @@
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B160" s="8">
         <v>20.0</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D160" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E160" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G160" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H160" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I160" s="8"/>
       <c r="J160" s="8"/>
@@ -7087,28 +7092,28 @@
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B162" s="8">
         <v>26.0</v>
       </c>
       <c r="C162" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E162" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D162" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E162" s="8" t="s">
-        <v>53</v>
-      </c>
       <c r="F162" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H162" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I162" s="8"/>
       <c r="J162" s="8"/>
@@ -7131,28 +7136,28 @@
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B163" s="8">
         <v>27.0</v>
       </c>
       <c r="C163" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D163" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E163" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D163" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E163" s="8" t="s">
-        <v>53</v>
-      </c>
       <c r="F163" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H163" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I163" s="8"/>
       <c r="J163" s="8"/>
@@ -7203,28 +7208,28 @@
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B165" s="8">
         <v>26.0</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F165" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H165" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I165" s="8"/>
       <c r="J165" s="8"/>
@@ -7247,28 +7252,28 @@
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B166" s="8">
         <v>27.0</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D166" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E166" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F166" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H166" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I166" s="8"/>
       <c r="J166" s="8"/>
@@ -7291,28 +7296,28 @@
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B167" s="8">
         <v>26.0</v>
       </c>
       <c r="C167" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D167" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E167" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D167" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E167" s="8" t="s">
-        <v>64</v>
-      </c>
       <c r="F167" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G167" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H167" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I167" s="8"/>
       <c r="J167" s="8"/>
@@ -7335,28 +7340,28 @@
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B168" s="8">
         <v>27.0</v>
       </c>
       <c r="C168" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D168" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E168" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D168" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E168" s="8" t="s">
-        <v>64</v>
-      </c>
       <c r="F168" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H168" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I168" s="8"/>
       <c r="J168" s="8"/>
@@ -7407,28 +7412,28 @@
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B170" s="8">
         <v>26.0</v>
       </c>
       <c r="C170" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D170" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E170" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D170" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E170" s="8" t="s">
-        <v>60</v>
-      </c>
       <c r="F170" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H170" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I170" s="8"/>
       <c r="J170" s="8"/>
@@ -7451,28 +7456,28 @@
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B171" s="8">
         <v>27.0</v>
       </c>
       <c r="C171" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D171" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E171" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D171" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E171" s="8" t="s">
-        <v>60</v>
-      </c>
       <c r="F171" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G171" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H171" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I171" s="8"/>
       <c r="J171" s="8"/>
@@ -7523,28 +7528,28 @@
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B173" s="8">
         <v>22.0</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F173" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G173" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H173" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I173" s="8"/>
       <c r="J173" s="8"/>
@@ -7567,28 +7572,28 @@
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B174" s="8">
         <v>23.0</v>
       </c>
       <c r="C174" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D174" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E174" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F174" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E174" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F174" s="12" t="s">
-        <v>98</v>
-      </c>
       <c r="G174" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I174" s="8"/>
       <c r="J174" s="8"/>
@@ -7639,28 +7644,28 @@
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B176" s="8">
         <v>22.0</v>
       </c>
       <c r="C176" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F176" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G176" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H176" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I176" s="8"/>
       <c r="J176" s="8"/>
@@ -7683,28 +7688,28 @@
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B177" s="8">
         <v>23.0</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D177" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F177" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E177" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F177" s="12" t="s">
-        <v>98</v>
-      </c>
       <c r="G177" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H177" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I177" s="8"/>
       <c r="J177" s="8"/>
@@ -7755,28 +7760,28 @@
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B179" s="8">
         <v>5.0</v>
       </c>
       <c r="C179" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E179" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F179" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G179" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H179" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I179" s="8"/>
       <c r="J179" s="8"/>
@@ -7799,28 +7804,28 @@
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B180" s="8">
         <v>19.0</v>
       </c>
       <c r="C180" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E180" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F180" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G180" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H180" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I180" s="8"/>
       <c r="J180" s="8"/>
@@ -7848,10 +7853,10 @@
       <c r="D181" s="10"/>
       <c r="E181" s="8"/>
       <c r="F181" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G181" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H181" s="8"/>
       <c r="I181" s="8"/>
@@ -7875,28 +7880,28 @@
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B182" s="8">
         <v>5.0</v>
       </c>
       <c r="C182" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D182" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E182" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F182" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G182" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H182" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I182" s="8"/>
       <c r="J182" s="8"/>
@@ -7919,28 +7924,28 @@
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B183" s="8">
         <v>19.0</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E183" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F183" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H183" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I183" s="8"/>
       <c r="J183" s="8"/>
@@ -7963,28 +7968,28 @@
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B184" s="8">
         <v>5.0</v>
       </c>
       <c r="C184" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D184" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E184" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F184" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G184" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H184" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I184" s="8"/>
       <c r="J184" s="8"/>
@@ -8007,28 +8012,28 @@
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B185" s="8">
         <v>19.0</v>
       </c>
       <c r="C185" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D185" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E185" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F185" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G185" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H185" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I185" s="8"/>
       <c r="J185" s="8"/>
@@ -8079,28 +8084,28 @@
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B187" s="8">
         <v>3.0</v>
       </c>
       <c r="C187" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D187" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E187" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F187" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G187" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H187" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I187" s="8"/>
       <c r="J187" s="8"/>
@@ -8123,28 +8128,28 @@
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B188" s="8">
         <v>4.0</v>
       </c>
       <c r="C188" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D188" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E188" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F188" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G188" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H188" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I188" s="8"/>
       <c r="J188" s="8"/>
@@ -8195,28 +8200,28 @@
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B190" s="8">
         <v>3.0</v>
       </c>
       <c r="C190" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D190" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E190" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D190" s="8" t="s">
+      <c r="F190" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G190" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="E190" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F190" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="G190" s="12" t="s">
-        <v>104</v>
-      </c>
       <c r="H190" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I190" s="8"/>
       <c r="J190" s="8"/>
@@ -8239,28 +8244,28 @@
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B191" s="8">
         <v>4.0</v>
       </c>
       <c r="C191" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D191" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E191" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D191" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E191" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="F191" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G191" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H191" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I191" s="8"/>
       <c r="J191" s="8"/>
@@ -8311,28 +8316,28 @@
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B193" s="8">
         <v>3.0</v>
       </c>
       <c r="C193" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D193" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E193" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F193" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G193" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H193" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I193" s="8"/>
       <c r="J193" s="8"/>
@@ -8355,28 +8360,28 @@
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B194" s="8">
         <v>4.0</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D194" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E194" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F194" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G194" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H194" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I194" s="8"/>
       <c r="J194" s="8"/>
@@ -8427,28 +8432,28 @@
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B196" s="8">
         <v>10.0</v>
       </c>
       <c r="C196" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D196" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E196" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D196" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E196" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="F196" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G196" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H196" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I196" s="8"/>
       <c r="J196" s="8"/>
@@ -8471,28 +8476,28 @@
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B197" s="8">
         <v>11.0</v>
       </c>
       <c r="C197" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D197" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E197" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D197" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E197" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="F197" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G197" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H197" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I197" s="8"/>
       <c r="J197" s="8"/>
@@ -8543,28 +8548,28 @@
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B199" s="8">
         <v>10.0</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D199" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E199" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F199" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G199" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="E199" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F199" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="G199" s="12" t="s">
-        <v>104</v>
-      </c>
       <c r="H199" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I199" s="8"/>
       <c r="J199" s="8"/>
@@ -8587,28 +8592,28 @@
     </row>
     <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B200" s="8">
         <v>11.0</v>
       </c>
       <c r="C200" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D200" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E200" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F200" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G200" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H200" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I200" s="8"/>
       <c r="J200" s="8"/>
@@ -8659,28 +8664,28 @@
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B202" s="8">
         <v>17.0</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D202" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E202" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F202" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G202" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="E202" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F202" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="G202" s="12" t="s">
-        <v>104</v>
-      </c>
       <c r="H202" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I202" s="8"/>
       <c r="J202" s="8"/>
@@ -8703,28 +8708,28 @@
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B203" s="8">
         <v>18.0</v>
       </c>
       <c r="C203" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D203" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E203" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F203" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G203" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H203" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I203" s="8"/>
       <c r="J203" s="8"/>
@@ -8775,28 +8780,28 @@
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B205" s="8">
         <v>17.0</v>
       </c>
       <c r="C205" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D205" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E205" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F205" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G205" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H205" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I205" s="8"/>
       <c r="J205" s="8"/>
@@ -8819,28 +8824,28 @@
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B206" s="8">
         <v>18.0</v>
       </c>
       <c r="C206" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D206" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E206" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F206" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G206" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H206" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I206" s="8"/>
       <c r="J206" s="8"/>
@@ -8891,28 +8896,28 @@
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B208" s="8">
         <v>17.0</v>
       </c>
       <c r="C208" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D208" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E208" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F208" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G208" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H208" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I208" s="8"/>
       <c r="J208" s="8"/>
@@ -8935,28 +8940,28 @@
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B209" s="8">
         <v>18.0</v>
       </c>
       <c r="C209" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D209" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E209" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F209" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G209" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H209" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I209" s="8"/>
       <c r="J209" s="8"/>
@@ -9007,28 +9012,28 @@
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B211" s="8">
         <v>24.0</v>
       </c>
       <c r="C211" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D211" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E211" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D211" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E211" s="8" t="s">
-        <v>53</v>
-      </c>
       <c r="F211" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G211" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H211" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I211" s="8"/>
       <c r="J211" s="8"/>
@@ -9051,28 +9056,28 @@
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B212" s="8">
         <v>25.0</v>
       </c>
       <c r="C212" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D212" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E212" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D212" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E212" s="8" t="s">
-        <v>53</v>
-      </c>
       <c r="F212" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G212" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H212" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I212" s="8"/>
       <c r="J212" s="8"/>
@@ -9123,28 +9128,28 @@
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B214" s="8">
         <v>24.0</v>
       </c>
       <c r="C214" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D214" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E214" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F214" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G214" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="E214" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F214" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="G214" s="12" t="s">
-        <v>104</v>
-      </c>
       <c r="H214" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I214" s="8"/>
       <c r="J214" s="8"/>
@@ -9167,28 +9172,28 @@
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B215" s="8">
         <v>25.0</v>
       </c>
       <c r="C215" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D215" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E215" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F215" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G215" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H215" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I215" s="8"/>
       <c r="J215" s="8"/>
@@ -9211,28 +9216,28 @@
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B216" s="8">
         <v>24.0</v>
       </c>
       <c r="C216" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D216" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E216" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D216" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="E216" s="12" t="s">
-        <v>64</v>
-      </c>
       <c r="F216" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G216" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H216" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I216" s="8"/>
       <c r="J216" s="8"/>
@@ -9255,28 +9260,28 @@
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B217" s="8">
         <v>25.0</v>
       </c>
       <c r="C217" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D217" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E217" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D217" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="E217" s="12" t="s">
-        <v>64</v>
-      </c>
       <c r="F217" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H217" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I217" s="8"/>
       <c r="J217" s="8"/>
@@ -9327,28 +9332,28 @@
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B219" s="8">
         <v>24.0</v>
       </c>
       <c r="C219" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D219" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E219" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D219" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="E219" s="12" t="s">
-        <v>60</v>
-      </c>
       <c r="F219" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G219" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H219" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I219" s="8"/>
       <c r="J219" s="8"/>
@@ -9371,28 +9376,28 @@
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B220" s="8">
         <v>25.0</v>
       </c>
       <c r="C220" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D220" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E220" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D220" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="E220" s="12" t="s">
-        <v>60</v>
-      </c>
       <c r="F220" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G220" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H220" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I220" s="8"/>
       <c r="J220" s="8"/>
@@ -9443,28 +9448,28 @@
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B222" s="8">
         <v>24.0</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D222" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E222" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F222" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G222" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H222" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I222" s="8"/>
       <c r="J222" s="8"/>
@@ -9487,28 +9492,28 @@
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B223" s="8">
         <v>25.0</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D223" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E223" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F223" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G223" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H223" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I223" s="8"/>
       <c r="J223" s="8"/>
@@ -9559,28 +9564,28 @@
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B225" s="8">
         <v>24.0</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D225" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E225" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F225" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G225" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I225" s="8"/>
       <c r="J225" s="8"/>
@@ -9603,28 +9608,28 @@
     </row>
     <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B226" s="8">
         <v>25.0</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D226" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E226" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F226" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G226" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H226" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I226" s="8"/>
       <c r="J226" s="8"/>
@@ -9675,28 +9680,28 @@
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B228" s="8">
         <v>2.0</v>
       </c>
       <c r="C228" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D228" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E228" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F228" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G228" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H228" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I228" s="8"/>
       <c r="J228" s="8"/>
@@ -9719,28 +9724,28 @@
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B229" s="8">
         <v>16.0</v>
       </c>
       <c r="C229" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D229" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E229" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F229" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G229" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H229" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I229" s="8"/>
       <c r="J229" s="8"/>
@@ -9791,28 +9796,28 @@
     </row>
     <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B231" s="8">
         <v>2.0</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D231" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E231" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F231" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G231" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H231" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I231" s="8"/>
       <c r="J231" s="8"/>
@@ -9835,28 +9840,28 @@
     </row>
     <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B232" s="8">
         <v>16.0</v>
       </c>
       <c r="C232" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D232" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E232" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F232" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G232" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H232" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I232" s="8"/>
       <c r="J232" s="8"/>
@@ -9879,28 +9884,28 @@
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B233" s="8">
         <v>2.0</v>
       </c>
       <c r="C233" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D233" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E233" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F233" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G233" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H233" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I233" s="8"/>
       <c r="J233" s="8"/>
@@ -9923,28 +9928,28 @@
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B234" s="8">
         <v>16.0</v>
       </c>
       <c r="C234" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D234" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E234" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F234" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G234" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H234" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I234" s="8"/>
       <c r="J234" s="8"/>
@@ -9995,28 +10000,28 @@
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B236" s="8">
         <v>7.0</v>
       </c>
       <c r="C236" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D236" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E236" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F236" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G236" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H236" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I236" s="8"/>
       <c r="J236" s="8"/>
@@ -10039,28 +10044,28 @@
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B237" s="8">
         <v>8.0</v>
       </c>
       <c r="C237" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D237" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E237" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F237" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G237" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H237" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I237" s="8"/>
       <c r="J237" s="8"/>
@@ -10111,28 +10116,28 @@
     </row>
     <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B239" s="8">
         <v>7.0</v>
       </c>
       <c r="C239" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D239" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E239" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D239" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E239" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="F239" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G239" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H239" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I239" s="8"/>
       <c r="J239" s="8"/>
@@ -10155,28 +10160,28 @@
     </row>
     <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B240" s="8">
         <v>8.0</v>
       </c>
       <c r="C240" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D240" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E240" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D240" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E240" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="F240" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G240" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H240" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I240" s="8"/>
       <c r="J240" s="8"/>
@@ -10227,28 +10232,28 @@
     </row>
     <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B242" s="8">
         <v>7.0</v>
       </c>
       <c r="C242" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D242" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E242" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F242" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G242" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H242" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I242" s="8"/>
       <c r="J242" s="8"/>
@@ -10271,28 +10276,28 @@
     </row>
     <row r="243" ht="15.75" customHeight="1">
       <c r="A243" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B243" s="8">
         <v>8.0</v>
       </c>
       <c r="C243" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D243" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E243" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F243" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G243" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H243" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I243" s="8"/>
       <c r="J243" s="8"/>
@@ -10343,28 +10348,28 @@
     </row>
     <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B245" s="8">
         <v>14.0</v>
       </c>
       <c r="C245" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D245" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E245" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D245" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="E245" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="F245" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G245" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H245" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I245" s="8"/>
       <c r="J245" s="8"/>
@@ -10387,28 +10392,28 @@
     </row>
     <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B246" s="8">
         <v>15.0</v>
       </c>
       <c r="C246" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D246" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E246" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D246" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E246" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="F246" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G246" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H246" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I246" s="8"/>
       <c r="J246" s="8"/>
@@ -10459,28 +10464,28 @@
     </row>
     <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B248" s="8">
         <v>14.0</v>
       </c>
       <c r="C248" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D248" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E248" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F248" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G248" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H248" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I248" s="8"/>
       <c r="J248" s="8"/>
@@ -10503,28 +10508,28 @@
     </row>
     <row r="249" ht="15.75" customHeight="1">
       <c r="A249" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B249" s="8">
         <v>15.0</v>
       </c>
       <c r="C249" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D249" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E249" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F249" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G249" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H249" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I249" s="8"/>
       <c r="J249" s="8"/>
@@ -10575,28 +10580,28 @@
     </row>
     <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B251" s="8">
         <v>21.0</v>
       </c>
       <c r="C251" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D251" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E251" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F251" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G251" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H251" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I251" s="8"/>
       <c r="J251" s="8"/>
@@ -10619,28 +10624,28 @@
     </row>
     <row r="252" ht="15.75" customHeight="1">
       <c r="A252" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B252" s="8">
         <v>22.0</v>
       </c>
       <c r="C252" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D252" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E252" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F252" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G252" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H252" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I252" s="8"/>
       <c r="J252" s="8"/>
@@ -10691,28 +10696,28 @@
     </row>
     <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B254" s="8">
         <v>21.0</v>
       </c>
       <c r="C254" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D254" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E254" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F254" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G254" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H254" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I254" s="8"/>
       <c r="J254" s="8"/>
@@ -10735,28 +10740,28 @@
     </row>
     <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B255" s="8">
         <v>22.0</v>
       </c>
       <c r="C255" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D255" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E255" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F255" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G255" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H255" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I255" s="8"/>
       <c r="J255" s="8"/>
@@ -10807,28 +10812,28 @@
     </row>
     <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B257" s="8">
         <v>21.0</v>
       </c>
       <c r="C257" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D257" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E257" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F257" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G257" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H257" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I257" s="8"/>
       <c r="J257" s="8"/>
@@ -10851,28 +10856,28 @@
     </row>
     <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B258" s="8">
         <v>22.0</v>
       </c>
       <c r="C258" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D258" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E258" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F258" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G258" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H258" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I258" s="8"/>
       <c r="J258" s="8"/>
@@ -10923,28 +10928,28 @@
     </row>
     <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B260" s="8">
         <v>28.0</v>
       </c>
       <c r="C260" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D260" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E260" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D260" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E260" s="8" t="s">
-        <v>53</v>
-      </c>
       <c r="F260" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G260" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H260" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I260" s="8"/>
       <c r="J260" s="8"/>
@@ -10967,28 +10972,28 @@
     </row>
     <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B261" s="8">
         <v>29.0</v>
       </c>
       <c r="C261" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D261" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E261" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D261" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E261" s="8" t="s">
-        <v>53</v>
-      </c>
       <c r="F261" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G261" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H261" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I261" s="8"/>
       <c r="J261" s="8"/>
@@ -11039,28 +11044,28 @@
     </row>
     <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B263" s="8">
         <v>28.0</v>
       </c>
       <c r="C263" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D263" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E263" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F263" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G263" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H263" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I263" s="8"/>
       <c r="J263" s="8"/>
@@ -11083,28 +11088,28 @@
     </row>
     <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B264" s="8">
         <v>29.0</v>
       </c>
       <c r="C264" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D264" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E264" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F264" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G264" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H264" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I264" s="8"/>
       <c r="J264" s="8"/>
@@ -11127,28 +11132,28 @@
     </row>
     <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B265" s="8">
         <v>28.0</v>
       </c>
       <c r="C265" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D265" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E265" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D265" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E265" s="8" t="s">
-        <v>64</v>
-      </c>
       <c r="F265" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G265" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H265" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I265" s="8"/>
       <c r="J265" s="8"/>
@@ -11171,28 +11176,28 @@
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B266" s="8">
         <v>29.0</v>
       </c>
       <c r="C266" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D266" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E266" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D266" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E266" s="8" t="s">
-        <v>64</v>
-      </c>
       <c r="F266" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G266" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H266" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I266" s="8"/>
       <c r="J266" s="8"/>
@@ -11243,28 +11248,28 @@
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B268" s="8">
         <v>28.0</v>
       </c>
       <c r="C268" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D268" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E268" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D268" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E268" s="8" t="s">
-        <v>60</v>
-      </c>
       <c r="F268" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G268" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H268" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I268" s="8"/>
       <c r="J268" s="8"/>
@@ -11287,28 +11292,28 @@
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B269" s="8">
         <v>29.0</v>
       </c>
       <c r="C269" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D269" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E269" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D269" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E269" s="8" t="s">
-        <v>60</v>
-      </c>
       <c r="F269" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G269" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H269" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I269" s="8"/>
       <c r="J269" s="8"/>
@@ -11359,28 +11364,28 @@
     </row>
     <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B271" s="8">
         <v>28.0</v>
       </c>
       <c r="C271" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D271" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E271" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F271" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G271" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="E271" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F271" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="G271" s="12" t="s">
-        <v>114</v>
-      </c>
       <c r="H271" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I271" s="8"/>
       <c r="J271" s="8"/>
@@ -11403,28 +11408,28 @@
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B272" s="8">
         <v>29.0</v>
       </c>
       <c r="C272" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D272" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E272" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F272" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G272" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H272" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I272" s="8"/>
       <c r="J272" s="8"/>
@@ -11475,28 +11480,28 @@
     </row>
     <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B274" s="8">
         <v>28.0</v>
       </c>
       <c r="C274" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D274" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E274" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F274" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G274" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="E274" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F274" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="G274" s="12" t="s">
-        <v>114</v>
-      </c>
       <c r="H274" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I274" s="8"/>
       <c r="J274" s="8"/>
@@ -11519,28 +11524,28 @@
     </row>
     <row r="275" ht="15.75" customHeight="1">
       <c r="A275" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B275" s="8">
         <v>29.0</v>
       </c>
       <c r="C275" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D275" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E275" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F275" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G275" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H275" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I275" s="8"/>
       <c r="J275" s="8"/>
@@ -11619,28 +11624,28 @@
     </row>
     <row r="278" ht="15.75" customHeight="1">
       <c r="A278" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B278" s="12">
         <v>7.0</v>
       </c>
       <c r="C278" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D278" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E278" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F278" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G278" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H278" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I278" s="8"/>
       <c r="J278" s="8"/>
@@ -11663,28 +11668,28 @@
     </row>
     <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B279" s="12">
         <v>14.0</v>
       </c>
       <c r="C279" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D279" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E279" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F279" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G279" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H279" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I279" s="8"/>
       <c r="J279" s="8"/>
@@ -11735,28 +11740,28 @@
     </row>
     <row r="281" ht="15.75" customHeight="1">
       <c r="A281" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B281" s="12">
         <v>7.0</v>
       </c>
       <c r="C281" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D281" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E281" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F281" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G281" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H281" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I281" s="8"/>
       <c r="J281" s="8"/>
@@ -11779,28 +11784,28 @@
     </row>
     <row r="282" ht="15.75" customHeight="1">
       <c r="A282" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B282" s="12">
         <v>14.0</v>
       </c>
       <c r="C282" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D282" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E282" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F282" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G282" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H282" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I282" s="8"/>
       <c r="J282" s="8"/>
@@ -11823,28 +11828,28 @@
     </row>
     <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B283" s="12">
         <v>7.0</v>
       </c>
       <c r="C283" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D283" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E283" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F283" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G283" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H283" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I283" s="8"/>
       <c r="J283" s="8"/>
@@ -11867,28 +11872,28 @@
     </row>
     <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B284" s="12">
         <v>14.0</v>
       </c>
       <c r="C284" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D284" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E284" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F284" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G284" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H284" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I284" s="8"/>
       <c r="J284" s="8"/>
@@ -11939,28 +11944,28 @@
     </row>
     <row r="286" ht="15.75" customHeight="1">
       <c r="A286" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B286" s="8">
         <v>5.0</v>
       </c>
       <c r="C286" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D286" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E286" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F286" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G286" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D286" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E286" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F286" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="G286" s="12" t="s">
-        <v>119</v>
-      </c>
       <c r="H286" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I286" s="8"/>
       <c r="J286" s="8"/>
@@ -11983,28 +11988,28 @@
     </row>
     <row r="287" ht="15.75" customHeight="1">
       <c r="A287" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B287" s="8">
         <v>6.0</v>
       </c>
       <c r="C287" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D287" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E287" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F287" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G287" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H287" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I287" s="8"/>
       <c r="J287" s="8"/>
@@ -12055,28 +12060,28 @@
     </row>
     <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B289" s="8">
         <v>5.0</v>
       </c>
       <c r="C289" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D289" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E289" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D289" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E289" s="12" t="s">
-        <v>77</v>
-      </c>
       <c r="F289" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G289" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H289" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I289" s="8"/>
       <c r="J289" s="8"/>
@@ -12099,28 +12104,28 @@
     </row>
     <row r="290" ht="15.75" customHeight="1">
       <c r="A290" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B290" s="8">
         <v>6.0</v>
       </c>
       <c r="C290" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D290" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E290" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D290" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E290" s="12" t="s">
-        <v>77</v>
-      </c>
       <c r="F290" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G290" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H290" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I290" s="8"/>
       <c r="J290" s="8"/>
@@ -12171,28 +12176,28 @@
     </row>
     <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B292" s="8">
         <v>5.0</v>
       </c>
       <c r="C292" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D292" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E292" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F292" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G292" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H292" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I292" s="8"/>
       <c r="J292" s="8"/>
@@ -12215,28 +12220,28 @@
     </row>
     <row r="293" ht="15.75" customHeight="1">
       <c r="A293" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B293" s="8">
         <v>6.0</v>
       </c>
       <c r="C293" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D293" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E293" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F293" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G293" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H293" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I293" s="8"/>
       <c r="J293" s="8"/>
@@ -12287,28 +12292,28 @@
     </row>
     <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B295" s="8">
         <v>5.0</v>
       </c>
       <c r="C295" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D295" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E295" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F295" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G295" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H295" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I295" s="8"/>
       <c r="J295" s="8"/>
@@ -12331,28 +12336,28 @@
     </row>
     <row r="296" ht="15.75" customHeight="1">
       <c r="A296" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B296" s="8">
         <v>6.0</v>
       </c>
       <c r="C296" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D296" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E296" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F296" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G296" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H296" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I296" s="8"/>
       <c r="J296" s="8"/>
@@ -12403,28 +12408,28 @@
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B298" s="8">
         <v>5.0</v>
       </c>
       <c r="C298" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D298" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E298" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F298" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G298" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H298" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I298" s="8"/>
       <c r="J298" s="8"/>
@@ -12447,28 +12452,28 @@
     </row>
     <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B299" s="8">
         <v>6.0</v>
       </c>
       <c r="C299" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D299" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D299" s="12" t="s">
-        <v>25</v>
-      </c>
       <c r="E299" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F299" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G299" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H299" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I299" s="8"/>
       <c r="J299" s="8"/>
@@ -12491,28 +12496,28 @@
     </row>
     <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B300" s="8">
         <v>5.0</v>
       </c>
       <c r="C300" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D300" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E300" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F300" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G300" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H300" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I300" s="8"/>
       <c r="J300" s="8"/>
@@ -12535,28 +12540,28 @@
     </row>
     <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B301" s="8">
         <v>6.0</v>
       </c>
       <c r="C301" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D301" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E301" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F301" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G301" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H301" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I301" s="8"/>
       <c r="J301" s="8"/>
@@ -12607,28 +12612,28 @@
     </row>
     <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B303" s="8">
         <v>12.0</v>
       </c>
       <c r="C303" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D303" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E303" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D303" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E303" s="12" t="s">
-        <v>48</v>
-      </c>
       <c r="F303" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G303" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H303" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I303" s="8"/>
       <c r="J303" s="8"/>
@@ -12651,28 +12656,28 @@
     </row>
     <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B304" s="8">
         <v>13.0</v>
       </c>
       <c r="C304" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D304" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E304" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D304" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E304" s="12" t="s">
-        <v>48</v>
-      </c>
       <c r="F304" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G304" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H304" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I304" s="8"/>
       <c r="J304" s="8"/>
@@ -12723,28 +12728,28 @@
     </row>
     <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B306" s="8">
         <v>12.0</v>
       </c>
       <c r="C306" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D306" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E306" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F306" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G306" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H306" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I306" s="8"/>
       <c r="J306" s="8"/>
@@ -12767,28 +12772,28 @@
     </row>
     <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B307" s="8">
         <v>13.0</v>
       </c>
       <c r="C307" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D307" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E307" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F307" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G307" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H307" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I307" s="8"/>
       <c r="J307" s="8"/>
@@ -12839,28 +12844,28 @@
     </row>
     <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B309" s="8">
         <v>12.0</v>
       </c>
       <c r="C309" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D309" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E309" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D309" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="E309" s="12" t="s">
-        <v>53</v>
-      </c>
       <c r="F309" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G309" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H309" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I309" s="8"/>
       <c r="J309" s="8"/>
@@ -12883,28 +12888,28 @@
     </row>
     <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B310" s="8">
         <v>13.0</v>
       </c>
       <c r="C310" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D310" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E310" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D310" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="E310" s="12" t="s">
-        <v>53</v>
-      </c>
       <c r="F310" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G310" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H310" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I310" s="8"/>
       <c r="J310" s="8"/>
@@ -12955,28 +12960,28 @@
     </row>
     <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B312" s="8">
         <v>12.0</v>
       </c>
       <c r="C312" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D312" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E312" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F312" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G312" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H312" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I312" s="8"/>
       <c r="J312" s="8"/>
@@ -12999,28 +13004,28 @@
     </row>
     <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B313" s="8">
         <v>13.0</v>
       </c>
       <c r="C313" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D313" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E313" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F313" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G313" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H313" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I313" s="8"/>
       <c r="J313" s="8"/>
@@ -13043,28 +13048,28 @@
     </row>
     <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B314" s="8">
         <v>12.0</v>
       </c>
       <c r="C314" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D314" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E314" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D314" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E314" s="8" t="s">
-        <v>64</v>
-      </c>
       <c r="F314" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G314" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H314" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I314" s="8"/>
       <c r="J314" s="8"/>
@@ -13087,28 +13092,28 @@
     </row>
     <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B315" s="8">
         <v>13.0</v>
       </c>
       <c r="C315" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D315" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E315" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D315" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E315" s="8" t="s">
-        <v>64</v>
-      </c>
       <c r="F315" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G315" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H315" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I315" s="8"/>
       <c r="J315" s="8"/>
@@ -13159,28 +13164,28 @@
     </row>
     <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B317" s="8">
         <v>12.0</v>
       </c>
       <c r="C317" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D317" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E317" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D317" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="E317" s="8" t="s">
-        <v>60</v>
-      </c>
       <c r="F317" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G317" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H317" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I317" s="8"/>
       <c r="J317" s="8"/>
@@ -13203,28 +13208,28 @@
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B318" s="8">
         <v>13.0</v>
       </c>
       <c r="C318" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D318" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E318" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D318" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="E318" s="8" t="s">
-        <v>60</v>
-      </c>
       <c r="F318" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G318" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H318" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I318" s="8"/>
       <c r="J318" s="8"/>
@@ -13275,28 +13280,28 @@
     </row>
     <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B320" s="12">
         <v>12.0</v>
       </c>
       <c r="C320" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D320" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E320" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F320" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G320" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H320" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I320" s="8"/>
       <c r="J320" s="8"/>
@@ -13319,28 +13324,28 @@
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B321" s="12">
         <v>13.0</v>
       </c>
       <c r="C321" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D321" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E321" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F321" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G321" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H321" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I321" s="8"/>
       <c r="J321" s="8"/>
@@ -13391,28 +13396,28 @@
     </row>
     <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B323" s="12">
         <v>12.0</v>
       </c>
       <c r="C323" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D323" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E323" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F323" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G323" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H323" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I323" s="8"/>
       <c r="J323" s="8"/>
@@ -13435,28 +13440,28 @@
     </row>
     <row r="324" ht="15.75" customHeight="1">
       <c r="A324" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B324" s="12">
         <v>13.0</v>
       </c>
       <c r="C324" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D324" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E324" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F324" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G324" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H324" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I324" s="8"/>
       <c r="J324" s="8"/>

--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -328,7 +328,7 @@
     <t xml:space="preserve">Procedimentos Intradérmicos e Intramusculares - Prática l</t>
   </si>
   <si>
-    <t xml:space="preserve">outubro</t>
+    <t xml:space="preserve">Outubro</t>
   </si>
   <si>
     <t xml:space="preserve">06/11/2026 a 10/11/2026</t>

--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="125">
   <si>
     <t xml:space="preserve">MÊS</t>
   </si>
@@ -291,18 +291,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">PROINSU SP 2.</t>
+      <t xml:space="preserve">PROINSU SP </t>
     </r>
     <r>
       <rPr>
-        <vertAlign val="superscript"/>
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">a</t>
+      <t xml:space="preserve">2a.f</t>
     </r>
     <r>
       <rPr>
@@ -312,7 +310,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.f. 010925</t>
+      <t xml:space="preserve"> 010925</t>
     </r>
   </si>
   <si>
@@ -358,13 +356,110 @@
     <t xml:space="preserve">Outubro</t>
   </si>
   <si>
-    <t xml:space="preserve">PROINSU 2a.f. 010925</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PROINSU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve"> SP 2a.f</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 010925</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">06/11/2026 a 10/11/2026</t>
   </si>
   <si>
     <t xml:space="preserve">20/11/2026 a 24/11/2026</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PROINSU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve"> SP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">.f</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 010925</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Procedimentos Intradérmicos e Intramusculares - Prática ll </t>
@@ -412,6 +507,9 @@
     <t xml:space="preserve">22/01/2027 a 26/01/2027</t>
   </si>
   <si>
+    <t xml:space="preserve">PROINSU SP 2a.f 010925</t>
+  </si>
+  <si>
     <t xml:space="preserve">PROINSU BA 280226 </t>
   </si>
   <si>
@@ -428,7 +526,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -482,12 +580,17 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
       <vertAlign val="superscript"/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -679,27 +782,27 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8407,7 +8510,7 @@
         <v>19</v>
       </c>
       <c r="C193" s="12" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D193" s="12" t="s">
         <v>59</v>
@@ -8598,7 +8701,7 @@
         <v>79</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E198" s="8" t="s">
         <v>78</v>
@@ -8642,7 +8745,7 @@
         <v>79</v>
       </c>
       <c r="D199" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E199" s="8" t="s">
         <v>78</v>
@@ -8946,7 +9049,7 @@
         <v>44</v>
       </c>
       <c r="D207" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E207" s="8" t="s">
         <v>42</v>
@@ -8990,7 +9093,7 @@
         <v>44</v>
       </c>
       <c r="D208" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E208" s="8" t="s">
         <v>42</v>
@@ -9062,7 +9165,7 @@
         <v>51</v>
       </c>
       <c r="D210" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E210" s="8" t="s">
         <v>52</v>
@@ -9106,7 +9209,7 @@
         <v>51</v>
       </c>
       <c r="D211" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E211" s="8" t="s">
         <v>52</v>
@@ -9294,7 +9397,7 @@
         <v>22</v>
       </c>
       <c r="D216" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E216" s="8" t="s">
         <v>17</v>
@@ -9338,7 +9441,7 @@
         <v>22</v>
       </c>
       <c r="D217" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E217" s="8" t="s">
         <v>17</v>
@@ -9410,7 +9513,7 @@
         <v>55</v>
       </c>
       <c r="D219" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E219" s="8" t="s">
         <v>54</v>
@@ -9454,7 +9557,7 @@
         <v>55</v>
       </c>
       <c r="D220" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E220" s="8" t="s">
         <v>54</v>
@@ -9526,7 +9629,7 @@
         <v>67</v>
       </c>
       <c r="D222" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E222" s="8" t="s">
         <v>65</v>
@@ -9570,7 +9673,7 @@
         <v>67</v>
       </c>
       <c r="D223" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E223" s="8" t="s">
         <v>65</v>
@@ -9614,7 +9717,7 @@
         <v>66</v>
       </c>
       <c r="D224" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E224" s="12" t="s">
         <v>65</v>
@@ -9658,7 +9761,7 @@
         <v>66</v>
       </c>
       <c r="D225" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E225" s="12" t="s">
         <v>65</v>
@@ -9730,7 +9833,7 @@
         <v>62</v>
       </c>
       <c r="D227" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E227" s="12" t="s">
         <v>61</v>
@@ -9774,7 +9877,7 @@
         <v>62</v>
       </c>
       <c r="D228" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E228" s="12" t="s">
         <v>61</v>
@@ -9846,7 +9949,7 @@
         <v>85</v>
       </c>
       <c r="D230" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E230" s="12" t="s">
         <v>11</v>
@@ -9890,7 +9993,7 @@
         <v>85</v>
       </c>
       <c r="D231" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E231" s="12" t="s">
         <v>11</v>
@@ -9962,7 +10065,7 @@
         <v>95</v>
       </c>
       <c r="D233" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E233" s="12" t="s">
         <v>11</v>
@@ -10006,7 +10109,7 @@
         <v>82</v>
       </c>
       <c r="D234" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E234" s="12" t="s">
         <v>11</v>
@@ -10069,7 +10172,7 @@
     </row>
     <row r="236" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B236" s="8" t="n">
         <v>2</v>
@@ -10078,16 +10181,16 @@
         <v>46</v>
       </c>
       <c r="D236" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E236" s="8" t="s">
         <v>47</v>
       </c>
       <c r="F236" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G236" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H236" s="8" t="s">
         <v>47</v>
@@ -10113,7 +10216,7 @@
     </row>
     <row r="237" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B237" s="8" t="n">
         <v>16</v>
@@ -10122,16 +10225,16 @@
         <v>46</v>
       </c>
       <c r="D237" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E237" s="8" t="s">
         <v>47</v>
       </c>
       <c r="F237" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G237" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H237" s="8" t="s">
         <v>47</v>
@@ -10185,7 +10288,7 @@
     </row>
     <row r="239" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B239" s="8" t="n">
         <v>2</v>
@@ -10194,16 +10297,16 @@
         <v>9</v>
       </c>
       <c r="D239" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E239" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F239" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G239" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H239" s="8" t="s">
         <v>17</v>
@@ -10229,7 +10332,7 @@
     </row>
     <row r="240" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B240" s="8" t="n">
         <v>16</v>
@@ -10238,16 +10341,16 @@
         <v>9</v>
       </c>
       <c r="D240" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E240" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F240" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G240" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H240" s="8" t="s">
         <v>17</v>
@@ -10273,16 +10376,16 @@
     </row>
     <row r="241" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B241" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C241" s="8" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D241" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E241" s="8" t="s">
         <v>17</v>
@@ -10317,16 +10420,16 @@
     </row>
     <row r="242" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B242" s="8" t="n">
         <v>16</v>
       </c>
       <c r="C242" s="8" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D242" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E242" s="8" t="s">
         <v>17</v>
@@ -10389,7 +10492,7 @@
     </row>
     <row r="244" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B244" s="8" t="n">
         <v>7</v>
@@ -10398,16 +10501,16 @@
         <v>76</v>
       </c>
       <c r="D244" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E244" s="8" t="s">
         <v>74</v>
       </c>
       <c r="F244" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G244" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H244" s="8" t="s">
         <v>74</v>
@@ -10433,7 +10536,7 @@
     </row>
     <row r="245" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B245" s="8" t="n">
         <v>8</v>
@@ -10442,16 +10545,16 @@
         <v>76</v>
       </c>
       <c r="D245" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E245" s="8" t="s">
         <v>74</v>
       </c>
       <c r="F245" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G245" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H245" s="8" t="s">
         <v>74</v>
@@ -10505,7 +10608,7 @@
     </row>
     <row r="247" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B247" s="8" t="n">
         <v>7</v>
@@ -10520,10 +10623,10 @@
         <v>78</v>
       </c>
       <c r="F247" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G247" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H247" s="8" t="s">
         <v>78</v>
@@ -10549,7 +10652,7 @@
     </row>
     <row r="248" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B248" s="8" t="n">
         <v>8</v>
@@ -10564,10 +10667,10 @@
         <v>78</v>
       </c>
       <c r="F248" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G248" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H248" s="8" t="s">
         <v>78</v>
@@ -10621,7 +10724,7 @@
     </row>
     <row r="250" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B250" s="8" t="n">
         <v>7</v>
@@ -10630,16 +10733,16 @@
         <v>92</v>
       </c>
       <c r="D250" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E250" s="8" t="s">
         <v>81</v>
       </c>
       <c r="F250" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G250" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H250" s="8" t="s">
         <v>81</v>
@@ -10665,7 +10768,7 @@
     </row>
     <row r="251" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B251" s="8" t="n">
         <v>8</v>
@@ -10674,16 +10777,16 @@
         <v>92</v>
       </c>
       <c r="D251" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E251" s="8" t="s">
         <v>81</v>
       </c>
       <c r="F251" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G251" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H251" s="8" t="s">
         <v>81</v>
@@ -10737,7 +10840,7 @@
     </row>
     <row r="253" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B253" s="8" t="n">
         <v>14</v>
@@ -10746,16 +10849,16 @@
         <v>50</v>
       </c>
       <c r="D253" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E253" s="8" t="s">
         <v>49</v>
       </c>
       <c r="F253" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G253" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H253" s="8" t="s">
         <v>49</v>
@@ -10781,7 +10884,7 @@
     </row>
     <row r="254" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B254" s="8" t="n">
         <v>15</v>
@@ -10790,16 +10893,16 @@
         <v>50</v>
       </c>
       <c r="D254" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E254" s="8" t="s">
         <v>49</v>
       </c>
       <c r="F254" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G254" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H254" s="8" t="s">
         <v>49</v>
@@ -10853,7 +10956,7 @@
     </row>
     <row r="256" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B256" s="8" t="n">
         <v>14</v>
@@ -10868,10 +10971,10 @@
         <v>42</v>
       </c>
       <c r="F256" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G256" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H256" s="8" t="s">
         <v>42</v>
@@ -10897,7 +11000,7 @@
     </row>
     <row r="257" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B257" s="8" t="n">
         <v>15</v>
@@ -10912,10 +11015,10 @@
         <v>42</v>
       </c>
       <c r="F257" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G257" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H257" s="8" t="s">
         <v>42</v>
@@ -10969,7 +11072,7 @@
     </row>
     <row r="259" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B259" s="8" t="n">
         <v>21</v>
@@ -10984,10 +11087,10 @@
         <v>52</v>
       </c>
       <c r="F259" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G259" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H259" s="8" t="s">
         <v>52</v>
@@ -11013,7 +11116,7 @@
     </row>
     <row r="260" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B260" s="8" t="n">
         <v>22</v>
@@ -11028,10 +11131,10 @@
         <v>52</v>
       </c>
       <c r="F260" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G260" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H260" s="8" t="s">
         <v>52</v>
@@ -11085,7 +11188,7 @@
     </row>
     <row r="262" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B262" s="8" t="n">
         <v>21</v>
@@ -11094,16 +11197,16 @@
         <v>27</v>
       </c>
       <c r="D262" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E262" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F262" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G262" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H262" s="8" t="s">
         <v>17</v>
@@ -11129,7 +11232,7 @@
     </row>
     <row r="263" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B263" s="8" t="n">
         <v>22</v>
@@ -11138,16 +11241,16 @@
         <v>27</v>
       </c>
       <c r="D263" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E263" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F263" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G263" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H263" s="8" t="s">
         <v>17</v>
@@ -11201,7 +11304,7 @@
     </row>
     <row r="265" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B265" s="8" t="n">
         <v>21</v>
@@ -11210,7 +11313,7 @@
         <v>22</v>
       </c>
       <c r="D265" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E265" s="8" t="s">
         <v>17</v>
@@ -11245,7 +11348,7 @@
     </row>
     <row r="266" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B266" s="8" t="n">
         <v>22</v>
@@ -11254,7 +11357,7 @@
         <v>22</v>
       </c>
       <c r="D266" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E266" s="8" t="s">
         <v>17</v>
@@ -11317,7 +11420,7 @@
     </row>
     <row r="268" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B268" s="8" t="n">
         <v>28</v>
@@ -11326,7 +11429,7 @@
         <v>55</v>
       </c>
       <c r="D268" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E268" s="8" t="s">
         <v>54</v>
@@ -11361,7 +11464,7 @@
     </row>
     <row r="269" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B269" s="8" t="n">
         <v>29</v>
@@ -11370,7 +11473,7 @@
         <v>55</v>
       </c>
       <c r="D269" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E269" s="8" t="s">
         <v>54</v>
@@ -11433,7 +11536,7 @@
     </row>
     <row r="271" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B271" s="8" t="n">
         <v>28</v>
@@ -11448,10 +11551,10 @@
         <v>65</v>
       </c>
       <c r="F271" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G271" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H271" s="8" t="s">
         <v>65</v>
@@ -11477,7 +11580,7 @@
     </row>
     <row r="272" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B272" s="8" t="n">
         <v>29</v>
@@ -11492,10 +11595,10 @@
         <v>65</v>
       </c>
       <c r="F272" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G272" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H272" s="8" t="s">
         <v>65</v>
@@ -11521,7 +11624,7 @@
     </row>
     <row r="273" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B273" s="8" t="n">
         <v>28</v>
@@ -11530,7 +11633,7 @@
         <v>66</v>
       </c>
       <c r="D273" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E273" s="8" t="s">
         <v>65</v>
@@ -11565,7 +11668,7 @@
     </row>
     <row r="274" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B274" s="8" t="n">
         <v>29</v>
@@ -11574,7 +11677,7 @@
         <v>66</v>
       </c>
       <c r="D274" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E274" s="8" t="s">
         <v>65</v>
@@ -11637,7 +11740,7 @@
     </row>
     <row r="276" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B276" s="8" t="n">
         <v>28</v>
@@ -11646,7 +11749,7 @@
         <v>62</v>
       </c>
       <c r="D276" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E276" s="8" t="s">
         <v>61</v>
@@ -11681,7 +11784,7 @@
     </row>
     <row r="277" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B277" s="8" t="n">
         <v>29</v>
@@ -11690,7 +11793,7 @@
         <v>62</v>
       </c>
       <c r="D277" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E277" s="8" t="s">
         <v>61</v>
@@ -11753,7 +11856,7 @@
     </row>
     <row r="279" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B279" s="8" t="n">
         <v>28</v>
@@ -11762,16 +11865,16 @@
         <v>85</v>
       </c>
       <c r="D279" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E279" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F279" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G279" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H279" s="8" t="s">
         <v>61</v>
@@ -11797,7 +11900,7 @@
     </row>
     <row r="280" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B280" s="8" t="n">
         <v>29</v>
@@ -11806,16 +11909,16 @@
         <v>85</v>
       </c>
       <c r="D280" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E280" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F280" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G280" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H280" s="8" t="s">
         <v>61</v>
@@ -11869,7 +11972,7 @@
     </row>
     <row r="282" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B282" s="8" t="n">
         <v>28</v>
@@ -11878,16 +11981,16 @@
         <v>95</v>
       </c>
       <c r="D282" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E282" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F282" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G282" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H282" s="8" t="s">
         <v>54</v>
@@ -11913,7 +12016,7 @@
     </row>
     <row r="283" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B283" s="8" t="n">
         <v>29</v>
@@ -11922,16 +12025,16 @@
         <v>82</v>
       </c>
       <c r="D283" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E283" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F283" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G283" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H283" s="8" t="s">
         <v>54</v>
@@ -12013,7 +12116,7 @@
     </row>
     <row r="286" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B286" s="12" t="n">
         <v>7</v>
@@ -12028,10 +12131,10 @@
         <v>47</v>
       </c>
       <c r="F286" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G286" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H286" s="12" t="s">
         <v>47</v>
@@ -12057,7 +12160,7 @@
     </row>
     <row r="287" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B287" s="12" t="n">
         <v>14</v>
@@ -12072,10 +12175,10 @@
         <v>47</v>
       </c>
       <c r="F287" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G287" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H287" s="12" t="s">
         <v>47</v>
@@ -12129,7 +12232,7 @@
     </row>
     <row r="289" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B289" s="12" t="n">
         <v>7</v>
@@ -12144,10 +12247,10 @@
         <v>17</v>
       </c>
       <c r="F289" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G289" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H289" s="12" t="s">
         <v>17</v>
@@ -12173,7 +12276,7 @@
     </row>
     <row r="290" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B290" s="12" t="n">
         <v>14</v>
@@ -12188,10 +12291,10 @@
         <v>17</v>
       </c>
       <c r="F290" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G290" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H290" s="12" t="s">
         <v>17</v>
@@ -12217,16 +12320,16 @@
     </row>
     <row r="291" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B291" s="12" t="n">
         <v>7</v>
       </c>
       <c r="C291" s="12" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="D291" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E291" s="12" t="s">
         <v>17</v>
@@ -12261,16 +12364,16 @@
     </row>
     <row r="292" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B292" s="12" t="n">
         <v>14</v>
       </c>
       <c r="C292" s="12" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="D292" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E292" s="12" t="s">
         <v>17</v>
@@ -12333,13 +12436,13 @@
     </row>
     <row r="294" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B294" s="8" t="n">
         <v>5</v>
       </c>
       <c r="C294" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D294" s="12" t="s">
         <v>33</v>
@@ -12348,10 +12451,10 @@
         <v>74</v>
       </c>
       <c r="F294" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G294" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H294" s="12" t="s">
         <v>74</v>
@@ -12377,7 +12480,7 @@
     </row>
     <row r="295" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B295" s="8" t="n">
         <v>6</v>
@@ -12392,10 +12495,10 @@
         <v>74</v>
       </c>
       <c r="F295" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G295" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H295" s="12" t="s">
         <v>74</v>
@@ -12449,7 +12552,7 @@
     </row>
     <row r="297" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B297" s="8" t="n">
         <v>5</v>
@@ -12464,10 +12567,10 @@
         <v>78</v>
       </c>
       <c r="F297" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G297" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H297" s="12" t="s">
         <v>78</v>
@@ -12493,7 +12596,7 @@
     </row>
     <row r="298" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B298" s="8" t="n">
         <v>6</v>
@@ -12508,10 +12611,10 @@
         <v>78</v>
       </c>
       <c r="F298" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G298" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H298" s="12" t="s">
         <v>78</v>
@@ -12565,7 +12668,7 @@
     </row>
     <row r="300" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B300" s="8" t="n">
         <v>5</v>
@@ -12580,10 +12683,10 @@
         <v>81</v>
       </c>
       <c r="F300" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G300" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H300" s="8" t="s">
         <v>81</v>
@@ -12609,7 +12712,7 @@
     </row>
     <row r="301" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B301" s="8" t="n">
         <v>6</v>
@@ -12624,10 +12727,10 @@
         <v>81</v>
       </c>
       <c r="F301" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G301" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H301" s="8" t="s">
         <v>81</v>
@@ -12681,7 +12784,7 @@
     </row>
     <row r="303" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B303" s="8" t="n">
         <v>5</v>
@@ -12696,10 +12799,10 @@
         <v>52</v>
       </c>
       <c r="F303" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G303" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H303" s="8" t="s">
         <v>52</v>
@@ -12725,7 +12828,7 @@
     </row>
     <row r="304" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B304" s="8" t="n">
         <v>6</v>
@@ -12740,10 +12843,10 @@
         <v>52</v>
       </c>
       <c r="F304" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G304" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H304" s="8" t="s">
         <v>52</v>
@@ -12797,7 +12900,7 @@
     </row>
     <row r="306" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B306" s="8" t="n">
         <v>5</v>
@@ -12812,10 +12915,10 @@
         <v>17</v>
       </c>
       <c r="F306" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G306" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H306" s="12" t="s">
         <v>17</v>
@@ -12841,7 +12944,7 @@
     </row>
     <row r="307" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B307" s="8" t="n">
         <v>6</v>
@@ -12856,10 +12959,10 @@
         <v>17</v>
       </c>
       <c r="F307" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G307" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H307" s="12" t="s">
         <v>17</v>
@@ -12885,7 +12988,7 @@
     </row>
     <row r="308" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B308" s="8" t="n">
         <v>5</v>
@@ -12894,7 +12997,7 @@
         <v>22</v>
       </c>
       <c r="D308" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E308" s="12" t="s">
         <v>17</v>
@@ -12929,7 +13032,7 @@
     </row>
     <row r="309" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B309" s="8" t="n">
         <v>6</v>
@@ -12938,7 +13041,7 @@
         <v>22</v>
       </c>
       <c r="D309" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E309" s="12" t="s">
         <v>17</v>
@@ -13001,7 +13104,7 @@
     </row>
     <row r="311" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B311" s="8" t="n">
         <v>12</v>
@@ -13016,10 +13119,10 @@
         <v>49</v>
       </c>
       <c r="F311" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G311" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H311" s="12" t="s">
         <v>49</v>
@@ -13045,7 +13148,7 @@
     </row>
     <row r="312" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B312" s="8" t="n">
         <v>13</v>
@@ -13060,10 +13163,10 @@
         <v>49</v>
       </c>
       <c r="F312" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G312" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H312" s="12" t="s">
         <v>49</v>
@@ -13117,7 +13220,7 @@
     </row>
     <row r="314" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B314" s="8" t="n">
         <v>12</v>
@@ -13132,10 +13235,10 @@
         <v>42</v>
       </c>
       <c r="F314" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G314" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H314" s="8" t="s">
         <v>42</v>
@@ -13161,7 +13264,7 @@
     </row>
     <row r="315" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B315" s="8" t="n">
         <v>13</v>
@@ -13176,10 +13279,10 @@
         <v>42</v>
       </c>
       <c r="F315" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G315" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H315" s="8" t="s">
         <v>42</v>
@@ -13233,7 +13336,7 @@
     </row>
     <row r="317" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B317" s="8" t="n">
         <v>12</v>
@@ -13242,7 +13345,7 @@
         <v>55</v>
       </c>
       <c r="D317" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E317" s="12" t="s">
         <v>54</v>
@@ -13277,7 +13380,7 @@
     </row>
     <row r="318" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B318" s="8" t="n">
         <v>13</v>
@@ -13286,7 +13389,7 @@
         <v>55</v>
       </c>
       <c r="D318" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E318" s="12" t="s">
         <v>54</v>
@@ -13349,7 +13452,7 @@
     </row>
     <row r="320" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B320" s="8" t="n">
         <v>12</v>
@@ -13364,10 +13467,10 @@
         <v>65</v>
       </c>
       <c r="F320" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G320" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H320" s="8" t="s">
         <v>65</v>
@@ -13393,7 +13496,7 @@
     </row>
     <row r="321" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B321" s="8" t="n">
         <v>13</v>
@@ -13408,10 +13511,10 @@
         <v>65</v>
       </c>
       <c r="F321" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G321" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H321" s="8" t="s">
         <v>65</v>
@@ -13437,7 +13540,7 @@
     </row>
     <row r="322" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B322" s="8" t="n">
         <v>12</v>
@@ -13446,7 +13549,7 @@
         <v>66</v>
       </c>
       <c r="D322" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E322" s="8" t="s">
         <v>65</v>
@@ -13481,7 +13584,7 @@
     </row>
     <row r="323" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B323" s="8" t="n">
         <v>13</v>
@@ -13490,7 +13593,7 @@
         <v>66</v>
       </c>
       <c r="D323" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E323" s="8" t="s">
         <v>65</v>
@@ -13553,7 +13656,7 @@
     </row>
     <row r="325" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B325" s="8" t="n">
         <v>12</v>
@@ -13562,7 +13665,7 @@
         <v>62</v>
       </c>
       <c r="D325" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E325" s="8" t="s">
         <v>61</v>
@@ -13597,7 +13700,7 @@
     </row>
     <row r="326" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B326" s="8" t="n">
         <v>13</v>
@@ -13606,7 +13709,7 @@
         <v>62</v>
       </c>
       <c r="D326" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E326" s="8" t="s">
         <v>61</v>
@@ -13669,7 +13772,7 @@
     </row>
     <row r="328" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B328" s="12" t="n">
         <v>12</v>
@@ -13678,16 +13781,16 @@
         <v>85</v>
       </c>
       <c r="D328" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E328" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F328" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G328" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H328" s="8" t="s">
         <v>61</v>
@@ -13713,7 +13816,7 @@
     </row>
     <row r="329" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B329" s="12" t="n">
         <v>13</v>
@@ -13722,16 +13825,16 @@
         <v>85</v>
       </c>
       <c r="D329" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E329" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F329" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G329" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H329" s="8" t="s">
         <v>61</v>
@@ -13785,7 +13888,7 @@
     </row>
     <row r="331" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B331" s="12" t="n">
         <v>12</v>
@@ -13794,16 +13897,16 @@
         <v>95</v>
       </c>
       <c r="D331" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E331" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F331" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G331" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H331" s="8" t="s">
         <v>54</v>
@@ -13829,7 +13932,7 @@
     </row>
     <row r="332" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B332" s="12" t="n">
         <v>13</v>
@@ -13838,16 +13941,16 @@
         <v>82</v>
       </c>
       <c r="D332" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E332" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F332" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G332" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H332" s="8" t="s">
         <v>54</v>

--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -7811,7 +7811,7 @@
         <v>83</v>
       </c>
       <c r="B181" s="9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C181" s="9" t="s">
         <v>91</v>
@@ -7855,7 +7855,7 @@
         <v>83</v>
       </c>
       <c r="B182" s="9" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C182" s="9" t="s">
         <v>79</v>
@@ -7927,7 +7927,7 @@
         <v>83</v>
       </c>
       <c r="B184" s="9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C184" s="9" t="s">
         <v>82</v>
@@ -7971,7 +7971,7 @@
         <v>83</v>
       </c>
       <c r="B185" s="9" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C185" s="9" t="s">
         <v>82</v>

--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -671,7 +671,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -728,6 +728,9 @@
     </xf>
     <xf borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11316,8 +11319,8 @@
       <c r="C268" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D268" s="8" t="s">
-        <v>108</v>
+      <c r="D268" s="19" t="s">
+        <v>107</v>
       </c>
       <c r="E268" s="8" t="s">
         <v>53</v>
@@ -11360,8 +11363,8 @@
       <c r="C269" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D269" s="8" t="s">
-        <v>108</v>
+      <c r="D269" s="19" t="s">
+        <v>107</v>
       </c>
       <c r="E269" s="8" t="s">
         <v>53</v>

--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -671,7 +671,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -727,6 +727,9 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -8469,8 +8472,8 @@
       <c r="A195" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B195" s="8">
-        <v>3.0</v>
+      <c r="B195" s="19">
+        <v>10.0</v>
       </c>
       <c r="C195" s="8" t="s">
         <v>75</v>
@@ -8513,8 +8516,8 @@
       <c r="A196" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B196" s="8">
-        <v>4.0</v>
+      <c r="B196" s="19">
+        <v>11.0</v>
       </c>
       <c r="C196" s="8" t="s">
         <v>75</v>
@@ -8585,8 +8588,8 @@
       <c r="A198" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B198" s="8">
-        <v>3.0</v>
+      <c r="B198" s="19">
+        <v>10.0</v>
       </c>
       <c r="C198" s="8" t="s">
         <v>78</v>
@@ -8629,8 +8632,8 @@
       <c r="A199" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B199" s="8">
-        <v>4.0</v>
+      <c r="B199" s="19">
+        <v>11.0</v>
       </c>
       <c r="C199" s="8" t="s">
         <v>78</v>
@@ -8701,8 +8704,8 @@
       <c r="A201" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B201" s="8">
-        <v>3.0</v>
+      <c r="B201" s="19">
+        <v>10.0</v>
       </c>
       <c r="C201" s="8" t="s">
         <v>92</v>
@@ -8745,8 +8748,8 @@
       <c r="A202" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B202" s="8">
-        <v>4.0</v>
+      <c r="B202" s="19">
+        <v>11.0</v>
       </c>
       <c r="C202" s="8" t="s">
         <v>92</v>
@@ -9397,8 +9400,8 @@
       <c r="A219" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B219" s="8">
-        <v>24.0</v>
+      <c r="B219" s="19">
+        <v>17.0</v>
       </c>
       <c r="C219" s="8" t="s">
         <v>54</v>
@@ -9441,8 +9444,8 @@
       <c r="A220" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B220" s="8">
-        <v>25.0</v>
+      <c r="B220" s="19">
+        <v>18.0</v>
       </c>
       <c r="C220" s="8" t="s">
         <v>54</v>
@@ -9513,8 +9516,8 @@
       <c r="A222" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B222" s="8">
-        <v>24.0</v>
+      <c r="B222" s="19">
+        <v>17.0</v>
       </c>
       <c r="C222" s="13" t="s">
         <v>66</v>
@@ -9557,8 +9560,8 @@
       <c r="A223" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B223" s="8">
-        <v>25.0</v>
+      <c r="B223" s="19">
+        <v>18.0</v>
       </c>
       <c r="C223" s="13" t="s">
         <v>66</v>
@@ -9601,8 +9604,8 @@
       <c r="A224" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B224" s="8">
-        <v>24.0</v>
+      <c r="B224" s="19">
+        <v>17.0</v>
       </c>
       <c r="C224" s="13" t="s">
         <v>65</v>
@@ -9645,8 +9648,8 @@
       <c r="A225" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B225" s="8">
-        <v>25.0</v>
+      <c r="B225" s="19">
+        <v>18.0</v>
       </c>
       <c r="C225" s="13" t="s">
         <v>65</v>
@@ -9717,8 +9720,8 @@
       <c r="A227" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B227" s="8">
-        <v>24.0</v>
+      <c r="B227" s="19">
+        <v>17.0</v>
       </c>
       <c r="C227" s="13" t="s">
         <v>61</v>
@@ -9761,8 +9764,8 @@
       <c r="A228" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B228" s="8">
-        <v>25.0</v>
+      <c r="B228" s="19">
+        <v>18.0</v>
       </c>
       <c r="C228" s="13" t="s">
         <v>61</v>
@@ -11319,7 +11322,7 @@
       <c r="C268" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D268" s="19" t="s">
+      <c r="D268" s="20" t="s">
         <v>107</v>
       </c>
       <c r="E268" s="8" t="s">
@@ -11363,7 +11366,7 @@
       <c r="C269" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D269" s="19" t="s">
+      <c r="D269" s="20" t="s">
         <v>107</v>
       </c>
       <c r="E269" s="8" t="s">

--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -412,10 +412,10 @@
     <t>Ciencia Estética</t>
   </si>
   <si>
-    <t>Anatomofisiologia da Cabeça e Pescoço</t>
+    <t>Novembro</t>
   </si>
   <si>
-    <t>Novembro</t>
+    <t>Anatomofisiologia da Cabeça e Pescoço</t>
   </si>
   <si>
     <t>Procedimentos Intradérmicos e Intramusculares - Prática ll</t>
@@ -671,7 +671,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -730,6 +730,9 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -9836,8 +9839,8 @@
       <c r="A230" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B230" s="8">
-        <v>24.0</v>
+      <c r="B230" s="19">
+        <v>31.0</v>
       </c>
       <c r="C230" s="8" t="s">
         <v>84</v>
@@ -9877,17 +9880,17 @@
       <c r="Z230" s="9"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B231" s="8">
-        <v>25.0</v>
+      <c r="A231" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B231" s="19">
+        <v>1.0</v>
       </c>
       <c r="C231" s="8" t="s">
         <v>84</v>
       </c>
       <c r="D231" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E231" s="13" t="s">
         <v>11</v>
@@ -9952,8 +9955,8 @@
       <c r="A233" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B233" s="8">
-        <v>24.0</v>
+      <c r="B233" s="19">
+        <v>31.0</v>
       </c>
       <c r="C233" s="8" t="s">
         <v>95</v>
@@ -9993,17 +9996,17 @@
       <c r="Z233" s="9"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="A234" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B234" s="8">
-        <v>25.0</v>
+      <c r="A234" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B234" s="19">
+        <v>1.0</v>
       </c>
       <c r="C234" s="8" t="s">
         <v>81</v>
       </c>
       <c r="D234" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E234" s="13" t="s">
         <v>11</v>
@@ -10066,7 +10069,7 @@
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B236" s="8">
         <v>2.0</v>
@@ -10110,7 +10113,7 @@
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B237" s="8">
         <v>16.0</v>
@@ -10182,7 +10185,7 @@
     </row>
     <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B239" s="8">
         <v>2.0</v>
@@ -10226,7 +10229,7 @@
     </row>
     <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B240" s="8">
         <v>16.0</v>
@@ -10270,7 +10273,7 @@
     </row>
     <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B241" s="8">
         <v>2.0</v>
@@ -10314,7 +10317,7 @@
     </row>
     <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B242" s="8">
         <v>16.0</v>
@@ -10386,7 +10389,7 @@
     </row>
     <row r="244" ht="15.75" customHeight="1">
       <c r="A244" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B244" s="8">
         <v>7.0</v>
@@ -10430,7 +10433,7 @@
     </row>
     <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B245" s="8">
         <v>8.0</v>
@@ -10502,7 +10505,7 @@
     </row>
     <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B247" s="8">
         <v>7.0</v>
@@ -10546,7 +10549,7 @@
     </row>
     <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B248" s="8">
         <v>8.0</v>
@@ -10618,7 +10621,7 @@
     </row>
     <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B250" s="8">
         <v>7.0</v>
@@ -10662,7 +10665,7 @@
     </row>
     <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B251" s="8">
         <v>8.0</v>
@@ -10734,7 +10737,7 @@
     </row>
     <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B253" s="8">
         <v>14.0</v>
@@ -10778,7 +10781,7 @@
     </row>
     <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B254" s="8">
         <v>15.0</v>
@@ -10850,7 +10853,7 @@
     </row>
     <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B256" s="8">
         <v>14.0</v>
@@ -10894,7 +10897,7 @@
     </row>
     <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B257" s="8">
         <v>15.0</v>
@@ -10966,7 +10969,7 @@
     </row>
     <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B259" s="8">
         <v>21.0</v>
@@ -11010,7 +11013,7 @@
     </row>
     <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B260" s="8">
         <v>22.0</v>
@@ -11082,7 +11085,7 @@
     </row>
     <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B262" s="8">
         <v>21.0</v>
@@ -11126,7 +11129,7 @@
     </row>
     <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B263" s="8">
         <v>22.0</v>
@@ -11198,7 +11201,7 @@
     </row>
     <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B265" s="8">
         <v>21.0</v>
@@ -11242,7 +11245,7 @@
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B266" s="8">
         <v>22.0</v>
@@ -11314,7 +11317,7 @@
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B268" s="8">
         <v>28.0</v>
@@ -11322,7 +11325,7 @@
       <c r="C268" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D268" s="20" t="s">
+      <c r="D268" s="21" t="s">
         <v>107</v>
       </c>
       <c r="E268" s="8" t="s">
@@ -11358,7 +11361,7 @@
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B269" s="8">
         <v>29.0</v>
@@ -11366,7 +11369,7 @@
       <c r="C269" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D269" s="20" t="s">
+      <c r="D269" s="21" t="s">
         <v>107</v>
       </c>
       <c r="E269" s="8" t="s">
@@ -11430,7 +11433,7 @@
     </row>
     <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B271" s="8">
         <v>28.0</v>
@@ -11474,7 +11477,7 @@
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B272" s="8">
         <v>29.0</v>
@@ -11518,7 +11521,7 @@
     </row>
     <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B273" s="8">
         <v>28.0</v>
@@ -11562,7 +11565,7 @@
     </row>
     <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B274" s="8">
         <v>29.0</v>
@@ -11634,7 +11637,7 @@
     </row>
     <row r="276" ht="15.75" customHeight="1">
       <c r="A276" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B276" s="8">
         <v>28.0</v>
@@ -11678,7 +11681,7 @@
     </row>
     <row r="277" ht="15.75" customHeight="1">
       <c r="A277" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B277" s="8">
         <v>29.0</v>
@@ -11750,7 +11753,7 @@
     </row>
     <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B279" s="8">
         <v>28.0</v>
@@ -11794,7 +11797,7 @@
     </row>
     <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B280" s="8">
         <v>29.0</v>
@@ -11866,7 +11869,7 @@
     </row>
     <row r="282" ht="15.75" customHeight="1">
       <c r="A282" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B282" s="8">
         <v>28.0</v>
@@ -11910,7 +11913,7 @@
     </row>
     <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B283" s="8">
         <v>29.0</v>

--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -671,7 +671,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -702,9 +702,6 @@
     <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
     <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
@@ -717,6 +714,9 @@
     <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
+    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="8" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -725,18 +725,6 @@
     </xf>
     <xf borderId="9" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1362,7 +1350,7 @@
       <c r="B10" s="6">
         <v>20.0</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="7" t="s">
@@ -1878,7 +1866,7 @@
       <c r="B22" s="6">
         <v>17.0</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D22" s="7" t="s">
@@ -2187,7 +2175,7 @@
       <c r="A32" s="5"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
-      <c r="D32" s="11"/>
+      <c r="D32" s="10"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
@@ -2527,7 +2515,7 @@
       <c r="A41" s="5"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
-      <c r="D41" s="11"/>
+      <c r="D41" s="10"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
@@ -3067,7 +3055,7 @@
       <c r="A56" s="5"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
-      <c r="D56" s="11"/>
+      <c r="D56" s="10"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
@@ -3407,7 +3395,7 @@
       <c r="A65" s="5"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
-      <c r="D65" s="11"/>
+      <c r="D65" s="10"/>
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
@@ -3663,7 +3651,7 @@
       <c r="A72" s="5"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
-      <c r="D72" s="11"/>
+      <c r="D72" s="10"/>
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
       <c r="G72" s="8"/>
@@ -4089,7 +4077,7 @@
       <c r="A83" s="5"/>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
-      <c r="D83" s="11"/>
+      <c r="D83" s="10"/>
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
@@ -4463,7 +4451,7 @@
       <c r="C92" s="8"/>
       <c r="D92" s="7"/>
       <c r="E92" s="6"/>
-      <c r="F92" s="12"/>
+      <c r="F92" s="11"/>
       <c r="G92" s="6"/>
       <c r="H92" s="6"/>
       <c r="I92" s="8"/>
@@ -4491,7 +4479,7 @@
       <c r="C93" s="8"/>
       <c r="D93" s="7"/>
       <c r="E93" s="6"/>
-      <c r="F93" s="12"/>
+      <c r="F93" s="11"/>
       <c r="G93" s="6"/>
       <c r="H93" s="6"/>
       <c r="I93" s="8"/>
@@ -4517,7 +4505,7 @@
       <c r="A94" s="5"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
-      <c r="D94" s="11"/>
+      <c r="D94" s="10"/>
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
       <c r="G94" s="8"/>
@@ -5135,7 +5123,7 @@
       <c r="A109" s="5"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
-      <c r="D109" s="11"/>
+      <c r="D109" s="10"/>
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
       <c r="G109" s="8"/>
@@ -5439,7 +5427,7 @@
       <c r="A117" s="5"/>
       <c r="B117" s="8"/>
       <c r="C117" s="8"/>
-      <c r="D117" s="11"/>
+      <c r="D117" s="10"/>
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
       <c r="G117" s="8"/>
@@ -5743,7 +5731,7 @@
       <c r="A125" s="5"/>
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
-      <c r="D125" s="11"/>
+      <c r="D125" s="10"/>
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
       <c r="G125" s="8"/>
@@ -6003,7 +5991,7 @@
       <c r="A132" s="5"/>
       <c r="B132" s="6"/>
       <c r="C132" s="8"/>
-      <c r="D132" s="11"/>
+      <c r="D132" s="10"/>
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
       <c r="G132" s="8"/>
@@ -6119,7 +6107,7 @@
       <c r="A135" s="5"/>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
-      <c r="D135" s="11"/>
+      <c r="D135" s="10"/>
       <c r="E135" s="8"/>
       <c r="F135" s="8"/>
       <c r="G135" s="8"/>
@@ -6235,7 +6223,7 @@
       <c r="A138" s="5"/>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
-      <c r="D138" s="11"/>
+      <c r="D138" s="10"/>
       <c r="E138" s="8"/>
       <c r="F138" s="8"/>
       <c r="G138" s="8"/>
@@ -6263,25 +6251,25 @@
       <c r="A139" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B139" s="13">
+      <c r="B139" s="12">
         <v>7.0</v>
       </c>
-      <c r="C139" s="13" t="s">
+      <c r="C139" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D139" s="13" t="s">
+      <c r="D139" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E139" s="13" t="s">
+      <c r="E139" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F139" s="13" t="s">
+      <c r="F139" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G139" s="13" t="s">
+      <c r="G139" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H139" s="13" t="s">
+      <c r="H139" s="12" t="s">
         <v>46</v>
       </c>
       <c r="I139" s="8"/>
@@ -6307,25 +6295,25 @@
       <c r="A140" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B140" s="13">
+      <c r="B140" s="12">
         <v>21.0</v>
       </c>
-      <c r="C140" s="13" t="s">
+      <c r="C140" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D140" s="13" t="s">
+      <c r="D140" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E140" s="13" t="s">
+      <c r="E140" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F140" s="13" t="s">
+      <c r="F140" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G140" s="13" t="s">
+      <c r="G140" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H140" s="13" t="s">
+      <c r="H140" s="12" t="s">
         <v>46</v>
       </c>
       <c r="I140" s="8"/>
@@ -6351,7 +6339,7 @@
       <c r="A141" s="5"/>
       <c r="B141" s="8"/>
       <c r="C141" s="8"/>
-      <c r="D141" s="11"/>
+      <c r="D141" s="10"/>
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
       <c r="G141" s="8"/>
@@ -6379,25 +6367,25 @@
       <c r="A142" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B142" s="13">
+      <c r="B142" s="12">
         <v>7.0</v>
       </c>
-      <c r="C142" s="13" t="s">
+      <c r="C142" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D142" s="13" t="s">
+      <c r="D142" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E142" s="13" t="s">
+      <c r="E142" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F142" s="13" t="s">
+      <c r="F142" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G142" s="13" t="s">
+      <c r="G142" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H142" s="13" t="s">
+      <c r="H142" s="12" t="s">
         <v>17</v>
       </c>
       <c r="I142" s="8"/>
@@ -6423,25 +6411,25 @@
       <c r="A143" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B143" s="13">
+      <c r="B143" s="12">
         <v>21.0</v>
       </c>
-      <c r="C143" s="13" t="s">
+      <c r="C143" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D143" s="13" t="s">
+      <c r="D143" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E143" s="13" t="s">
+      <c r="E143" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F143" s="13" t="s">
+      <c r="F143" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G143" s="13" t="s">
+      <c r="G143" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H143" s="13" t="s">
+      <c r="H143" s="12" t="s">
         <v>17</v>
       </c>
       <c r="I143" s="8"/>
@@ -6467,25 +6455,25 @@
       <c r="A144" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B144" s="13">
+      <c r="B144" s="12">
         <v>7.0</v>
       </c>
-      <c r="C144" s="13" t="s">
+      <c r="C144" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="D144" s="13" t="s">
+      <c r="D144" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E144" s="13" t="s">
+      <c r="E144" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F144" s="13" t="s">
+      <c r="F144" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G144" s="13" t="s">
+      <c r="G144" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H144" s="13" t="s">
+      <c r="H144" s="12" t="s">
         <v>17</v>
       </c>
       <c r="I144" s="8"/>
@@ -6511,25 +6499,25 @@
       <c r="A145" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B145" s="13">
+      <c r="B145" s="12">
         <v>21.0</v>
       </c>
-      <c r="C145" s="13" t="s">
+      <c r="C145" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D145" s="13" t="s">
+      <c r="D145" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E145" s="13" t="s">
+      <c r="E145" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F145" s="13" t="s">
+      <c r="F145" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G145" s="13" t="s">
+      <c r="G145" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H145" s="13" t="s">
+      <c r="H145" s="12" t="s">
         <v>17</v>
       </c>
       <c r="I145" s="8"/>
@@ -6555,7 +6543,7 @@
       <c r="A146" s="5"/>
       <c r="B146" s="8"/>
       <c r="C146" s="8"/>
-      <c r="D146" s="11"/>
+      <c r="D146" s="10"/>
       <c r="E146" s="8"/>
       <c r="F146" s="8"/>
       <c r="G146" s="8"/>
@@ -6595,10 +6583,10 @@
       <c r="E147" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F147" s="14" t="s">
+      <c r="F147" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G147" s="14" t="s">
+      <c r="G147" s="13" t="s">
         <v>69</v>
       </c>
       <c r="H147" s="8" t="s">
@@ -6639,10 +6627,10 @@
       <c r="E148" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F148" s="14" t="s">
+      <c r="F148" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G148" s="14" t="s">
+      <c r="G148" s="13" t="s">
         <v>69</v>
       </c>
       <c r="H148" s="8" t="s">
@@ -6671,7 +6659,7 @@
       <c r="A149" s="5"/>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
-      <c r="D149" s="11"/>
+      <c r="D149" s="10"/>
       <c r="E149" s="8"/>
       <c r="F149" s="8"/>
       <c r="G149" s="8"/>
@@ -6787,7 +6775,7 @@
       <c r="A152" s="5"/>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
-      <c r="D152" s="11"/>
+      <c r="D152" s="10"/>
       <c r="E152" s="8"/>
       <c r="F152" s="8"/>
       <c r="G152" s="8"/>
@@ -6827,10 +6815,10 @@
       <c r="E153" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F153" s="14" t="s">
+      <c r="F153" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G153" s="14" t="s">
+      <c r="G153" s="13" t="s">
         <v>69</v>
       </c>
       <c r="H153" s="8" t="s">
@@ -6871,10 +6859,10 @@
       <c r="E154" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F154" s="14" t="s">
+      <c r="F154" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G154" s="14" t="s">
+      <c r="G154" s="13" t="s">
         <v>69</v>
       </c>
       <c r="H154" s="8" t="s">
@@ -6903,7 +6891,7 @@
       <c r="A155" s="5"/>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
-      <c r="D155" s="11"/>
+      <c r="D155" s="10"/>
       <c r="E155" s="8"/>
       <c r="F155" s="8"/>
       <c r="G155" s="8"/>
@@ -6937,16 +6925,16 @@
       <c r="C156" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D156" s="11" t="s">
+      <c r="D156" s="10" t="s">
         <v>88</v>
       </c>
       <c r="E156" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F156" s="14" t="s">
+      <c r="F156" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G156" s="14" t="s">
+      <c r="G156" s="13" t="s">
         <v>69</v>
       </c>
       <c r="H156" s="8" t="s">
@@ -6981,16 +6969,16 @@
       <c r="C157" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D157" s="11" t="s">
+      <c r="D157" s="10" t="s">
         <v>89</v>
       </c>
       <c r="E157" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F157" s="14" t="s">
+      <c r="F157" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G157" s="14" t="s">
+      <c r="G157" s="13" t="s">
         <v>69</v>
       </c>
       <c r="H157" s="8" t="s">
@@ -7019,7 +7007,7 @@
       <c r="A158" s="5"/>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
-      <c r="D158" s="11"/>
+      <c r="D158" s="10"/>
       <c r="E158" s="8"/>
       <c r="F158" s="8"/>
       <c r="G158" s="8"/>
@@ -7135,7 +7123,7 @@
       <c r="A161" s="5"/>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
-      <c r="D161" s="11"/>
+      <c r="D161" s="10"/>
       <c r="E161" s="8"/>
       <c r="F161" s="8"/>
       <c r="G161" s="8"/>
@@ -7251,7 +7239,7 @@
       <c r="A164" s="5"/>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
-      <c r="D164" s="11"/>
+      <c r="D164" s="10"/>
       <c r="E164" s="8"/>
       <c r="F164" s="8"/>
       <c r="G164" s="8"/>
@@ -7288,7 +7276,7 @@
       <c r="D165" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E165" s="13" t="s">
+      <c r="E165" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F165" s="8" t="s">
@@ -7332,13 +7320,13 @@
       <c r="D166" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="E166" s="13" t="s">
+      <c r="E166" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F166" s="14" t="s">
+      <c r="F166" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G166" s="14" t="s">
+      <c r="G166" s="13" t="s">
         <v>69</v>
       </c>
       <c r="H166" s="8" t="s">
@@ -7455,7 +7443,7 @@
       <c r="A169" s="5"/>
       <c r="B169" s="8"/>
       <c r="C169" s="8"/>
-      <c r="D169" s="11"/>
+      <c r="D169" s="10"/>
       <c r="E169" s="8"/>
       <c r="F169" s="8"/>
       <c r="G169" s="8"/>
@@ -7571,7 +7559,7 @@
       <c r="A172" s="5"/>
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
-      <c r="D172" s="11"/>
+      <c r="D172" s="10"/>
       <c r="E172" s="8"/>
       <c r="F172" s="8"/>
       <c r="G172" s="8"/>
@@ -7775,7 +7763,7 @@
       <c r="A177" s="5"/>
       <c r="B177" s="8"/>
       <c r="C177" s="8"/>
-      <c r="D177" s="11"/>
+      <c r="D177" s="10"/>
       <c r="E177" s="8"/>
       <c r="F177" s="8"/>
       <c r="G177" s="8"/>
@@ -7859,10 +7847,10 @@
       <c r="E179" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F179" s="14" t="s">
+      <c r="F179" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G179" s="14" t="s">
+      <c r="G179" s="13" t="s">
         <v>69</v>
       </c>
       <c r="H179" s="8" t="s">
@@ -7891,7 +7879,7 @@
       <c r="A180" s="5"/>
       <c r="B180" s="8"/>
       <c r="C180" s="8"/>
-      <c r="D180" s="11"/>
+      <c r="D180" s="10"/>
       <c r="E180" s="8"/>
       <c r="F180" s="8"/>
       <c r="G180" s="8"/>
@@ -7919,8 +7907,8 @@
       <c r="A181" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B181" s="8">
-        <v>22.0</v>
+      <c r="B181" s="14">
+        <v>27.0</v>
       </c>
       <c r="C181" s="8" t="s">
         <v>95</v>
@@ -7931,10 +7919,10 @@
       <c r="E181" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F181" s="14" t="s">
+      <c r="F181" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G181" s="14" t="s">
+      <c r="G181" s="13" t="s">
         <v>69</v>
       </c>
       <c r="H181" s="6" t="s">
@@ -7963,8 +7951,8 @@
       <c r="A182" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B182" s="8">
-        <v>23.0</v>
+      <c r="B182" s="14">
+        <v>26.0</v>
       </c>
       <c r="C182" s="8" t="s">
         <v>81</v>
@@ -7975,10 +7963,10 @@
       <c r="E182" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F182" s="14" t="s">
+      <c r="F182" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G182" s="14" t="s">
+      <c r="G182" s="13" t="s">
         <v>69</v>
       </c>
       <c r="H182" s="6" t="s">
@@ -8007,7 +7995,7 @@
       <c r="A183" s="5"/>
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
-      <c r="D183" s="11"/>
+      <c r="D183" s="10"/>
       <c r="E183" s="8"/>
       <c r="F183" s="8"/>
       <c r="G183" s="8"/>
@@ -8035,8 +8023,8 @@
       <c r="A184" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B184" s="8">
-        <v>22.0</v>
+      <c r="B184" s="14">
+        <v>27.0</v>
       </c>
       <c r="C184" s="8" t="s">
         <v>84</v>
@@ -8047,10 +8035,10 @@
       <c r="E184" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F184" s="14" t="s">
+      <c r="F184" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G184" s="14" t="s">
+      <c r="G184" s="13" t="s">
         <v>69</v>
       </c>
       <c r="H184" s="8" t="s">
@@ -8079,8 +8067,8 @@
       <c r="A185" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B185" s="8">
-        <v>23.0</v>
+      <c r="B185" s="14">
+        <v>26.0</v>
       </c>
       <c r="C185" s="8" t="s">
         <v>84</v>
@@ -8091,10 +8079,10 @@
       <c r="E185" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F185" s="14" t="s">
+      <c r="F185" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G185" s="14" t="s">
+      <c r="G185" s="13" t="s">
         <v>69</v>
       </c>
       <c r="H185" s="8" t="s">
@@ -8121,30 +8109,30 @@
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="15"/>
-      <c r="B186" s="13"/>
-      <c r="C186" s="13"/>
+      <c r="B186" s="12"/>
+      <c r="C186" s="12"/>
       <c r="D186" s="16"/>
-      <c r="E186" s="13"/>
-      <c r="F186" s="13"/>
-      <c r="G186" s="13"/>
-      <c r="H186" s="13"/>
-      <c r="I186" s="13"/>
-      <c r="J186" s="13"/>
-      <c r="K186" s="13"/>
-      <c r="L186" s="13"/>
-      <c r="M186" s="13"/>
-      <c r="N186" s="13"/>
-      <c r="O186" s="13"/>
-      <c r="P186" s="13"/>
-      <c r="Q186" s="13"/>
-      <c r="R186" s="13"/>
-      <c r="S186" s="13"/>
-      <c r="T186" s="13"/>
-      <c r="U186" s="13"/>
-      <c r="V186" s="13"/>
-      <c r="W186" s="13"/>
-      <c r="X186" s="13"/>
-      <c r="Y186" s="13"/>
+      <c r="E186" s="12"/>
+      <c r="F186" s="12"/>
+      <c r="G186" s="12"/>
+      <c r="H186" s="12"/>
+      <c r="I186" s="12"/>
+      <c r="J186" s="12"/>
+      <c r="K186" s="12"/>
+      <c r="L186" s="12"/>
+      <c r="M186" s="12"/>
+      <c r="N186" s="12"/>
+      <c r="O186" s="12"/>
+      <c r="P186" s="12"/>
+      <c r="Q186" s="12"/>
+      <c r="R186" s="12"/>
+      <c r="S186" s="12"/>
+      <c r="T186" s="12"/>
+      <c r="U186" s="12"/>
+      <c r="V186" s="12"/>
+      <c r="W186" s="12"/>
+      <c r="X186" s="12"/>
+      <c r="Y186" s="12"/>
       <c r="Z186" s="17"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
@@ -8154,13 +8142,13 @@
       <c r="B187" s="8">
         <v>5.0</v>
       </c>
-      <c r="C187" s="13" t="s">
+      <c r="C187" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D187" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="E187" s="13" t="s">
+      <c r="E187" s="12" t="s">
         <v>46</v>
       </c>
       <c r="F187" s="8" t="s">
@@ -8169,7 +8157,7 @@
       <c r="G187" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H187" s="13" t="s">
+      <c r="H187" s="12" t="s">
         <v>46</v>
       </c>
       <c r="I187" s="8"/>
@@ -8198,13 +8186,13 @@
       <c r="B188" s="8">
         <v>19.0</v>
       </c>
-      <c r="C188" s="13" t="s">
+      <c r="C188" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D188" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E188" s="13" t="s">
+      <c r="E188" s="12" t="s">
         <v>46</v>
       </c>
       <c r="F188" s="8" t="s">
@@ -8213,7 +8201,7 @@
       <c r="G188" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H188" s="13" t="s">
+      <c r="H188" s="12" t="s">
         <v>46</v>
       </c>
       <c r="I188" s="8"/>
@@ -8239,7 +8227,7 @@
       <c r="A189" s="5"/>
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
-      <c r="D189" s="11"/>
+      <c r="D189" s="10"/>
       <c r="E189" s="8"/>
       <c r="F189" s="8" t="s">
         <v>28</v>
@@ -8274,13 +8262,13 @@
       <c r="B190" s="8">
         <v>5.0</v>
       </c>
-      <c r="C190" s="13" t="s">
+      <c r="C190" s="12" t="s">
         <v>9</v>
       </c>
       <c r="D190" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="E190" s="13" t="s">
+      <c r="E190" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F190" s="8" t="s">
@@ -8289,7 +8277,7 @@
       <c r="G190" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H190" s="13" t="s">
+      <c r="H190" s="12" t="s">
         <v>17</v>
       </c>
       <c r="I190" s="8"/>
@@ -8318,13 +8306,13 @@
       <c r="B191" s="8">
         <v>19.0</v>
       </c>
-      <c r="C191" s="13" t="s">
+      <c r="C191" s="12" t="s">
         <v>9</v>
       </c>
       <c r="D191" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E191" s="13" t="s">
+      <c r="E191" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F191" s="8" t="s">
@@ -8333,7 +8321,7 @@
       <c r="G191" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H191" s="13" t="s">
+      <c r="H191" s="12" t="s">
         <v>17</v>
       </c>
       <c r="I191" s="8"/>
@@ -8362,22 +8350,22 @@
       <c r="B192" s="8">
         <v>5.0</v>
       </c>
-      <c r="C192" s="13" t="s">
+      <c r="C192" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="D192" s="13" t="s">
+      <c r="D192" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="E192" s="13" t="s">
+      <c r="E192" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F192" s="13" t="s">
+      <c r="F192" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G192" s="13" t="s">
+      <c r="G192" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="H192" s="13" t="s">
+      <c r="H192" s="12" t="s">
         <v>17</v>
       </c>
       <c r="I192" s="8"/>
@@ -8406,22 +8394,22 @@
       <c r="B193" s="8">
         <v>19.0</v>
       </c>
-      <c r="C193" s="18" t="s">
+      <c r="C193" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="D193" s="13" t="s">
+      <c r="D193" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="E193" s="13" t="s">
+      <c r="E193" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F193" s="13" t="s">
+      <c r="F193" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G193" s="13" t="s">
+      <c r="G193" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="H193" s="13" t="s">
+      <c r="H193" s="12" t="s">
         <v>17</v>
       </c>
       <c r="I193" s="8"/>
@@ -8447,7 +8435,7 @@
       <c r="A194" s="5"/>
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
-      <c r="D194" s="11"/>
+      <c r="D194" s="10"/>
       <c r="E194" s="8"/>
       <c r="F194" s="8"/>
       <c r="G194" s="8"/>
@@ -8475,7 +8463,7 @@
       <c r="A195" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B195" s="19">
+      <c r="B195" s="8">
         <v>10.0</v>
       </c>
       <c r="C195" s="8" t="s">
@@ -8487,10 +8475,10 @@
       <c r="E195" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F195" s="13" t="s">
+      <c r="F195" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G195" s="13" t="s">
+      <c r="G195" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H195" s="8" t="s">
@@ -8519,7 +8507,7 @@
       <c r="A196" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B196" s="19">
+      <c r="B196" s="8">
         <v>11.0</v>
       </c>
       <c r="C196" s="8" t="s">
@@ -8531,10 +8519,10 @@
       <c r="E196" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F196" s="13" t="s">
+      <c r="F196" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G196" s="13" t="s">
+      <c r="G196" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H196" s="8" t="s">
@@ -8563,7 +8551,7 @@
       <c r="A197" s="5"/>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
-      <c r="D197" s="11"/>
+      <c r="D197" s="10"/>
       <c r="E197" s="8"/>
       <c r="F197" s="8"/>
       <c r="G197" s="8"/>
@@ -8591,7 +8579,7 @@
       <c r="A198" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B198" s="19">
+      <c r="B198" s="8">
         <v>10.0</v>
       </c>
       <c r="C198" s="8" t="s">
@@ -8603,10 +8591,10 @@
       <c r="E198" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="F198" s="13" t="s">
+      <c r="F198" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G198" s="13" t="s">
+      <c r="G198" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H198" s="8" t="s">
@@ -8635,7 +8623,7 @@
       <c r="A199" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B199" s="19">
+      <c r="B199" s="8">
         <v>11.0</v>
       </c>
       <c r="C199" s="8" t="s">
@@ -8647,10 +8635,10 @@
       <c r="E199" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="F199" s="13" t="s">
+      <c r="F199" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G199" s="13" t="s">
+      <c r="G199" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H199" s="8" t="s">
@@ -8679,7 +8667,7 @@
       <c r="A200" s="5"/>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
-      <c r="D200" s="11"/>
+      <c r="D200" s="10"/>
       <c r="E200" s="8"/>
       <c r="F200" s="8"/>
       <c r="G200" s="8"/>
@@ -8707,22 +8695,22 @@
       <c r="A201" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B201" s="19">
+      <c r="B201" s="8">
         <v>10.0</v>
       </c>
       <c r="C201" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D201" s="11" t="s">
+      <c r="D201" s="10" t="s">
         <v>90</v>
       </c>
       <c r="E201" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F201" s="13" t="s">
+      <c r="F201" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G201" s="13" t="s">
+      <c r="G201" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H201" s="8" t="s">
@@ -8751,22 +8739,22 @@
       <c r="A202" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B202" s="19">
+      <c r="B202" s="8">
         <v>11.0</v>
       </c>
       <c r="C202" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D202" s="11" t="s">
+      <c r="D202" s="10" t="s">
         <v>99</v>
       </c>
       <c r="E202" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F202" s="13" t="s">
+      <c r="F202" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G202" s="13" t="s">
+      <c r="G202" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H202" s="8" t="s">
@@ -8795,7 +8783,7 @@
       <c r="A203" s="5"/>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
-      <c r="D203" s="11"/>
+      <c r="D203" s="10"/>
       <c r="E203" s="8"/>
       <c r="F203" s="8"/>
       <c r="G203" s="8"/>
@@ -8829,16 +8817,16 @@
       <c r="C204" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D204" s="11" t="s">
+      <c r="D204" s="10" t="s">
         <v>90</v>
       </c>
       <c r="E204" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F204" s="13" t="s">
+      <c r="F204" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G204" s="13" t="s">
+      <c r="G204" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H204" s="8" t="s">
@@ -8873,16 +8861,16 @@
       <c r="C205" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D205" s="11" t="s">
+      <c r="D205" s="10" t="s">
         <v>99</v>
       </c>
       <c r="E205" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F205" s="13" t="s">
+      <c r="F205" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G205" s="13" t="s">
+      <c r="G205" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H205" s="8" t="s">
@@ -8911,7 +8899,7 @@
       <c r="A206" s="5"/>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
-      <c r="D206" s="11"/>
+      <c r="D206" s="10"/>
       <c r="E206" s="8"/>
       <c r="F206" s="8"/>
       <c r="G206" s="8"/>
@@ -8951,10 +8939,10 @@
       <c r="E207" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F207" s="13" t="s">
+      <c r="F207" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G207" s="13" t="s">
+      <c r="G207" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H207" s="8" t="s">
@@ -8995,10 +8983,10 @@
       <c r="E208" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F208" s="13" t="s">
+      <c r="F208" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G208" s="13" t="s">
+      <c r="G208" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H208" s="8" t="s">
@@ -9027,7 +9015,7 @@
       <c r="A209" s="5"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
-      <c r="D209" s="11"/>
+      <c r="D209" s="10"/>
       <c r="E209" s="8"/>
       <c r="F209" s="8"/>
       <c r="G209" s="8"/>
@@ -9067,10 +9055,10 @@
       <c r="E210" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F210" s="13" t="s">
+      <c r="F210" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G210" s="13" t="s">
+      <c r="G210" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H210" s="8" t="s">
@@ -9111,10 +9099,10 @@
       <c r="E211" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F211" s="13" t="s">
+      <c r="F211" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G211" s="13" t="s">
+      <c r="G211" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H211" s="8" t="s">
@@ -9143,7 +9131,7 @@
       <c r="A212" s="5"/>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
-      <c r="D212" s="11"/>
+      <c r="D212" s="10"/>
       <c r="E212" s="8"/>
       <c r="F212" s="8"/>
       <c r="G212" s="8"/>
@@ -9177,16 +9165,16 @@
       <c r="C213" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D213" s="11" t="s">
+      <c r="D213" s="10" t="s">
         <v>90</v>
       </c>
       <c r="E213" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F213" s="13" t="s">
+      <c r="F213" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G213" s="13" t="s">
+      <c r="G213" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H213" s="8" t="s">
@@ -9221,16 +9209,16 @@
       <c r="C214" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D214" s="11" t="s">
+      <c r="D214" s="10" t="s">
         <v>99</v>
       </c>
       <c r="E214" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F214" s="13" t="s">
+      <c r="F214" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G214" s="13" t="s">
+      <c r="G214" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H214" s="8" t="s">
@@ -9259,7 +9247,7 @@
       <c r="A215" s="5"/>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
-      <c r="D215" s="11"/>
+      <c r="D215" s="10"/>
       <c r="E215" s="8"/>
       <c r="F215" s="8"/>
       <c r="G215" s="8"/>
@@ -9375,7 +9363,7 @@
       <c r="A218" s="5"/>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
-      <c r="D218" s="11"/>
+      <c r="D218" s="10"/>
       <c r="E218" s="8"/>
       <c r="F218" s="8"/>
       <c r="G218" s="8"/>
@@ -9403,7 +9391,7 @@
       <c r="A219" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B219" s="19">
+      <c r="B219" s="8">
         <v>17.0</v>
       </c>
       <c r="C219" s="8" t="s">
@@ -9447,7 +9435,7 @@
       <c r="A220" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B220" s="19">
+      <c r="B220" s="8">
         <v>18.0</v>
       </c>
       <c r="C220" s="8" t="s">
@@ -9491,7 +9479,7 @@
       <c r="A221" s="5"/>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
-      <c r="D221" s="11"/>
+      <c r="D221" s="10"/>
       <c r="E221" s="8"/>
       <c r="F221" s="8"/>
       <c r="G221" s="8"/>
@@ -9519,10 +9507,10 @@
       <c r="A222" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B222" s="19">
+      <c r="B222" s="8">
         <v>17.0</v>
       </c>
-      <c r="C222" s="13" t="s">
+      <c r="C222" s="12" t="s">
         <v>66</v>
       </c>
       <c r="D222" s="8" t="s">
@@ -9531,10 +9519,10 @@
       <c r="E222" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F222" s="13" t="s">
+      <c r="F222" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G222" s="13" t="s">
+      <c r="G222" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H222" s="8" t="s">
@@ -9563,10 +9551,10 @@
       <c r="A223" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B223" s="19">
+      <c r="B223" s="8">
         <v>18.0</v>
       </c>
-      <c r="C223" s="13" t="s">
+      <c r="C223" s="12" t="s">
         <v>66</v>
       </c>
       <c r="D223" s="8" t="s">
@@ -9575,10 +9563,10 @@
       <c r="E223" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F223" s="13" t="s">
+      <c r="F223" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G223" s="13" t="s">
+      <c r="G223" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H223" s="8" t="s">
@@ -9607,16 +9595,16 @@
       <c r="A224" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B224" s="19">
+      <c r="B224" s="8">
         <v>17.0</v>
       </c>
-      <c r="C224" s="13" t="s">
+      <c r="C224" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D224" s="13" t="s">
+      <c r="D224" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="E224" s="13" t="s">
+      <c r="E224" s="12" t="s">
         <v>64</v>
       </c>
       <c r="F224" s="8" t="s">
@@ -9625,7 +9613,7 @@
       <c r="G224" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H224" s="13" t="s">
+      <c r="H224" s="12" t="s">
         <v>64</v>
       </c>
       <c r="I224" s="8"/>
@@ -9651,16 +9639,16 @@
       <c r="A225" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B225" s="19">
+      <c r="B225" s="8">
         <v>18.0</v>
       </c>
-      <c r="C225" s="13" t="s">
+      <c r="C225" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D225" s="13" t="s">
+      <c r="D225" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="E225" s="13" t="s">
+      <c r="E225" s="12" t="s">
         <v>64</v>
       </c>
       <c r="F225" s="8" t="s">
@@ -9669,7 +9657,7 @@
       <c r="G225" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H225" s="13" t="s">
+      <c r="H225" s="12" t="s">
         <v>64</v>
       </c>
       <c r="I225" s="8"/>
@@ -9695,7 +9683,7 @@
       <c r="A226" s="5"/>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
-      <c r="D226" s="11"/>
+      <c r="D226" s="10"/>
       <c r="E226" s="8"/>
       <c r="F226" s="8"/>
       <c r="G226" s="8"/>
@@ -9723,16 +9711,16 @@
       <c r="A227" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B227" s="19">
+      <c r="B227" s="8">
         <v>17.0</v>
       </c>
-      <c r="C227" s="13" t="s">
+      <c r="C227" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D227" s="13" t="s">
+      <c r="D227" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="E227" s="13" t="s">
+      <c r="E227" s="12" t="s">
         <v>60</v>
       </c>
       <c r="F227" s="8" t="s">
@@ -9741,7 +9729,7 @@
       <c r="G227" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H227" s="13" t="s">
+      <c r="H227" s="12" t="s">
         <v>60</v>
       </c>
       <c r="I227" s="8"/>
@@ -9767,16 +9755,16 @@
       <c r="A228" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B228" s="19">
+      <c r="B228" s="8">
         <v>18.0</v>
       </c>
-      <c r="C228" s="13" t="s">
+      <c r="C228" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D228" s="13" t="s">
+      <c r="D228" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="E228" s="13" t="s">
+      <c r="E228" s="12" t="s">
         <v>60</v>
       </c>
       <c r="F228" s="8" t="s">
@@ -9785,7 +9773,7 @@
       <c r="G228" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H228" s="13" t="s">
+      <c r="H228" s="12" t="s">
         <v>60</v>
       </c>
       <c r="I228" s="8"/>
@@ -9811,7 +9799,7 @@
       <c r="A229" s="5"/>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
-      <c r="D229" s="11"/>
+      <c r="D229" s="10"/>
       <c r="E229" s="8"/>
       <c r="F229" s="8"/>
       <c r="G229" s="8"/>
@@ -9839,22 +9827,22 @@
       <c r="A230" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B230" s="19">
+      <c r="B230" s="8">
         <v>31.0</v>
       </c>
       <c r="C230" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D230" s="13" t="s">
+      <c r="D230" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="E230" s="13" t="s">
+      <c r="E230" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F230" s="13" t="s">
+      <c r="F230" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G230" s="13" t="s">
+      <c r="G230" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H230" s="8" t="s">
@@ -9880,25 +9868,25 @@
       <c r="Z230" s="9"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="20" t="s">
+      <c r="A231" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B231" s="19">
+      <c r="B231" s="8">
         <v>1.0</v>
       </c>
       <c r="C231" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D231" s="13" t="s">
+      <c r="D231" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="E231" s="13" t="s">
+      <c r="E231" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F231" s="13" t="s">
+      <c r="F231" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G231" s="13" t="s">
+      <c r="G231" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H231" s="8" t="s">
@@ -9927,7 +9915,7 @@
       <c r="A232" s="5"/>
       <c r="B232" s="8"/>
       <c r="C232" s="8"/>
-      <c r="D232" s="11"/>
+      <c r="D232" s="10"/>
       <c r="E232" s="8"/>
       <c r="F232" s="8"/>
       <c r="G232" s="8"/>
@@ -9955,22 +9943,22 @@
       <c r="A233" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B233" s="19">
+      <c r="B233" s="8">
         <v>31.0</v>
       </c>
       <c r="C233" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D233" s="13" t="s">
+      <c r="D233" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="E233" s="13" t="s">
+      <c r="E233" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F233" s="13" t="s">
+      <c r="F233" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G233" s="13" t="s">
+      <c r="G233" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H233" s="8" t="s">
@@ -9996,25 +9984,25 @@
       <c r="Z233" s="9"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="A234" s="20" t="s">
+      <c r="A234" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B234" s="19">
+      <c r="B234" s="8">
         <v>1.0</v>
       </c>
       <c r="C234" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D234" s="13" t="s">
+      <c r="D234" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="E234" s="13" t="s">
+      <c r="E234" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F234" s="13" t="s">
+      <c r="F234" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G234" s="13" t="s">
+      <c r="G234" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H234" s="8" t="s">
@@ -10041,30 +10029,30 @@
     </row>
     <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="15"/>
-      <c r="B235" s="13"/>
-      <c r="C235" s="13"/>
+      <c r="B235" s="12"/>
+      <c r="C235" s="12"/>
       <c r="D235" s="16"/>
-      <c r="E235" s="13"/>
-      <c r="F235" s="13"/>
-      <c r="G235" s="13"/>
-      <c r="H235" s="13"/>
-      <c r="I235" s="13"/>
-      <c r="J235" s="13"/>
-      <c r="K235" s="13"/>
-      <c r="L235" s="13"/>
-      <c r="M235" s="13"/>
-      <c r="N235" s="13"/>
-      <c r="O235" s="13"/>
-      <c r="P235" s="13"/>
-      <c r="Q235" s="13"/>
-      <c r="R235" s="13"/>
-      <c r="S235" s="13"/>
-      <c r="T235" s="13"/>
-      <c r="U235" s="13"/>
-      <c r="V235" s="13"/>
-      <c r="W235" s="13"/>
-      <c r="X235" s="13"/>
-      <c r="Y235" s="13"/>
+      <c r="E235" s="12"/>
+      <c r="F235" s="12"/>
+      <c r="G235" s="12"/>
+      <c r="H235" s="12"/>
+      <c r="I235" s="12"/>
+      <c r="J235" s="12"/>
+      <c r="K235" s="12"/>
+      <c r="L235" s="12"/>
+      <c r="M235" s="12"/>
+      <c r="N235" s="12"/>
+      <c r="O235" s="12"/>
+      <c r="P235" s="12"/>
+      <c r="Q235" s="12"/>
+      <c r="R235" s="12"/>
+      <c r="S235" s="12"/>
+      <c r="T235" s="12"/>
+      <c r="U235" s="12"/>
+      <c r="V235" s="12"/>
+      <c r="W235" s="12"/>
+      <c r="X235" s="12"/>
+      <c r="Y235" s="12"/>
       <c r="Z235" s="17"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
@@ -10159,7 +10147,7 @@
       <c r="A238" s="5"/>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
-      <c r="D238" s="11"/>
+      <c r="D238" s="10"/>
       <c r="E238" s="8"/>
       <c r="F238" s="8"/>
       <c r="G238" s="8"/>
@@ -10363,7 +10351,7 @@
       <c r="A243" s="5"/>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
-      <c r="D243" s="11"/>
+      <c r="D243" s="10"/>
       <c r="E243" s="8"/>
       <c r="F243" s="8"/>
       <c r="G243" s="8"/>
@@ -10479,7 +10467,7 @@
       <c r="A246" s="5"/>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
-      <c r="D246" s="11"/>
+      <c r="D246" s="10"/>
       <c r="E246" s="8"/>
       <c r="F246" s="8"/>
       <c r="G246" s="8"/>
@@ -10595,7 +10583,7 @@
       <c r="A249" s="5"/>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
-      <c r="D249" s="11"/>
+      <c r="D249" s="10"/>
       <c r="E249" s="8"/>
       <c r="F249" s="8"/>
       <c r="G249" s="8"/>
@@ -10711,7 +10699,7 @@
       <c r="A252" s="5"/>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
-      <c r="D252" s="11"/>
+      <c r="D252" s="10"/>
       <c r="E252" s="8"/>
       <c r="F252" s="8"/>
       <c r="G252" s="8"/>
@@ -10827,7 +10815,7 @@
       <c r="A255" s="5"/>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
-      <c r="D255" s="11"/>
+      <c r="D255" s="10"/>
       <c r="E255" s="8"/>
       <c r="F255" s="8"/>
       <c r="G255" s="8"/>
@@ -10943,7 +10931,7 @@
       <c r="A258" s="5"/>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
-      <c r="D258" s="11"/>
+      <c r="D258" s="10"/>
       <c r="E258" s="8"/>
       <c r="F258" s="8"/>
       <c r="G258" s="8"/>
@@ -11059,7 +11047,7 @@
       <c r="A261" s="5"/>
       <c r="B261" s="8"/>
       <c r="C261" s="8"/>
-      <c r="D261" s="11"/>
+      <c r="D261" s="10"/>
       <c r="E261" s="8"/>
       <c r="F261" s="8"/>
       <c r="G261" s="8"/>
@@ -11175,7 +11163,7 @@
       <c r="A264" s="5"/>
       <c r="B264" s="8"/>
       <c r="C264" s="8"/>
-      <c r="D264" s="11"/>
+      <c r="D264" s="10"/>
       <c r="E264" s="8"/>
       <c r="F264" s="8"/>
       <c r="G264" s="8"/>
@@ -11291,7 +11279,7 @@
       <c r="A267" s="5"/>
       <c r="B267" s="8"/>
       <c r="C267" s="8"/>
-      <c r="D267" s="11"/>
+      <c r="D267" s="10"/>
       <c r="E267" s="8"/>
       <c r="F267" s="8"/>
       <c r="G267" s="8"/>
@@ -11325,7 +11313,7 @@
       <c r="C268" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D268" s="21" t="s">
+      <c r="D268" s="13" t="s">
         <v>107</v>
       </c>
       <c r="E268" s="8" t="s">
@@ -11369,7 +11357,7 @@
       <c r="C269" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D269" s="21" t="s">
+      <c r="D269" s="13" t="s">
         <v>107</v>
       </c>
       <c r="E269" s="8" t="s">
@@ -11407,7 +11395,7 @@
       <c r="A270" s="5"/>
       <c r="B270" s="8"/>
       <c r="C270" s="8"/>
-      <c r="D270" s="11"/>
+      <c r="D270" s="10"/>
       <c r="E270" s="8"/>
       <c r="F270" s="8"/>
       <c r="G270" s="8"/>
@@ -11764,13 +11752,13 @@
       <c r="D279" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="E279" s="13" t="s">
+      <c r="E279" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F279" s="13" t="s">
+      <c r="F279" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="G279" s="13" t="s">
+      <c r="G279" s="12" t="s">
         <v>114</v>
       </c>
       <c r="H279" s="8" t="s">
@@ -11805,16 +11793,16 @@
       <c r="C280" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D280" s="13" t="s">
+      <c r="D280" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="E280" s="13" t="s">
+      <c r="E280" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F280" s="13" t="s">
+      <c r="F280" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="G280" s="13" t="s">
+      <c r="G280" s="12" t="s">
         <v>114</v>
       </c>
       <c r="H280" s="8" t="s">
@@ -11880,13 +11868,13 @@
       <c r="D282" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="E282" s="13" t="s">
+      <c r="E282" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F282" s="13" t="s">
+      <c r="F282" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="G282" s="13" t="s">
+      <c r="G282" s="12" t="s">
         <v>114</v>
       </c>
       <c r="H282" s="8" t="s">
@@ -11921,16 +11909,16 @@
       <c r="C283" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D283" s="13" t="s">
+      <c r="D283" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="E283" s="13" t="s">
+      <c r="E283" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F283" s="13" t="s">
+      <c r="F283" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="G283" s="13" t="s">
+      <c r="G283" s="12" t="s">
         <v>114</v>
       </c>
       <c r="H283" s="8" t="s">
@@ -11957,30 +11945,30 @@
     </row>
     <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="15"/>
-      <c r="B284" s="13"/>
-      <c r="C284" s="13"/>
-      <c r="D284" s="13"/>
-      <c r="E284" s="13"/>
-      <c r="F284" s="13"/>
-      <c r="G284" s="13"/>
-      <c r="H284" s="13"/>
-      <c r="I284" s="13"/>
-      <c r="J284" s="13"/>
-      <c r="K284" s="13"/>
-      <c r="L284" s="13"/>
-      <c r="M284" s="13"/>
-      <c r="N284" s="13"/>
-      <c r="O284" s="13"/>
-      <c r="P284" s="13"/>
-      <c r="Q284" s="13"/>
-      <c r="R284" s="13"/>
-      <c r="S284" s="13"/>
-      <c r="T284" s="13"/>
-      <c r="U284" s="13"/>
-      <c r="V284" s="13"/>
-      <c r="W284" s="13"/>
-      <c r="X284" s="13"/>
-      <c r="Y284" s="13"/>
+      <c r="B284" s="12"/>
+      <c r="C284" s="12"/>
+      <c r="D284" s="12"/>
+      <c r="E284" s="12"/>
+      <c r="F284" s="12"/>
+      <c r="G284" s="12"/>
+      <c r="H284" s="12"/>
+      <c r="I284" s="12"/>
+      <c r="J284" s="12"/>
+      <c r="K284" s="12"/>
+      <c r="L284" s="12"/>
+      <c r="M284" s="12"/>
+      <c r="N284" s="12"/>
+      <c r="O284" s="12"/>
+      <c r="P284" s="12"/>
+      <c r="Q284" s="12"/>
+      <c r="R284" s="12"/>
+      <c r="S284" s="12"/>
+      <c r="T284" s="12"/>
+      <c r="U284" s="12"/>
+      <c r="V284" s="12"/>
+      <c r="W284" s="12"/>
+      <c r="X284" s="12"/>
+      <c r="Y284" s="12"/>
       <c r="Z284" s="17"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
@@ -12015,25 +12003,25 @@
       <c r="A286" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B286" s="13">
+      <c r="B286" s="12">
         <v>7.0</v>
       </c>
-      <c r="C286" s="13" t="s">
+      <c r="C286" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D286" s="13" t="s">
+      <c r="D286" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="E286" s="13" t="s">
+      <c r="E286" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F286" s="13" t="s">
+      <c r="F286" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G286" s="13" t="s">
+      <c r="G286" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H286" s="13" t="s">
+      <c r="H286" s="12" t="s">
         <v>46</v>
       </c>
       <c r="I286" s="8"/>
@@ -12059,25 +12047,25 @@
       <c r="A287" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B287" s="13">
+      <c r="B287" s="12">
         <v>14.0</v>
       </c>
-      <c r="C287" s="13" t="s">
+      <c r="C287" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D287" s="13" t="s">
+      <c r="D287" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E287" s="13" t="s">
+      <c r="E287" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F287" s="13" t="s">
+      <c r="F287" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G287" s="13" t="s">
+      <c r="G287" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H287" s="13" t="s">
+      <c r="H287" s="12" t="s">
         <v>46</v>
       </c>
       <c r="I287" s="8"/>
@@ -12131,25 +12119,25 @@
       <c r="A289" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B289" s="13">
+      <c r="B289" s="12">
         <v>7.0</v>
       </c>
-      <c r="C289" s="13" t="s">
+      <c r="C289" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D289" s="13" t="s">
+      <c r="D289" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="E289" s="13" t="s">
+      <c r="E289" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F289" s="13" t="s">
+      <c r="F289" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G289" s="13" t="s">
+      <c r="G289" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H289" s="13" t="s">
+      <c r="H289" s="12" t="s">
         <v>17</v>
       </c>
       <c r="I289" s="8"/>
@@ -12175,25 +12163,25 @@
       <c r="A290" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B290" s="13">
+      <c r="B290" s="12">
         <v>14.0</v>
       </c>
-      <c r="C290" s="13" t="s">
+      <c r="C290" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D290" s="13" t="s">
+      <c r="D290" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E290" s="13" t="s">
+      <c r="E290" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F290" s="13" t="s">
+      <c r="F290" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G290" s="13" t="s">
+      <c r="G290" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H290" s="13" t="s">
+      <c r="H290" s="12" t="s">
         <v>17</v>
       </c>
       <c r="I290" s="8"/>
@@ -12219,16 +12207,16 @@
       <c r="A291" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B291" s="13">
+      <c r="B291" s="12">
         <v>7.0</v>
       </c>
-      <c r="C291" s="13" t="s">
+      <c r="C291" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D291" s="13" t="s">
+      <c r="D291" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="E291" s="13" t="s">
+      <c r="E291" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F291" s="8" t="s">
@@ -12237,7 +12225,7 @@
       <c r="G291" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H291" s="13" t="s">
+      <c r="H291" s="12" t="s">
         <v>17</v>
       </c>
       <c r="I291" s="8"/>
@@ -12263,16 +12251,16 @@
       <c r="A292" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B292" s="13">
+      <c r="B292" s="12">
         <v>14.0</v>
       </c>
-      <c r="C292" s="13" t="s">
+      <c r="C292" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D292" s="13" t="s">
+      <c r="D292" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="E292" s="13" t="s">
+      <c r="E292" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F292" s="8" t="s">
@@ -12281,7 +12269,7 @@
       <c r="G292" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H292" s="13" t="s">
+      <c r="H292" s="12" t="s">
         <v>17</v>
       </c>
       <c r="I292" s="8"/>
@@ -12338,22 +12326,22 @@
       <c r="B294" s="8">
         <v>5.0</v>
       </c>
-      <c r="C294" s="13" t="s">
+      <c r="C294" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="D294" s="13" t="s">
+      <c r="D294" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E294" s="13" t="s">
+      <c r="E294" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F294" s="13" t="s">
+      <c r="F294" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G294" s="13" t="s">
+      <c r="G294" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H294" s="13" t="s">
+      <c r="H294" s="12" t="s">
         <v>73</v>
       </c>
       <c r="I294" s="8"/>
@@ -12382,22 +12370,22 @@
       <c r="B295" s="8">
         <v>6.0</v>
       </c>
-      <c r="C295" s="13" t="s">
+      <c r="C295" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D295" s="13" t="s">
+      <c r="D295" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E295" s="13" t="s">
+      <c r="E295" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F295" s="13" t="s">
+      <c r="F295" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G295" s="13" t="s">
+      <c r="G295" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H295" s="13" t="s">
+      <c r="H295" s="12" t="s">
         <v>73</v>
       </c>
       <c r="I295" s="8"/>
@@ -12454,22 +12442,22 @@
       <c r="B297" s="8">
         <v>5.0</v>
       </c>
-      <c r="C297" s="13" t="s">
+      <c r="C297" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D297" s="13" t="s">
+      <c r="D297" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E297" s="13" t="s">
+      <c r="E297" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="F297" s="13" t="s">
+      <c r="F297" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G297" s="13" t="s">
+      <c r="G297" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H297" s="13" t="s">
+      <c r="H297" s="12" t="s">
         <v>77</v>
       </c>
       <c r="I297" s="8"/>
@@ -12498,22 +12486,22 @@
       <c r="B298" s="8">
         <v>6.0</v>
       </c>
-      <c r="C298" s="13" t="s">
+      <c r="C298" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D298" s="13" t="s">
+      <c r="D298" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E298" s="13" t="s">
+      <c r="E298" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="F298" s="13" t="s">
+      <c r="F298" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G298" s="13" t="s">
+      <c r="G298" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H298" s="13" t="s">
+      <c r="H298" s="12" t="s">
         <v>77</v>
       </c>
       <c r="I298" s="8"/>
@@ -12573,16 +12561,16 @@
       <c r="C300" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D300" s="13" t="s">
+      <c r="D300" s="12" t="s">
         <v>32</v>
       </c>
       <c r="E300" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F300" s="13" t="s">
+      <c r="F300" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G300" s="13" t="s">
+      <c r="G300" s="12" t="s">
         <v>121</v>
       </c>
       <c r="H300" s="8" t="s">
@@ -12617,16 +12605,16 @@
       <c r="C301" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D301" s="13" t="s">
+      <c r="D301" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E301" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F301" s="13" t="s">
+      <c r="F301" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G301" s="13" t="s">
+      <c r="G301" s="12" t="s">
         <v>121</v>
       </c>
       <c r="H301" s="8" t="s">
@@ -12689,16 +12677,16 @@
       <c r="C303" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D303" s="13" t="s">
+      <c r="D303" s="12" t="s">
         <v>32</v>
       </c>
       <c r="E303" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F303" s="13" t="s">
+      <c r="F303" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G303" s="13" t="s">
+      <c r="G303" s="12" t="s">
         <v>121</v>
       </c>
       <c r="H303" s="8" t="s">
@@ -12733,16 +12721,16 @@
       <c r="C304" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D304" s="13" t="s">
+      <c r="D304" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E304" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F304" s="13" t="s">
+      <c r="F304" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G304" s="13" t="s">
+      <c r="G304" s="12" t="s">
         <v>121</v>
       </c>
       <c r="H304" s="8" t="s">
@@ -12805,19 +12793,19 @@
       <c r="C306" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D306" s="13" t="s">
+      <c r="D306" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E306" s="13" t="s">
+      <c r="E306" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F306" s="13" t="s">
+      <c r="F306" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G306" s="13" t="s">
+      <c r="G306" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H306" s="13" t="s">
+      <c r="H306" s="12" t="s">
         <v>17</v>
       </c>
       <c r="I306" s="8"/>
@@ -12849,19 +12837,19 @@
       <c r="C307" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D307" s="13" t="s">
+      <c r="D307" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E307" s="13" t="s">
+      <c r="E307" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F307" s="13" t="s">
+      <c r="F307" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G307" s="13" t="s">
+      <c r="G307" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H307" s="13" t="s">
+      <c r="H307" s="12" t="s">
         <v>17</v>
       </c>
       <c r="I307" s="8"/>
@@ -12890,13 +12878,13 @@
       <c r="B308" s="8">
         <v>5.0</v>
       </c>
-      <c r="C308" s="13" t="s">
+      <c r="C308" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D308" s="13" t="s">
+      <c r="D308" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="E308" s="13" t="s">
+      <c r="E308" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F308" s="8" t="s">
@@ -12905,7 +12893,7 @@
       <c r="G308" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H308" s="13" t="s">
+      <c r="H308" s="12" t="s">
         <v>17</v>
       </c>
       <c r="I308" s="8"/>
@@ -12934,13 +12922,13 @@
       <c r="B309" s="8">
         <v>6.0</v>
       </c>
-      <c r="C309" s="13" t="s">
+      <c r="C309" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D309" s="13" t="s">
+      <c r="D309" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="E309" s="13" t="s">
+      <c r="E309" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F309" s="8" t="s">
@@ -12949,7 +12937,7 @@
       <c r="G309" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H309" s="13" t="s">
+      <c r="H309" s="12" t="s">
         <v>17</v>
       </c>
       <c r="I309" s="8"/>
@@ -13006,22 +12994,22 @@
       <c r="B311" s="8">
         <v>12.0</v>
       </c>
-      <c r="C311" s="13" t="s">
+      <c r="C311" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D311" s="13" t="s">
+      <c r="D311" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E311" s="13" t="s">
+      <c r="E311" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F311" s="13" t="s">
+      <c r="F311" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G311" s="13" t="s">
+      <c r="G311" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H311" s="13" t="s">
+      <c r="H311" s="12" t="s">
         <v>48</v>
       </c>
       <c r="I311" s="8"/>
@@ -13050,22 +13038,22 @@
       <c r="B312" s="8">
         <v>13.0</v>
       </c>
-      <c r="C312" s="13" t="s">
+      <c r="C312" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D312" s="13" t="s">
+      <c r="D312" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E312" s="13" t="s">
+      <c r="E312" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F312" s="13" t="s">
+      <c r="F312" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G312" s="13" t="s">
+      <c r="G312" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H312" s="13" t="s">
+      <c r="H312" s="12" t="s">
         <v>48</v>
       </c>
       <c r="I312" s="8"/>
@@ -13122,19 +13110,19 @@
       <c r="B314" s="8">
         <v>12.0</v>
       </c>
-      <c r="C314" s="13" t="s">
+      <c r="C314" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D314" s="13" t="s">
+      <c r="D314" s="12" t="s">
         <v>32</v>
       </c>
       <c r="E314" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F314" s="13" t="s">
+      <c r="F314" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G314" s="13" t="s">
+      <c r="G314" s="12" t="s">
         <v>121</v>
       </c>
       <c r="H314" s="8" t="s">
@@ -13166,19 +13154,19 @@
       <c r="B315" s="8">
         <v>13.0</v>
       </c>
-      <c r="C315" s="13" t="s">
+      <c r="C315" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D315" s="13" t="s">
+      <c r="D315" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E315" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F315" s="13" t="s">
+      <c r="F315" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G315" s="13" t="s">
+      <c r="G315" s="12" t="s">
         <v>121</v>
       </c>
       <c r="H315" s="8" t="s">
@@ -13238,13 +13226,13 @@
       <c r="B317" s="8">
         <v>12.0</v>
       </c>
-      <c r="C317" s="13" t="s">
+      <c r="C317" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D317" s="13" t="s">
+      <c r="D317" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E317" s="13" t="s">
+      <c r="E317" s="12" t="s">
         <v>53</v>
       </c>
       <c r="F317" s="8" t="s">
@@ -13253,7 +13241,7 @@
       <c r="G317" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H317" s="13" t="s">
+      <c r="H317" s="12" t="s">
         <v>53</v>
       </c>
       <c r="I317" s="8"/>
@@ -13282,13 +13270,13 @@
       <c r="B318" s="8">
         <v>13.0</v>
       </c>
-      <c r="C318" s="13" t="s">
+      <c r="C318" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D318" s="13" t="s">
+      <c r="D318" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E318" s="13" t="s">
+      <c r="E318" s="12" t="s">
         <v>53</v>
       </c>
       <c r="F318" s="8" t="s">
@@ -13297,7 +13285,7 @@
       <c r="G318" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H318" s="13" t="s">
+      <c r="H318" s="12" t="s">
         <v>53</v>
       </c>
       <c r="I318" s="8"/>
@@ -13357,16 +13345,16 @@
       <c r="C320" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D320" s="13" t="s">
+      <c r="D320" s="12" t="s">
         <v>32</v>
       </c>
       <c r="E320" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F320" s="13" t="s">
+      <c r="F320" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G320" s="13" t="s">
+      <c r="G320" s="12" t="s">
         <v>121</v>
       </c>
       <c r="H320" s="8" t="s">
@@ -13401,16 +13389,16 @@
       <c r="C321" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D321" s="13" t="s">
+      <c r="D321" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E321" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F321" s="13" t="s">
+      <c r="F321" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G321" s="13" t="s">
+      <c r="G321" s="12" t="s">
         <v>121</v>
       </c>
       <c r="H321" s="8" t="s">
@@ -13445,7 +13433,7 @@
       <c r="C322" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D322" s="13" t="s">
+      <c r="D322" s="12" t="s">
         <v>124</v>
       </c>
       <c r="E322" s="8" t="s">
@@ -13489,7 +13477,7 @@
       <c r="C323" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D323" s="13" t="s">
+      <c r="D323" s="12" t="s">
         <v>124</v>
       </c>
       <c r="E323" s="8" t="s">
@@ -13671,7 +13659,7 @@
       <c r="A328" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B328" s="13">
+      <c r="B328" s="12">
         <v>12.0</v>
       </c>
       <c r="C328" s="8" t="s">
@@ -13680,13 +13668,13 @@
       <c r="D328" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="E328" s="13" t="s">
+      <c r="E328" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F328" s="13" t="s">
+      <c r="F328" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G328" s="13" t="s">
+      <c r="G328" s="12" t="s">
         <v>121</v>
       </c>
       <c r="H328" s="8" t="s">
@@ -13715,22 +13703,22 @@
       <c r="A329" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B329" s="13">
+      <c r="B329" s="12">
         <v>13.0</v>
       </c>
       <c r="C329" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D329" s="13" t="s">
+      <c r="D329" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="E329" s="13" t="s">
+      <c r="E329" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F329" s="13" t="s">
+      <c r="F329" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G329" s="13" t="s">
+      <c r="G329" s="12" t="s">
         <v>121</v>
       </c>
       <c r="H329" s="8" t="s">
@@ -13787,7 +13775,7 @@
       <c r="A331" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B331" s="13">
+      <c r="B331" s="12">
         <v>12.0</v>
       </c>
       <c r="C331" s="8" t="s">
@@ -13796,13 +13784,13 @@
       <c r="D331" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="E331" s="13" t="s">
+      <c r="E331" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F331" s="13" t="s">
+      <c r="F331" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G331" s="13" t="s">
+      <c r="G331" s="12" t="s">
         <v>121</v>
       </c>
       <c r="H331" s="8" t="s">
@@ -13831,22 +13819,22 @@
       <c r="A332" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B332" s="13">
+      <c r="B332" s="12">
         <v>13.0</v>
       </c>
       <c r="C332" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D332" s="13" t="s">
+      <c r="D332" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="E332" s="13" t="s">
+      <c r="E332" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F332" s="13" t="s">
+      <c r="F332" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G332" s="13" t="s">
+      <c r="G332" s="12" t="s">
         <v>121</v>
       </c>
       <c r="H332" s="8" t="s">

--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="121">
   <si>
     <t xml:space="preserve">MÊS</t>
   </si>
@@ -239,9 +239,6 @@
   </si>
   <si>
     <t xml:space="preserve">Avaliação após término da disciplina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procedimentos Intradérmicos e Intramusculares – Teoria</t>
   </si>
   <si>
     <t xml:space="preserve">PROINSU BA 220225</t>
@@ -5006,28 +5003,14 @@
       <c r="Z107" s="9"/>
     </row>
     <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B108" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D108" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F108" s="8" t="s">
-        <v>72</v>
-      </c>
+      <c r="A108" s="5"/>
+      <c r="B108" s="6"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="7"/>
+      <c r="E108" s="6"/>
+      <c r="F108" s="8"/>
       <c r="G108" s="8"/>
-      <c r="H108" s="6" t="s">
-        <v>64</v>
-      </c>
+      <c r="H108" s="6"/>
       <c r="I108" s="8"/>
       <c r="J108" s="8"/>
       <c r="K108" s="8"/>
@@ -5127,22 +5110,22 @@
         <v>4</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D111" s="7" t="s">
         <v>31</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I111" s="8"/>
       <c r="J111" s="8"/>
@@ -5171,7 +5154,7 @@
         <v>25</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D112" s="7" t="s">
         <v>56</v>
@@ -5183,10 +5166,10 @@
         <v>42</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I112" s="8"/>
       <c r="J112" s="8"/>
@@ -5215,7 +5198,7 @@
         <v>26</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D113" s="7" t="s">
         <v>29</v>
@@ -5227,10 +5210,10 @@
         <v>28</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I113" s="8"/>
       <c r="J113" s="8"/>
@@ -5259,13 +5242,13 @@
         <v>1</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D114" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>44</v>
@@ -5274,7 +5257,7 @@
         <v>35</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I114" s="8"/>
       <c r="J114" s="8"/>
@@ -5303,13 +5286,13 @@
         <v>2</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D115" s="7" t="s">
         <v>37</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F115" s="6" t="s">
         <v>44</v>
@@ -5318,7 +5301,7 @@
         <v>35</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I115" s="8"/>
       <c r="J115" s="8"/>
@@ -5431,22 +5414,22 @@
         <v>4</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D119" s="7" t="s">
         <v>16</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I119" s="8"/>
       <c r="J119" s="8"/>
@@ -5475,7 +5458,7 @@
         <v>25</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D120" s="7" t="s">
         <v>56</v>
@@ -5487,10 +5470,10 @@
         <v>28</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I120" s="8"/>
       <c r="J120" s="8"/>
@@ -5519,7 +5502,7 @@
         <v>26</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D121" s="7" t="s">
         <v>29</v>
@@ -5531,10 +5514,10 @@
         <v>28</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H121" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I121" s="8"/>
       <c r="J121" s="8"/>
@@ -5563,13 +5546,13 @@
         <v>1</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D122" s="7" t="s">
         <v>37</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>44</v>
@@ -5578,7 +5561,7 @@
         <v>35</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I122" s="8"/>
       <c r="J122" s="8"/>
@@ -5607,13 +5590,13 @@
         <v>2</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D123" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F123" s="6" t="s">
         <v>44</v>
@@ -5622,7 +5605,7 @@
         <v>35</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I123" s="8"/>
       <c r="J123" s="8"/>
@@ -5735,7 +5718,7 @@
         <v>25</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D127" s="7" t="s">
         <v>56</v>
@@ -5750,7 +5733,7 @@
         <v>35</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I127" s="8"/>
       <c r="J127" s="8"/>
@@ -5779,7 +5762,7 @@
         <v>26</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D128" s="7" t="s">
         <v>29</v>
@@ -5794,7 +5777,7 @@
         <v>35</v>
       </c>
       <c r="H128" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I128" s="8"/>
       <c r="J128" s="8"/>
@@ -5823,13 +5806,13 @@
         <v>1</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D129" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F129" s="6" t="s">
         <v>44</v>
@@ -5838,7 +5821,7 @@
         <v>35</v>
       </c>
       <c r="H129" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I129" s="8"/>
       <c r="J129" s="8"/>
@@ -5867,13 +5850,13 @@
         <v>2</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D130" s="7" t="s">
         <v>37</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>44</v>
@@ -5882,7 +5865,7 @@
         <v>35</v>
       </c>
       <c r="H130" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I130" s="8"/>
       <c r="J130" s="8"/>
@@ -5995,10 +5978,10 @@
         <v>22</v>
       </c>
       <c r="C134" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D134" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>11</v>
@@ -6039,10 +6022,10 @@
         <v>23</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E135" s="6" t="s">
         <v>11</v>
@@ -6111,10 +6094,10 @@
         <v>22</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E137" s="6" t="s">
         <v>11</v>
@@ -6155,10 +6138,10 @@
         <v>23</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>11</v>
@@ -6431,7 +6414,7 @@
         <v>7</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D145" s="12" t="s">
         <v>36</v>
@@ -6475,7 +6458,7 @@
         <v>21</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D146" s="12" t="s">
         <v>38</v>
@@ -6547,13 +6530,13 @@
         <v>5</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F148" s="13" t="s">
         <v>69</v>
@@ -6562,7 +6545,7 @@
         <v>70</v>
       </c>
       <c r="H148" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I148" s="8"/>
       <c r="J148" s="8"/>
@@ -6591,13 +6574,13 @@
         <v>6</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E149" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F149" s="13" t="s">
         <v>69</v>
@@ -6606,7 +6589,7 @@
         <v>70</v>
       </c>
       <c r="H149" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I149" s="8"/>
       <c r="J149" s="8"/>
@@ -6663,22 +6646,22 @@
         <v>5</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H151" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I151" s="8"/>
       <c r="J151" s="8"/>
@@ -6707,22 +6690,22 @@
         <v>6</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G152" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H152" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I152" s="8"/>
       <c r="J152" s="8"/>
@@ -6779,13 +6762,13 @@
         <v>5</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F154" s="13" t="s">
         <v>69</v>
@@ -6794,7 +6777,7 @@
         <v>70</v>
       </c>
       <c r="H154" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I154" s="8"/>
       <c r="J154" s="8"/>
@@ -6823,13 +6806,13 @@
         <v>6</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F155" s="13" t="s">
         <v>69</v>
@@ -6838,7 +6821,7 @@
         <v>70</v>
       </c>
       <c r="H155" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I155" s="8"/>
       <c r="J155" s="8"/>
@@ -6898,7 +6881,7 @@
         <v>49</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E157" s="8" t="s">
         <v>48</v>
@@ -6942,7 +6925,7 @@
         <v>49</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E158" s="8" t="s">
         <v>48</v>
@@ -7014,7 +6997,7 @@
         <v>43</v>
       </c>
       <c r="D160" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E160" s="8" t="s">
         <v>41</v>
@@ -7023,7 +7006,7 @@
         <v>28</v>
       </c>
       <c r="G160" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H160" s="8" t="s">
         <v>41</v>
@@ -7058,7 +7041,7 @@
         <v>43</v>
       </c>
       <c r="D161" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E161" s="8" t="s">
         <v>41</v>
@@ -7067,7 +7050,7 @@
         <v>28</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H161" s="8" t="s">
         <v>41</v>
@@ -7130,7 +7113,7 @@
         <v>50</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E163" s="8" t="s">
         <v>51</v>
@@ -7139,7 +7122,7 @@
         <v>28</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H163" s="8" t="s">
         <v>51</v>
@@ -7174,7 +7157,7 @@
         <v>50</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E164" s="8" t="s">
         <v>51</v>
@@ -7183,7 +7166,7 @@
         <v>28</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H164" s="8" t="s">
         <v>51</v>
@@ -7246,7 +7229,7 @@
         <v>26</v>
       </c>
       <c r="D166" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E166" s="12" t="s">
         <v>17</v>
@@ -7255,7 +7238,7 @@
         <v>28</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H166" s="8" t="s">
         <v>17</v>
@@ -7290,7 +7273,7 @@
         <v>26</v>
       </c>
       <c r="D167" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E167" s="12" t="s">
         <v>17</v>
@@ -7566,7 +7549,7 @@
         <v>66</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E174" s="8" t="s">
         <v>64</v>
@@ -7575,7 +7558,7 @@
         <v>28</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H174" s="8" t="s">
         <v>64</v>
@@ -7610,7 +7593,7 @@
         <v>66</v>
       </c>
       <c r="D175" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E175" s="8" t="s">
         <v>64</v>
@@ -7619,7 +7602,7 @@
         <v>28</v>
       </c>
       <c r="G175" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H175" s="8" t="s">
         <v>64</v>
@@ -7654,7 +7637,7 @@
         <v>65</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E176" s="8" t="s">
         <v>64</v>
@@ -7883,10 +7866,10 @@
         <v>27</v>
       </c>
       <c r="C182" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D182" s="8" t="s">
         <v>95</v>
-      </c>
-      <c r="D182" s="8" t="s">
-        <v>96</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>11</v>
@@ -7927,10 +7910,10 @@
         <v>26</v>
       </c>
       <c r="C183" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E183" s="6" t="s">
         <v>11</v>
@@ -7999,10 +7982,10 @@
         <v>27</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E185" s="6" t="s">
         <v>11</v>
@@ -8043,10 +8026,10 @@
         <v>26</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D186" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>11</v>
@@ -8109,7 +8092,7 @@
     </row>
     <row r="188" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B188" s="8" t="n">
         <v>5</v>
@@ -8118,7 +8101,7 @@
         <v>45</v>
       </c>
       <c r="D188" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E188" s="12" t="s">
         <v>46</v>
@@ -8127,7 +8110,7 @@
         <v>28</v>
       </c>
       <c r="G188" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H188" s="12" t="s">
         <v>46</v>
@@ -8153,7 +8136,7 @@
     </row>
     <row r="189" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B189" s="8" t="n">
         <v>19</v>
@@ -8162,7 +8145,7 @@
         <v>45</v>
       </c>
       <c r="D189" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E189" s="12" t="s">
         <v>46</v>
@@ -8171,7 +8154,7 @@
         <v>28</v>
       </c>
       <c r="G189" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H189" s="12" t="s">
         <v>46</v>
@@ -8205,7 +8188,7 @@
         <v>28</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H190" s="8"/>
       <c r="I190" s="8"/>
@@ -8229,7 +8212,7 @@
     </row>
     <row r="191" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B191" s="8" t="n">
         <v>5</v>
@@ -8238,7 +8221,7 @@
         <v>9</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E191" s="12" t="s">
         <v>17</v>
@@ -8247,7 +8230,7 @@
         <v>28</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H191" s="12" t="s">
         <v>17</v>
@@ -8273,7 +8256,7 @@
     </row>
     <row r="192" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B192" s="8" t="n">
         <v>19</v>
@@ -8282,7 +8265,7 @@
         <v>9</v>
       </c>
       <c r="D192" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E192" s="12" t="s">
         <v>17</v>
@@ -8291,7 +8274,7 @@
         <v>28</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H192" s="12" t="s">
         <v>17</v>
@@ -8317,13 +8300,13 @@
     </row>
     <row r="193" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B193" s="8" t="n">
         <v>5</v>
       </c>
       <c r="C193" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D193" s="12" t="s">
         <v>57</v>
@@ -8332,10 +8315,10 @@
         <v>17</v>
       </c>
       <c r="F193" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G193" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="G193" s="12" t="s">
-        <v>103</v>
       </c>
       <c r="H193" s="12" t="s">
         <v>17</v>
@@ -8361,13 +8344,13 @@
     </row>
     <row r="194" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B194" s="8" t="n">
         <v>19</v>
       </c>
       <c r="C194" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D194" s="12" t="s">
         <v>58</v>
@@ -8376,10 +8359,10 @@
         <v>17</v>
       </c>
       <c r="F194" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G194" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="G194" s="12" t="s">
-        <v>103</v>
       </c>
       <c r="H194" s="12" t="s">
         <v>17</v>
@@ -8433,28 +8416,28 @@
     </row>
     <row r="196" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B196" s="8" t="n">
         <v>10</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D196" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E196" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F196" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G196" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G196" s="12" t="s">
-        <v>103</v>
-      </c>
       <c r="H196" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I196" s="8"/>
       <c r="J196" s="8"/>
@@ -8477,28 +8460,28 @@
     </row>
     <row r="197" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B197" s="8" t="n">
         <v>11</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D197" s="8" t="s">
         <v>71</v>
       </c>
       <c r="E197" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F197" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G197" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G197" s="12" t="s">
-        <v>103</v>
-      </c>
       <c r="H197" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I197" s="8"/>
       <c r="J197" s="8"/>
@@ -8549,28 +8532,28 @@
     </row>
     <row r="199" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B199" s="8" t="n">
         <v>10</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D199" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E199" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F199" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G199" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G199" s="12" t="s">
-        <v>103</v>
-      </c>
       <c r="H199" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I199" s="8"/>
       <c r="J199" s="8"/>
@@ -8593,28 +8576,28 @@
     </row>
     <row r="200" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B200" s="8" t="n">
         <v>11</v>
       </c>
       <c r="C200" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D200" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E200" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F200" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G200" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G200" s="12" t="s">
-        <v>103</v>
-      </c>
       <c r="H200" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I200" s="8"/>
       <c r="J200" s="8"/>
@@ -8665,28 +8648,28 @@
     </row>
     <row r="202" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B202" s="8" t="n">
         <v>10</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D202" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E202" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F202" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G202" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G202" s="12" t="s">
-        <v>103</v>
-      </c>
       <c r="H202" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I202" s="8"/>
       <c r="J202" s="8"/>
@@ -8709,28 +8692,28 @@
     </row>
     <row r="203" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B203" s="8" t="n">
         <v>11</v>
       </c>
       <c r="C203" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D203" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E203" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F203" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G203" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G203" s="12" t="s">
-        <v>103</v>
-      </c>
       <c r="H203" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I203" s="8"/>
       <c r="J203" s="8"/>
@@ -8781,7 +8764,7 @@
     </row>
     <row r="205" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B205" s="8" t="n">
         <v>10</v>
@@ -8790,16 +8773,16 @@
         <v>49</v>
       </c>
       <c r="D205" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E205" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F205" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G205" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="G205" s="12" t="s">
-        <v>103</v>
       </c>
       <c r="H205" s="8" t="s">
         <v>48</v>
@@ -8825,7 +8808,7 @@
     </row>
     <row r="206" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B206" s="8" t="n">
         <v>11</v>
@@ -8834,16 +8817,16 @@
         <v>49</v>
       </c>
       <c r="D206" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E206" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F206" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G206" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="G206" s="12" t="s">
-        <v>103</v>
       </c>
       <c r="H206" s="8" t="s">
         <v>48</v>
@@ -8897,7 +8880,7 @@
     </row>
     <row r="208" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B208" s="8" t="n">
         <v>10</v>
@@ -8906,16 +8889,16 @@
         <v>43</v>
       </c>
       <c r="D208" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E208" s="8" t="s">
         <v>41</v>
       </c>
       <c r="F208" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G208" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="G208" s="12" t="s">
-        <v>103</v>
       </c>
       <c r="H208" s="8" t="s">
         <v>41</v>
@@ -8941,7 +8924,7 @@
     </row>
     <row r="209" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B209" s="8" t="n">
         <v>11</v>
@@ -8950,16 +8933,16 @@
         <v>43</v>
       </c>
       <c r="D209" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E209" s="8" t="s">
         <v>41</v>
       </c>
       <c r="F209" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G209" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="G209" s="12" t="s">
-        <v>103</v>
       </c>
       <c r="H209" s="8" t="s">
         <v>41</v>
@@ -9013,7 +8996,7 @@
     </row>
     <row r="211" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B211" s="8" t="n">
         <v>17</v>
@@ -9022,16 +9005,16 @@
         <v>50</v>
       </c>
       <c r="D211" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E211" s="8" t="s">
         <v>51</v>
       </c>
       <c r="F211" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G211" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="G211" s="12" t="s">
-        <v>103</v>
       </c>
       <c r="H211" s="8" t="s">
         <v>51</v>
@@ -9057,7 +9040,7 @@
     </row>
     <row r="212" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B212" s="8" t="n">
         <v>18</v>
@@ -9066,16 +9049,16 @@
         <v>50</v>
       </c>
       <c r="D212" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E212" s="8" t="s">
         <v>51</v>
       </c>
       <c r="F212" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G212" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="G212" s="12" t="s">
-        <v>103</v>
       </c>
       <c r="H212" s="8" t="s">
         <v>51</v>
@@ -9129,7 +9112,7 @@
     </row>
     <row r="214" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B214" s="8" t="n">
         <v>17</v>
@@ -9138,16 +9121,16 @@
         <v>26</v>
       </c>
       <c r="D214" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E214" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F214" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G214" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="G214" s="12" t="s">
-        <v>103</v>
       </c>
       <c r="H214" s="8" t="s">
         <v>17</v>
@@ -9173,7 +9156,7 @@
     </row>
     <row r="215" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B215" s="8" t="n">
         <v>18</v>
@@ -9182,16 +9165,16 @@
         <v>26</v>
       </c>
       <c r="D215" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E215" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F215" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G215" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="G215" s="12" t="s">
-        <v>103</v>
       </c>
       <c r="H215" s="8" t="s">
         <v>17</v>
@@ -9245,7 +9228,7 @@
     </row>
     <row r="217" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B217" s="8" t="n">
         <v>17</v>
@@ -9254,7 +9237,7 @@
         <v>22</v>
       </c>
       <c r="D217" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E217" s="8" t="s">
         <v>17</v>
@@ -9263,7 +9246,7 @@
         <v>42</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H217" s="8" t="s">
         <v>17</v>
@@ -9289,7 +9272,7 @@
     </row>
     <row r="218" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B218" s="8" t="n">
         <v>18</v>
@@ -9298,7 +9281,7 @@
         <v>22</v>
       </c>
       <c r="D218" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E218" s="8" t="s">
         <v>17</v>
@@ -9307,7 +9290,7 @@
         <v>42</v>
       </c>
       <c r="G218" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H218" s="8" t="s">
         <v>17</v>
@@ -9361,7 +9344,7 @@
     </row>
     <row r="220" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B220" s="8" t="n">
         <v>17</v>
@@ -9370,7 +9353,7 @@
         <v>54</v>
       </c>
       <c r="D220" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E220" s="8" t="s">
         <v>53</v>
@@ -9379,7 +9362,7 @@
         <v>28</v>
       </c>
       <c r="G220" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H220" s="8" t="s">
         <v>53</v>
@@ -9405,7 +9388,7 @@
     </row>
     <row r="221" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B221" s="8" t="n">
         <v>18</v>
@@ -9414,7 +9397,7 @@
         <v>54</v>
       </c>
       <c r="D221" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E221" s="8" t="s">
         <v>53</v>
@@ -9423,7 +9406,7 @@
         <v>28</v>
       </c>
       <c r="G221" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H221" s="8" t="s">
         <v>53</v>
@@ -9477,7 +9460,7 @@
     </row>
     <row r="223" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B223" s="8" t="n">
         <v>17</v>
@@ -9486,16 +9469,16 @@
         <v>66</v>
       </c>
       <c r="D223" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E223" s="8" t="s">
         <v>64</v>
       </c>
       <c r="F223" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G223" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="G223" s="12" t="s">
-        <v>103</v>
       </c>
       <c r="H223" s="8" t="s">
         <v>64</v>
@@ -9521,7 +9504,7 @@
     </row>
     <row r="224" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B224" s="8" t="n">
         <v>18</v>
@@ -9530,16 +9513,16 @@
         <v>66</v>
       </c>
       <c r="D224" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E224" s="8" t="s">
         <v>64</v>
       </c>
       <c r="F224" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G224" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="G224" s="12" t="s">
-        <v>103</v>
       </c>
       <c r="H224" s="8" t="s">
         <v>64</v>
@@ -9565,7 +9548,7 @@
     </row>
     <row r="225" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B225" s="8" t="n">
         <v>17</v>
@@ -9574,7 +9557,7 @@
         <v>65</v>
       </c>
       <c r="D225" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E225" s="12" t="s">
         <v>64</v>
@@ -9583,7 +9566,7 @@
         <v>42</v>
       </c>
       <c r="G225" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H225" s="12" t="s">
         <v>64</v>
@@ -9609,7 +9592,7 @@
     </row>
     <row r="226" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B226" s="8" t="n">
         <v>18</v>
@@ -9618,7 +9601,7 @@
         <v>65</v>
       </c>
       <c r="D226" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E226" s="12" t="s">
         <v>64</v>
@@ -9627,7 +9610,7 @@
         <v>42</v>
       </c>
       <c r="G226" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H226" s="12" t="s">
         <v>64</v>
@@ -9681,7 +9664,7 @@
     </row>
     <row r="228" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B228" s="8" t="n">
         <v>17</v>
@@ -9690,7 +9673,7 @@
         <v>61</v>
       </c>
       <c r="D228" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E228" s="12" t="s">
         <v>60</v>
@@ -9699,7 +9682,7 @@
         <v>42</v>
       </c>
       <c r="G228" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H228" s="12" t="s">
         <v>60</v>
@@ -9725,7 +9708,7 @@
     </row>
     <row r="229" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B229" s="8" t="n">
         <v>18</v>
@@ -9734,7 +9717,7 @@
         <v>61</v>
       </c>
       <c r="D229" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E229" s="12" t="s">
         <v>60</v>
@@ -9743,7 +9726,7 @@
         <v>42</v>
       </c>
       <c r="G229" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H229" s="12" t="s">
         <v>60</v>
@@ -9797,25 +9780,25 @@
     </row>
     <row r="231" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B231" s="8" t="n">
         <v>31</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D231" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E231" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F231" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G231" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="G231" s="12" t="s">
-        <v>103</v>
       </c>
       <c r="H231" s="8" t="s">
         <v>60</v>
@@ -9841,25 +9824,25 @@
     </row>
     <row r="232" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B232" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C232" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D232" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E232" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F232" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G232" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="G232" s="12" t="s">
-        <v>103</v>
       </c>
       <c r="H232" s="8" t="s">
         <v>60</v>
@@ -9913,25 +9896,25 @@
     </row>
     <row r="234" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B234" s="8" t="n">
         <v>31</v>
       </c>
       <c r="C234" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D234" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E234" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F234" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G234" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="G234" s="12" t="s">
-        <v>103</v>
       </c>
       <c r="H234" s="8" t="s">
         <v>53</v>
@@ -9957,25 +9940,25 @@
     </row>
     <row r="235" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B235" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C235" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D235" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E235" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F235" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G235" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="G235" s="12" t="s">
-        <v>103</v>
       </c>
       <c r="H235" s="8" t="s">
         <v>53</v>
@@ -10029,7 +10012,7 @@
     </row>
     <row r="237" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B237" s="8" t="n">
         <v>2</v>
@@ -10038,16 +10021,16 @@
         <v>45</v>
       </c>
       <c r="D237" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E237" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F237" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G237" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="G237" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="H237" s="8" t="s">
         <v>46</v>
@@ -10073,7 +10056,7 @@
     </row>
     <row r="238" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B238" s="8" t="n">
         <v>16</v>
@@ -10082,16 +10065,16 @@
         <v>45</v>
       </c>
       <c r="D238" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E238" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F238" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G238" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="G238" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="H238" s="8" t="s">
         <v>46</v>
@@ -10145,7 +10128,7 @@
     </row>
     <row r="240" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B240" s="8" t="n">
         <v>2</v>
@@ -10154,16 +10137,16 @@
         <v>9</v>
       </c>
       <c r="D240" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E240" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F240" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G240" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="G240" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="H240" s="8" t="s">
         <v>17</v>
@@ -10189,7 +10172,7 @@
     </row>
     <row r="241" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B241" s="8" t="n">
         <v>16</v>
@@ -10198,16 +10181,16 @@
         <v>9</v>
       </c>
       <c r="D241" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E241" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F241" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G241" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="G241" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="H241" s="8" t="s">
         <v>17</v>
@@ -10233,16 +10216,16 @@
     </row>
     <row r="242" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B242" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C242" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D242" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E242" s="8" t="s">
         <v>17</v>
@@ -10251,7 +10234,7 @@
         <v>42</v>
       </c>
       <c r="G242" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H242" s="8" t="s">
         <v>17</v>
@@ -10277,16 +10260,16 @@
     </row>
     <row r="243" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B243" s="8" t="n">
         <v>16</v>
       </c>
       <c r="C243" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D243" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E243" s="8" t="s">
         <v>17</v>
@@ -10295,7 +10278,7 @@
         <v>42</v>
       </c>
       <c r="G243" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H243" s="8" t="s">
         <v>17</v>
@@ -10349,28 +10332,28 @@
     </row>
     <row r="245" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B245" s="8" t="n">
         <v>7</v>
       </c>
       <c r="C245" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D245" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E245" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F245" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G245" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="G245" s="8" t="s">
-        <v>113</v>
-      </c>
       <c r="H245" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I245" s="8"/>
       <c r="J245" s="8"/>
@@ -10393,28 +10376,28 @@
     </row>
     <row r="246" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B246" s="8" t="n">
         <v>8</v>
       </c>
       <c r="C246" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D246" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E246" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F246" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G246" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="G246" s="8" t="s">
-        <v>113</v>
-      </c>
       <c r="H246" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I246" s="8"/>
       <c r="J246" s="8"/>
@@ -10465,28 +10448,28 @@
     </row>
     <row r="248" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B248" s="8" t="n">
         <v>7</v>
       </c>
       <c r="C248" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D248" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E248" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F248" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G248" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="G248" s="8" t="s">
-        <v>113</v>
-      </c>
       <c r="H248" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I248" s="8"/>
       <c r="J248" s="8"/>
@@ -10509,28 +10492,28 @@
     </row>
     <row r="249" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B249" s="8" t="n">
         <v>8</v>
       </c>
       <c r="C249" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D249" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E249" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F249" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G249" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="G249" s="8" t="s">
-        <v>113</v>
-      </c>
       <c r="H249" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I249" s="8"/>
       <c r="J249" s="8"/>
@@ -10581,28 +10564,28 @@
     </row>
     <row r="251" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B251" s="8" t="n">
         <v>7</v>
       </c>
       <c r="C251" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D251" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E251" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F251" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G251" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="G251" s="8" t="s">
-        <v>113</v>
-      </c>
       <c r="H251" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I251" s="8"/>
       <c r="J251" s="8"/>
@@ -10625,28 +10608,28 @@
     </row>
     <row r="252" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B252" s="8" t="n">
         <v>8</v>
       </c>
       <c r="C252" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D252" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E252" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F252" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G252" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="G252" s="8" t="s">
-        <v>113</v>
-      </c>
       <c r="H252" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I252" s="8"/>
       <c r="J252" s="8"/>
@@ -10697,7 +10680,7 @@
     </row>
     <row r="254" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B254" s="8" t="n">
         <v>14</v>
@@ -10706,16 +10689,16 @@
         <v>49</v>
       </c>
       <c r="D254" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E254" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F254" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G254" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="G254" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="H254" s="8" t="s">
         <v>48</v>
@@ -10741,7 +10724,7 @@
     </row>
     <row r="255" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B255" s="8" t="n">
         <v>15</v>
@@ -10750,16 +10733,16 @@
         <v>49</v>
       </c>
       <c r="D255" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E255" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F255" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G255" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="G255" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="H255" s="8" t="s">
         <v>48</v>
@@ -10813,7 +10796,7 @@
     </row>
     <row r="257" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B257" s="8" t="n">
         <v>14</v>
@@ -10822,16 +10805,16 @@
         <v>43</v>
       </c>
       <c r="D257" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E257" s="8" t="s">
         <v>41</v>
       </c>
       <c r="F257" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G257" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="G257" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="H257" s="8" t="s">
         <v>41</v>
@@ -10857,7 +10840,7 @@
     </row>
     <row r="258" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B258" s="8" t="n">
         <v>15</v>
@@ -10866,16 +10849,16 @@
         <v>43</v>
       </c>
       <c r="D258" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E258" s="8" t="s">
         <v>41</v>
       </c>
       <c r="F258" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G258" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="G258" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="H258" s="8" t="s">
         <v>41</v>
@@ -10929,7 +10912,7 @@
     </row>
     <row r="260" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B260" s="8" t="n">
         <v>21</v>
@@ -10938,16 +10921,16 @@
         <v>50</v>
       </c>
       <c r="D260" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E260" s="8" t="s">
         <v>51</v>
       </c>
       <c r="F260" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G260" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="G260" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="H260" s="8" t="s">
         <v>51</v>
@@ -10973,7 +10956,7 @@
     </row>
     <row r="261" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B261" s="8" t="n">
         <v>22</v>
@@ -10982,16 +10965,16 @@
         <v>50</v>
       </c>
       <c r="D261" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E261" s="8" t="s">
         <v>51</v>
       </c>
       <c r="F261" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G261" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="G261" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="H261" s="8" t="s">
         <v>51</v>
@@ -11045,7 +11028,7 @@
     </row>
     <row r="263" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B263" s="8" t="n">
         <v>21</v>
@@ -11054,16 +11037,16 @@
         <v>26</v>
       </c>
       <c r="D263" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E263" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F263" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G263" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="G263" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="H263" s="8" t="s">
         <v>17</v>
@@ -11089,7 +11072,7 @@
     </row>
     <row r="264" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B264" s="8" t="n">
         <v>22</v>
@@ -11098,16 +11081,16 @@
         <v>26</v>
       </c>
       <c r="D264" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E264" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F264" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G264" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="G264" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="H264" s="8" t="s">
         <v>17</v>
@@ -11161,7 +11144,7 @@
     </row>
     <row r="266" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B266" s="8" t="n">
         <v>21</v>
@@ -11170,7 +11153,7 @@
         <v>22</v>
       </c>
       <c r="D266" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E266" s="8" t="s">
         <v>17</v>
@@ -11179,7 +11162,7 @@
         <v>42</v>
       </c>
       <c r="G266" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H266" s="8" t="s">
         <v>17</v>
@@ -11205,7 +11188,7 @@
     </row>
     <row r="267" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B267" s="8" t="n">
         <v>22</v>
@@ -11214,7 +11197,7 @@
         <v>22</v>
       </c>
       <c r="D267" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E267" s="8" t="s">
         <v>17</v>
@@ -11223,7 +11206,7 @@
         <v>42</v>
       </c>
       <c r="G267" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H267" s="8" t="s">
         <v>17</v>
@@ -11277,7 +11260,7 @@
     </row>
     <row r="269" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B269" s="8" t="n">
         <v>28</v>
@@ -11286,7 +11269,7 @@
         <v>54</v>
       </c>
       <c r="D269" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E269" s="8" t="s">
         <v>53</v>
@@ -11295,7 +11278,7 @@
         <v>42</v>
       </c>
       <c r="G269" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H269" s="8" t="s">
         <v>53</v>
@@ -11321,7 +11304,7 @@
     </row>
     <row r="270" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B270" s="8" t="n">
         <v>29</v>
@@ -11330,7 +11313,7 @@
         <v>54</v>
       </c>
       <c r="D270" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E270" s="8" t="s">
         <v>53</v>
@@ -11339,7 +11322,7 @@
         <v>42</v>
       </c>
       <c r="G270" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H270" s="8" t="s">
         <v>53</v>
@@ -11393,7 +11376,7 @@
     </row>
     <row r="272" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B272" s="8" t="n">
         <v>28</v>
@@ -11402,16 +11385,16 @@
         <v>66</v>
       </c>
       <c r="D272" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E272" s="8" t="s">
         <v>64</v>
       </c>
       <c r="F272" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G272" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="G272" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="H272" s="8" t="s">
         <v>64</v>
@@ -11437,7 +11420,7 @@
     </row>
     <row r="273" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B273" s="8" t="n">
         <v>29</v>
@@ -11446,16 +11429,16 @@
         <v>66</v>
       </c>
       <c r="D273" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E273" s="8" t="s">
         <v>64</v>
       </c>
       <c r="F273" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G273" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="G273" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="H273" s="8" t="s">
         <v>64</v>
@@ -11481,7 +11464,7 @@
     </row>
     <row r="274" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B274" s="8" t="n">
         <v>28</v>
@@ -11490,7 +11473,7 @@
         <v>65</v>
       </c>
       <c r="D274" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E274" s="8" t="s">
         <v>64</v>
@@ -11499,7 +11482,7 @@
         <v>42</v>
       </c>
       <c r="G274" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H274" s="8" t="s">
         <v>64</v>
@@ -11525,7 +11508,7 @@
     </row>
     <row r="275" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B275" s="8" t="n">
         <v>29</v>
@@ -11534,7 +11517,7 @@
         <v>65</v>
       </c>
       <c r="D275" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E275" s="8" t="s">
         <v>64</v>
@@ -11543,7 +11526,7 @@
         <v>42</v>
       </c>
       <c r="G275" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H275" s="8" t="s">
         <v>64</v>
@@ -11597,7 +11580,7 @@
     </row>
     <row r="277" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B277" s="8" t="n">
         <v>28</v>
@@ -11606,7 +11589,7 @@
         <v>61</v>
       </c>
       <c r="D277" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E277" s="8" t="s">
         <v>60</v>
@@ -11615,7 +11598,7 @@
         <v>42</v>
       </c>
       <c r="G277" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H277" s="8" t="s">
         <v>60</v>
@@ -11641,7 +11624,7 @@
     </row>
     <row r="278" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B278" s="8" t="n">
         <v>29</v>
@@ -11650,7 +11633,7 @@
         <v>61</v>
       </c>
       <c r="D278" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E278" s="8" t="s">
         <v>60</v>
@@ -11659,7 +11642,7 @@
         <v>42</v>
       </c>
       <c r="G278" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H278" s="8" t="s">
         <v>60</v>
@@ -11713,25 +11696,25 @@
     </row>
     <row r="280" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B280" s="8" t="n">
         <v>28</v>
       </c>
       <c r="C280" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D280" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E280" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F280" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G280" s="12" t="s">
         <v>112</v>
-      </c>
-      <c r="G280" s="12" t="s">
-        <v>113</v>
       </c>
       <c r="H280" s="8" t="s">
         <v>60</v>
@@ -11757,25 +11740,25 @@
     </row>
     <row r="281" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B281" s="8" t="n">
         <v>29</v>
       </c>
       <c r="C281" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D281" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E281" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F281" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G281" s="12" t="s">
         <v>112</v>
-      </c>
-      <c r="G281" s="12" t="s">
-        <v>113</v>
       </c>
       <c r="H281" s="8" t="s">
         <v>60</v>
@@ -11829,25 +11812,25 @@
     </row>
     <row r="283" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B283" s="8" t="n">
         <v>28</v>
       </c>
       <c r="C283" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D283" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E283" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F283" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G283" s="12" t="s">
         <v>112</v>
-      </c>
-      <c r="G283" s="12" t="s">
-        <v>113</v>
       </c>
       <c r="H283" s="8" t="s">
         <v>53</v>
@@ -11873,25 +11856,25 @@
     </row>
     <row r="284" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B284" s="8" t="n">
         <v>29</v>
       </c>
       <c r="C284" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D284" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E284" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F284" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G284" s="12" t="s">
         <v>112</v>
-      </c>
-      <c r="G284" s="12" t="s">
-        <v>113</v>
       </c>
       <c r="H284" s="8" t="s">
         <v>53</v>
@@ -11973,7 +11956,7 @@
     </row>
     <row r="287" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B287" s="12" t="n">
         <v>7</v>
@@ -11982,16 +11965,16 @@
         <v>45</v>
       </c>
       <c r="D287" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E287" s="12" t="s">
         <v>46</v>
       </c>
       <c r="F287" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G287" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="G287" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="H287" s="12" t="s">
         <v>46</v>
@@ -12017,7 +12000,7 @@
     </row>
     <row r="288" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B288" s="12" t="n">
         <v>14</v>
@@ -12026,16 +12009,16 @@
         <v>45</v>
       </c>
       <c r="D288" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E288" s="12" t="s">
         <v>46</v>
       </c>
       <c r="F288" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G288" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="G288" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="H288" s="12" t="s">
         <v>46</v>
@@ -12089,7 +12072,7 @@
     </row>
     <row r="290" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B290" s="12" t="n">
         <v>7</v>
@@ -12098,16 +12081,16 @@
         <v>9</v>
       </c>
       <c r="D290" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E290" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F290" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G290" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="G290" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="H290" s="12" t="s">
         <v>17</v>
@@ -12133,7 +12116,7 @@
     </row>
     <row r="291" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B291" s="12" t="n">
         <v>14</v>
@@ -12142,16 +12125,16 @@
         <v>9</v>
       </c>
       <c r="D291" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E291" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F291" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G291" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="G291" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="H291" s="12" t="s">
         <v>17</v>
@@ -12177,16 +12160,16 @@
     </row>
     <row r="292" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B292" s="12" t="n">
         <v>7</v>
       </c>
       <c r="C292" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D292" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E292" s="12" t="s">
         <v>17</v>
@@ -12195,7 +12178,7 @@
         <v>42</v>
       </c>
       <c r="G292" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H292" s="12" t="s">
         <v>17</v>
@@ -12221,16 +12204,16 @@
     </row>
     <row r="293" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B293" s="12" t="n">
         <v>14</v>
       </c>
       <c r="C293" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D293" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E293" s="12" t="s">
         <v>17</v>
@@ -12239,7 +12222,7 @@
         <v>42</v>
       </c>
       <c r="G293" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H293" s="12" t="s">
         <v>17</v>
@@ -12293,28 +12276,28 @@
     </row>
     <row r="295" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B295" s="8" t="n">
         <v>5</v>
       </c>
       <c r="C295" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D295" s="12" t="s">
         <v>32</v>
       </c>
       <c r="E295" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F295" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G295" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="G295" s="12" t="s">
-        <v>118</v>
-      </c>
       <c r="H295" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I295" s="8"/>
       <c r="J295" s="8"/>
@@ -12337,28 +12320,28 @@
     </row>
     <row r="296" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B296" s="8" t="n">
         <v>6</v>
       </c>
       <c r="C296" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D296" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E296" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F296" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G296" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="G296" s="12" t="s">
-        <v>118</v>
-      </c>
       <c r="H296" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I296" s="8"/>
       <c r="J296" s="8"/>
@@ -12409,28 +12392,28 @@
     </row>
     <row r="298" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B298" s="8" t="n">
         <v>5</v>
       </c>
       <c r="C298" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D298" s="12" t="s">
         <v>20</v>
       </c>
       <c r="E298" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F298" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G298" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="G298" s="12" t="s">
-        <v>118</v>
-      </c>
       <c r="H298" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I298" s="8"/>
       <c r="J298" s="8"/>
@@ -12453,28 +12436,28 @@
     </row>
     <row r="299" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B299" s="8" t="n">
         <v>6</v>
       </c>
       <c r="C299" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D299" s="12" t="s">
         <v>25</v>
       </c>
       <c r="E299" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F299" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G299" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="G299" s="12" t="s">
-        <v>118</v>
-      </c>
       <c r="H299" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I299" s="8"/>
       <c r="J299" s="8"/>
@@ -12525,28 +12508,28 @@
     </row>
     <row r="301" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B301" s="8" t="n">
         <v>5</v>
       </c>
       <c r="C301" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D301" s="12" t="s">
         <v>32</v>
       </c>
       <c r="E301" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F301" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G301" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="G301" s="12" t="s">
-        <v>118</v>
-      </c>
       <c r="H301" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I301" s="8"/>
       <c r="J301" s="8"/>
@@ -12569,28 +12552,28 @@
     </row>
     <row r="302" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B302" s="8" t="n">
         <v>6</v>
       </c>
       <c r="C302" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D302" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E302" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F302" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G302" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="G302" s="12" t="s">
-        <v>118</v>
-      </c>
       <c r="H302" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I302" s="8"/>
       <c r="J302" s="8"/>
@@ -12641,7 +12624,7 @@
     </row>
     <row r="304" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B304" s="8" t="n">
         <v>5</v>
@@ -12656,10 +12639,10 @@
         <v>51</v>
       </c>
       <c r="F304" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G304" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="G304" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="H304" s="8" t="s">
         <v>51</v>
@@ -12685,7 +12668,7 @@
     </row>
     <row r="305" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B305" s="8" t="n">
         <v>6</v>
@@ -12700,10 +12683,10 @@
         <v>51</v>
       </c>
       <c r="F305" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G305" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="G305" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="H305" s="8" t="s">
         <v>51</v>
@@ -12757,7 +12740,7 @@
     </row>
     <row r="307" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B307" s="8" t="n">
         <v>5</v>
@@ -12772,10 +12755,10 @@
         <v>17</v>
       </c>
       <c r="F307" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G307" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="G307" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="H307" s="12" t="s">
         <v>17</v>
@@ -12801,7 +12784,7 @@
     </row>
     <row r="308" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B308" s="8" t="n">
         <v>6</v>
@@ -12816,10 +12799,10 @@
         <v>17</v>
       </c>
       <c r="F308" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G308" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="G308" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="H308" s="12" t="s">
         <v>17</v>
@@ -12845,7 +12828,7 @@
     </row>
     <row r="309" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B309" s="8" t="n">
         <v>5</v>
@@ -12854,7 +12837,7 @@
         <v>22</v>
       </c>
       <c r="D309" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E309" s="12" t="s">
         <v>17</v>
@@ -12863,7 +12846,7 @@
         <v>42</v>
       </c>
       <c r="G309" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H309" s="12" t="s">
         <v>17</v>
@@ -12889,7 +12872,7 @@
     </row>
     <row r="310" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B310" s="8" t="n">
         <v>6</v>
@@ -12898,7 +12881,7 @@
         <v>22</v>
       </c>
       <c r="D310" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E310" s="12" t="s">
         <v>17</v>
@@ -12907,7 +12890,7 @@
         <v>42</v>
       </c>
       <c r="G310" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H310" s="12" t="s">
         <v>17</v>
@@ -12961,7 +12944,7 @@
     </row>
     <row r="312" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B312" s="8" t="n">
         <v>12</v>
@@ -12976,10 +12959,10 @@
         <v>48</v>
       </c>
       <c r="F312" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G312" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="G312" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="H312" s="12" t="s">
         <v>48</v>
@@ -13005,7 +12988,7 @@
     </row>
     <row r="313" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B313" s="8" t="n">
         <v>13</v>
@@ -13020,10 +13003,10 @@
         <v>48</v>
       </c>
       <c r="F313" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G313" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="G313" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="H313" s="12" t="s">
         <v>48</v>
@@ -13077,7 +13060,7 @@
     </row>
     <row r="315" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B315" s="8" t="n">
         <v>12</v>
@@ -13092,10 +13075,10 @@
         <v>41</v>
       </c>
       <c r="F315" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G315" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="G315" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="H315" s="8" t="s">
         <v>41</v>
@@ -13121,7 +13104,7 @@
     </row>
     <row r="316" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B316" s="8" t="n">
         <v>13</v>
@@ -13136,10 +13119,10 @@
         <v>41</v>
       </c>
       <c r="F316" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G316" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="G316" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="H316" s="8" t="s">
         <v>41</v>
@@ -13193,7 +13176,7 @@
     </row>
     <row r="318" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B318" s="8" t="n">
         <v>12</v>
@@ -13202,7 +13185,7 @@
         <v>54</v>
       </c>
       <c r="D318" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E318" s="12" t="s">
         <v>53</v>
@@ -13211,7 +13194,7 @@
         <v>42</v>
       </c>
       <c r="G318" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H318" s="12" t="s">
         <v>53</v>
@@ -13237,7 +13220,7 @@
     </row>
     <row r="319" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B319" s="8" t="n">
         <v>13</v>
@@ -13246,7 +13229,7 @@
         <v>54</v>
       </c>
       <c r="D319" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E319" s="12" t="s">
         <v>53</v>
@@ -13255,7 +13238,7 @@
         <v>42</v>
       </c>
       <c r="G319" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H319" s="12" t="s">
         <v>53</v>
@@ -13309,7 +13292,7 @@
     </row>
     <row r="321" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B321" s="8" t="n">
         <v>12</v>
@@ -13324,10 +13307,10 @@
         <v>64</v>
       </c>
       <c r="F321" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G321" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="G321" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="H321" s="8" t="s">
         <v>64</v>
@@ -13353,7 +13336,7 @@
     </row>
     <row r="322" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B322" s="8" t="n">
         <v>13</v>
@@ -13368,10 +13351,10 @@
         <v>64</v>
       </c>
       <c r="F322" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G322" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="G322" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="H322" s="8" t="s">
         <v>64</v>
@@ -13397,7 +13380,7 @@
     </row>
     <row r="323" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B323" s="8" t="n">
         <v>12</v>
@@ -13406,7 +13389,7 @@
         <v>65</v>
       </c>
       <c r="D323" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E323" s="8" t="s">
         <v>64</v>
@@ -13415,7 +13398,7 @@
         <v>42</v>
       </c>
       <c r="G323" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H323" s="8" t="s">
         <v>64</v>
@@ -13441,7 +13424,7 @@
     </row>
     <row r="324" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B324" s="8" t="n">
         <v>13</v>
@@ -13450,7 +13433,7 @@
         <v>65</v>
       </c>
       <c r="D324" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E324" s="8" t="s">
         <v>64</v>
@@ -13459,7 +13442,7 @@
         <v>42</v>
       </c>
       <c r="G324" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H324" s="8" t="s">
         <v>64</v>
@@ -13513,7 +13496,7 @@
     </row>
     <row r="326" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B326" s="8" t="n">
         <v>12</v>
@@ -13522,7 +13505,7 @@
         <v>61</v>
       </c>
       <c r="D326" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E326" s="8" t="s">
         <v>60</v>
@@ -13531,7 +13514,7 @@
         <v>42</v>
       </c>
       <c r="G326" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H326" s="8" t="s">
         <v>60</v>
@@ -13557,7 +13540,7 @@
     </row>
     <row r="327" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B327" s="8" t="n">
         <v>13</v>
@@ -13566,7 +13549,7 @@
         <v>61</v>
       </c>
       <c r="D327" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E327" s="8" t="s">
         <v>60</v>
@@ -13575,7 +13558,7 @@
         <v>42</v>
       </c>
       <c r="G327" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H327" s="8" t="s">
         <v>60</v>
@@ -13629,25 +13612,25 @@
     </row>
     <row r="329" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B329" s="12" t="n">
         <v>12</v>
       </c>
       <c r="C329" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D329" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E329" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F329" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G329" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="G329" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="H329" s="8" t="s">
         <v>60</v>
@@ -13673,25 +13656,25 @@
     </row>
     <row r="330" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B330" s="12" t="n">
         <v>13</v>
       </c>
       <c r="C330" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D330" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E330" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F330" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G330" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="G330" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="H330" s="8" t="s">
         <v>60</v>
@@ -13745,25 +13728,25 @@
     </row>
     <row r="332" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B332" s="12" t="n">
         <v>12</v>
       </c>
       <c r="C332" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D332" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E332" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F332" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G332" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="G332" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="H332" s="8" t="s">
         <v>53</v>
@@ -13789,25 +13772,25 @@
     </row>
     <row r="333" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B333" s="12" t="n">
         <v>13</v>
       </c>
       <c r="C333" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D333" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E333" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F333" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G333" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="G333" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="H333" s="8" t="s">
         <v>53</v>

--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="125">
   <si>
     <t>MÊS</t>
   </si>
@@ -223,12 +223,6 @@
     <t>16/10/2026 a 20/10/2026</t>
   </si>
   <si>
-    <t>Procedimentos Intradérmicos e Intramusculares - Prática I</t>
-  </si>
-  <si>
-    <t>Avaliação após término da disciplina</t>
-  </si>
-  <si>
     <t>PROINSU BA 220225</t>
   </si>
   <si>
@@ -395,6 +389,9 @@
   </si>
   <si>
     <t>PROINSU  SP 2a.f 010925</t>
+  </si>
+  <si>
+    <t>Procedimentos Intradérmicos e Intramusculares - Prática I</t>
   </si>
   <si>
     <t xml:space="preserve">Procedimentos Intradérmicos e Intramusculares - Prática ll </t>
@@ -5034,28 +5031,14 @@
       <c r="Z106" s="9"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B107" s="6">
-        <v>27.0</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E107" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F107" s="8" t="s">
-        <v>71</v>
-      </c>
+      <c r="A107" s="5"/>
+      <c r="B107" s="6"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="7"/>
+      <c r="E107" s="6"/>
+      <c r="F107" s="8"/>
       <c r="G107" s="8"/>
-      <c r="H107" s="6" t="s">
-        <v>64</v>
-      </c>
+      <c r="H107" s="6"/>
       <c r="I107" s="8"/>
       <c r="J107" s="8"/>
       <c r="K107" s="8"/>
@@ -5155,22 +5138,22 @@
         <v>4.0</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D110" s="7" t="s">
         <v>31</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I110" s="8"/>
       <c r="J110" s="8"/>
@@ -5199,7 +5182,7 @@
         <v>25.0</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D111" s="7" t="s">
         <v>56</v>
@@ -5211,10 +5194,10 @@
         <v>42</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I111" s="8"/>
       <c r="J111" s="8"/>
@@ -5243,7 +5226,7 @@
         <v>26.0</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D112" s="7" t="s">
         <v>29</v>
@@ -5255,10 +5238,10 @@
         <v>28</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I112" s="8"/>
       <c r="J112" s="8"/>
@@ -5287,13 +5270,13 @@
         <v>1.0</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D113" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F113" s="6" t="s">
         <v>44</v>
@@ -5302,7 +5285,7 @@
         <v>35</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I113" s="8"/>
       <c r="J113" s="8"/>
@@ -5331,13 +5314,13 @@
         <v>2.0</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D114" s="7" t="s">
         <v>37</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>44</v>
@@ -5346,7 +5329,7 @@
         <v>35</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I114" s="8"/>
       <c r="J114" s="8"/>
@@ -5459,22 +5442,22 @@
         <v>4.0</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D118" s="7" t="s">
         <v>16</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I118" s="8"/>
       <c r="J118" s="8"/>
@@ -5503,7 +5486,7 @@
         <v>25.0</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D119" s="7" t="s">
         <v>56</v>
@@ -5515,10 +5498,10 @@
         <v>28</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I119" s="8"/>
       <c r="J119" s="8"/>
@@ -5547,7 +5530,7 @@
         <v>26.0</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D120" s="7" t="s">
         <v>29</v>
@@ -5559,10 +5542,10 @@
         <v>28</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I120" s="8"/>
       <c r="J120" s="8"/>
@@ -5591,13 +5574,13 @@
         <v>1.0</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D121" s="7" t="s">
         <v>37</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F121" s="6" t="s">
         <v>44</v>
@@ -5606,7 +5589,7 @@
         <v>35</v>
       </c>
       <c r="H121" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I121" s="8"/>
       <c r="J121" s="8"/>
@@ -5635,13 +5618,13 @@
         <v>2.0</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D122" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>44</v>
@@ -5650,7 +5633,7 @@
         <v>35</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I122" s="8"/>
       <c r="J122" s="8"/>
@@ -5763,7 +5746,7 @@
         <v>25.0</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D126" s="7" t="s">
         <v>56</v>
@@ -5778,7 +5761,7 @@
         <v>35</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I126" s="8"/>
       <c r="J126" s="8"/>
@@ -5807,7 +5790,7 @@
         <v>26.0</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D127" s="7" t="s">
         <v>29</v>
@@ -5822,7 +5805,7 @@
         <v>35</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I127" s="8"/>
       <c r="J127" s="8"/>
@@ -5851,13 +5834,13 @@
         <v>1.0</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D128" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>44</v>
@@ -5866,7 +5849,7 @@
         <v>35</v>
       </c>
       <c r="H128" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I128" s="8"/>
       <c r="J128" s="8"/>
@@ -5895,13 +5878,13 @@
         <v>2.0</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D129" s="7" t="s">
         <v>37</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F129" s="6" t="s">
         <v>44</v>
@@ -5910,7 +5893,7 @@
         <v>35</v>
       </c>
       <c r="H129" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I129" s="8"/>
       <c r="J129" s="8"/>
@@ -6023,10 +6006,10 @@
         <v>22.0</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E133" s="6" t="s">
         <v>11</v>
@@ -6067,10 +6050,10 @@
         <v>23.0</v>
       </c>
       <c r="C134" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D134" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>11</v>
@@ -6139,10 +6122,10 @@
         <v>22.0</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>11</v>
@@ -6183,10 +6166,10 @@
         <v>23.0</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E137" s="6" t="s">
         <v>11</v>
@@ -6249,7 +6232,7 @@
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B139" s="12">
         <v>7.0</v>
@@ -6293,7 +6276,7 @@
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B140" s="12">
         <v>21.0</v>
@@ -6365,7 +6348,7 @@
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B142" s="12">
         <v>7.0</v>
@@ -6409,7 +6392,7 @@
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B143" s="12">
         <v>21.0</v>
@@ -6453,13 +6436,13 @@
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B144" s="12">
         <v>7.0</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D144" s="12" t="s">
         <v>36</v>
@@ -6497,13 +6480,13 @@
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B145" s="12">
         <v>21.0</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D145" s="12" t="s">
         <v>38</v>
@@ -6569,19 +6552,19 @@
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B147" s="8">
         <v>5.0</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F147" s="13" t="s">
         <v>68</v>
@@ -6590,7 +6573,7 @@
         <v>69</v>
       </c>
       <c r="H147" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I147" s="8"/>
       <c r="J147" s="8"/>
@@ -6613,19 +6596,19 @@
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B148" s="8">
         <v>6.0</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F148" s="13" t="s">
         <v>68</v>
@@ -6634,7 +6617,7 @@
         <v>69</v>
       </c>
       <c r="H148" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I148" s="8"/>
       <c r="J148" s="8"/>
@@ -6685,28 +6668,28 @@
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B150" s="8">
         <v>5.0</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G150" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H150" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I150" s="8"/>
       <c r="J150" s="8"/>
@@ -6729,28 +6712,28 @@
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B151" s="8">
         <v>6.0</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H151" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I151" s="8"/>
       <c r="J151" s="8"/>
@@ -6801,19 +6784,19 @@
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B153" s="8">
         <v>5.0</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F153" s="13" t="s">
         <v>68</v>
@@ -6822,7 +6805,7 @@
         <v>69</v>
       </c>
       <c r="H153" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I153" s="8"/>
       <c r="J153" s="8"/>
@@ -6845,19 +6828,19 @@
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B154" s="8">
         <v>6.0</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F154" s="13" t="s">
         <v>68</v>
@@ -6866,7 +6849,7 @@
         <v>69</v>
       </c>
       <c r="H154" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I154" s="8"/>
       <c r="J154" s="8"/>
@@ -6917,7 +6900,7 @@
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B156" s="8">
         <v>12.0</v>
@@ -6926,7 +6909,7 @@
         <v>49</v>
       </c>
       <c r="D156" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E156" s="8" t="s">
         <v>48</v>
@@ -6961,7 +6944,7 @@
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B157" s="8">
         <v>13.0</v>
@@ -6970,7 +6953,7 @@
         <v>49</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E157" s="8" t="s">
         <v>48</v>
@@ -7033,7 +7016,7 @@
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B159" s="8">
         <v>12.0</v>
@@ -7042,7 +7025,7 @@
         <v>43</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E159" s="8" t="s">
         <v>41</v>
@@ -7051,7 +7034,7 @@
         <v>28</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H159" s="8" t="s">
         <v>41</v>
@@ -7077,7 +7060,7 @@
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B160" s="8">
         <v>13.0</v>
@@ -7086,7 +7069,7 @@
         <v>43</v>
       </c>
       <c r="D160" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E160" s="8" t="s">
         <v>41</v>
@@ -7095,7 +7078,7 @@
         <v>28</v>
       </c>
       <c r="G160" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H160" s="8" t="s">
         <v>41</v>
@@ -7149,7 +7132,7 @@
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B162" s="8">
         <v>19.0</v>
@@ -7158,7 +7141,7 @@
         <v>50</v>
       </c>
       <c r="D162" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E162" s="8" t="s">
         <v>51</v>
@@ -7167,7 +7150,7 @@
         <v>28</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H162" s="8" t="s">
         <v>51</v>
@@ -7193,7 +7176,7 @@
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B163" s="8">
         <v>20.0</v>
@@ -7202,7 +7185,7 @@
         <v>50</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E163" s="8" t="s">
         <v>51</v>
@@ -7211,7 +7194,7 @@
         <v>28</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H163" s="8" t="s">
         <v>51</v>
@@ -7265,7 +7248,7 @@
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B165" s="8">
         <v>19.0</v>
@@ -7274,7 +7257,7 @@
         <v>26</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E165" s="12" t="s">
         <v>17</v>
@@ -7283,7 +7266,7 @@
         <v>28</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H165" s="8" t="s">
         <v>17</v>
@@ -7309,7 +7292,7 @@
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B166" s="8">
         <v>20.0</v>
@@ -7318,7 +7301,7 @@
         <v>26</v>
       </c>
       <c r="D166" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E166" s="12" t="s">
         <v>17</v>
@@ -7353,7 +7336,7 @@
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B167" s="8">
         <v>19.0</v>
@@ -7397,7 +7380,7 @@
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B168" s="8">
         <v>20.0</v>
@@ -7469,7 +7452,7 @@
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B170" s="8">
         <v>26.0</v>
@@ -7513,7 +7496,7 @@
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B171" s="8">
         <v>27.0</v>
@@ -7585,7 +7568,7 @@
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B173" s="8">
         <v>26.0</v>
@@ -7594,7 +7577,7 @@
         <v>66</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E173" s="8" t="s">
         <v>64</v>
@@ -7603,7 +7586,7 @@
         <v>28</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H173" s="8" t="s">
         <v>64</v>
@@ -7629,7 +7612,7 @@
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B174" s="8">
         <v>27.0</v>
@@ -7638,7 +7621,7 @@
         <v>66</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E174" s="8" t="s">
         <v>64</v>
@@ -7647,7 +7630,7 @@
         <v>28</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H174" s="8" t="s">
         <v>64</v>
@@ -7673,7 +7656,7 @@
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B175" s="8">
         <v>26.0</v>
@@ -7682,7 +7665,7 @@
         <v>65</v>
       </c>
       <c r="D175" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E175" s="8" t="s">
         <v>64</v>
@@ -7717,7 +7700,7 @@
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B176" s="8">
         <v>27.0</v>
@@ -7789,7 +7772,7 @@
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B178" s="8">
         <v>26.0</v>
@@ -7833,7 +7816,7 @@
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B179" s="8">
         <v>27.0</v>
@@ -7905,16 +7888,16 @@
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B181" s="14">
         <v>27.0</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E181" s="6" t="s">
         <v>11</v>
@@ -7949,16 +7932,16 @@
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B182" s="14">
         <v>26.0</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D182" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>11</v>
@@ -8021,16 +8004,16 @@
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B184" s="14">
         <v>27.0</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>11</v>
@@ -8065,16 +8048,16 @@
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B185" s="14">
         <v>26.0</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E185" s="6" t="s">
         <v>11</v>
@@ -8137,7 +8120,7 @@
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B187" s="8">
         <v>5.0</v>
@@ -8146,7 +8129,7 @@
         <v>45</v>
       </c>
       <c r="D187" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E187" s="12" t="s">
         <v>46</v>
@@ -8155,7 +8138,7 @@
         <v>28</v>
       </c>
       <c r="G187" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H187" s="12" t="s">
         <v>46</v>
@@ -8181,7 +8164,7 @@
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B188" s="8">
         <v>19.0</v>
@@ -8190,7 +8173,7 @@
         <v>45</v>
       </c>
       <c r="D188" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E188" s="12" t="s">
         <v>46</v>
@@ -8199,7 +8182,7 @@
         <v>28</v>
       </c>
       <c r="G188" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H188" s="12" t="s">
         <v>46</v>
@@ -8233,7 +8216,7 @@
         <v>28</v>
       </c>
       <c r="G189" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H189" s="8"/>
       <c r="I189" s="8"/>
@@ -8257,7 +8240,7 @@
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B190" s="8">
         <v>5.0</v>
@@ -8266,7 +8249,7 @@
         <v>9</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E190" s="12" t="s">
         <v>17</v>
@@ -8275,7 +8258,7 @@
         <v>28</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H190" s="12" t="s">
         <v>17</v>
@@ -8301,7 +8284,7 @@
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B191" s="8">
         <v>19.0</v>
@@ -8310,7 +8293,7 @@
         <v>9</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E191" s="12" t="s">
         <v>17</v>
@@ -8319,7 +8302,7 @@
         <v>28</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H191" s="12" t="s">
         <v>17</v>
@@ -8345,13 +8328,13 @@
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B192" s="8">
         <v>5.0</v>
       </c>
       <c r="C192" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D192" s="12" t="s">
         <v>57</v>
@@ -8360,10 +8343,10 @@
         <v>17</v>
       </c>
       <c r="F192" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G192" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H192" s="12" t="s">
         <v>17</v>
@@ -8389,13 +8372,13 @@
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B193" s="8">
         <v>19.0</v>
       </c>
       <c r="C193" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D193" s="12" t="s">
         <v>58</v>
@@ -8404,10 +8387,10 @@
         <v>17</v>
       </c>
       <c r="F193" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G193" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H193" s="12" t="s">
         <v>17</v>
@@ -8461,28 +8444,28 @@
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B195" s="8">
         <v>10.0</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D195" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E195" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F195" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G195" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H195" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I195" s="8"/>
       <c r="J195" s="8"/>
@@ -8505,28 +8488,28 @@
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B196" s="8">
         <v>11.0</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D196" s="8" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="E196" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F196" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G196" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H196" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I196" s="8"/>
       <c r="J196" s="8"/>
@@ -8577,28 +8560,28 @@
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B198" s="8">
         <v>10.0</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E198" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F198" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G198" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H198" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I198" s="8"/>
       <c r="J198" s="8"/>
@@ -8621,28 +8604,28 @@
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B199" s="8">
         <v>11.0</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D199" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E199" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F199" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G199" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H199" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I199" s="8"/>
       <c r="J199" s="8"/>
@@ -8693,28 +8676,28 @@
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B201" s="8">
         <v>10.0</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D201" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E201" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F201" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G201" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H201" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I201" s="8"/>
       <c r="J201" s="8"/>
@@ -8737,28 +8720,28 @@
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B202" s="8">
         <v>11.0</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D202" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E202" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F202" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G202" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H202" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I202" s="8"/>
       <c r="J202" s="8"/>
@@ -8809,7 +8792,7 @@
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B204" s="8">
         <v>10.0</v>
@@ -8818,16 +8801,16 @@
         <v>49</v>
       </c>
       <c r="D204" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E204" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F204" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G204" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H204" s="8" t="s">
         <v>48</v>
@@ -8853,7 +8836,7 @@
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B205" s="8">
         <v>11.0</v>
@@ -8862,16 +8845,16 @@
         <v>49</v>
       </c>
       <c r="D205" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E205" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F205" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G205" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H205" s="8" t="s">
         <v>48</v>
@@ -8925,7 +8908,7 @@
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B207" s="8">
         <v>10.0</v>
@@ -8934,16 +8917,16 @@
         <v>43</v>
       </c>
       <c r="D207" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E207" s="8" t="s">
         <v>41</v>
       </c>
       <c r="F207" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G207" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H207" s="8" t="s">
         <v>41</v>
@@ -8969,7 +8952,7 @@
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B208" s="8">
         <v>11.0</v>
@@ -8978,16 +8961,16 @@
         <v>43</v>
       </c>
       <c r="D208" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E208" s="8" t="s">
         <v>41</v>
       </c>
       <c r="F208" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G208" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H208" s="8" t="s">
         <v>41</v>
@@ -9041,7 +9024,7 @@
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B210" s="8">
         <v>17.0</v>
@@ -9050,16 +9033,16 @@
         <v>50</v>
       </c>
       <c r="D210" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E210" s="8" t="s">
         <v>51</v>
       </c>
       <c r="F210" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G210" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H210" s="8" t="s">
         <v>51</v>
@@ -9085,7 +9068,7 @@
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B211" s="8">
         <v>18.0</v>
@@ -9094,16 +9077,16 @@
         <v>50</v>
       </c>
       <c r="D211" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E211" s="8" t="s">
         <v>51</v>
       </c>
       <c r="F211" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G211" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H211" s="8" t="s">
         <v>51</v>
@@ -9157,7 +9140,7 @@
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B213" s="8">
         <v>17.0</v>
@@ -9166,16 +9149,16 @@
         <v>26</v>
       </c>
       <c r="D213" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E213" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F213" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G213" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H213" s="8" t="s">
         <v>17</v>
@@ -9201,7 +9184,7 @@
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B214" s="8">
         <v>18.0</v>
@@ -9210,16 +9193,16 @@
         <v>26</v>
       </c>
       <c r="D214" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E214" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F214" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G214" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H214" s="8" t="s">
         <v>17</v>
@@ -9273,7 +9256,7 @@
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B216" s="8">
         <v>17.0</v>
@@ -9282,7 +9265,7 @@
         <v>22</v>
       </c>
       <c r="D216" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E216" s="8" t="s">
         <v>17</v>
@@ -9291,7 +9274,7 @@
         <v>42</v>
       </c>
       <c r="G216" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H216" s="8" t="s">
         <v>17</v>
@@ -9317,7 +9300,7 @@
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B217" s="8">
         <v>18.0</v>
@@ -9326,7 +9309,7 @@
         <v>22</v>
       </c>
       <c r="D217" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E217" s="8" t="s">
         <v>17</v>
@@ -9335,7 +9318,7 @@
         <v>42</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H217" s="8" t="s">
         <v>17</v>
@@ -9389,7 +9372,7 @@
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B219" s="8">
         <v>17.0</v>
@@ -9398,7 +9381,7 @@
         <v>54</v>
       </c>
       <c r="D219" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E219" s="8" t="s">
         <v>53</v>
@@ -9407,7 +9390,7 @@
         <v>28</v>
       </c>
       <c r="G219" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H219" s="8" t="s">
         <v>53</v>
@@ -9433,7 +9416,7 @@
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B220" s="8">
         <v>18.0</v>
@@ -9442,7 +9425,7 @@
         <v>54</v>
       </c>
       <c r="D220" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E220" s="8" t="s">
         <v>53</v>
@@ -9451,7 +9434,7 @@
         <v>28</v>
       </c>
       <c r="G220" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H220" s="8" t="s">
         <v>53</v>
@@ -9505,7 +9488,7 @@
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B222" s="8">
         <v>17.0</v>
@@ -9514,16 +9497,16 @@
         <v>66</v>
       </c>
       <c r="D222" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E222" s="8" t="s">
         <v>64</v>
       </c>
       <c r="F222" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G222" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H222" s="8" t="s">
         <v>64</v>
@@ -9549,7 +9532,7 @@
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B223" s="8">
         <v>18.0</v>
@@ -9558,16 +9541,16 @@
         <v>66</v>
       </c>
       <c r="D223" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E223" s="8" t="s">
         <v>64</v>
       </c>
       <c r="F223" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G223" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H223" s="8" t="s">
         <v>64</v>
@@ -9593,7 +9576,7 @@
     </row>
     <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B224" s="8">
         <v>17.0</v>
@@ -9602,7 +9585,7 @@
         <v>65</v>
       </c>
       <c r="D224" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E224" s="12" t="s">
         <v>64</v>
@@ -9611,7 +9594,7 @@
         <v>42</v>
       </c>
       <c r="G224" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H224" s="12" t="s">
         <v>64</v>
@@ -9637,7 +9620,7 @@
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B225" s="8">
         <v>18.0</v>
@@ -9646,7 +9629,7 @@
         <v>65</v>
       </c>
       <c r="D225" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E225" s="12" t="s">
         <v>64</v>
@@ -9655,7 +9638,7 @@
         <v>42</v>
       </c>
       <c r="G225" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H225" s="12" t="s">
         <v>64</v>
@@ -9709,7 +9692,7 @@
     </row>
     <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B227" s="8">
         <v>17.0</v>
@@ -9718,7 +9701,7 @@
         <v>61</v>
       </c>
       <c r="D227" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E227" s="12" t="s">
         <v>60</v>
@@ -9727,7 +9710,7 @@
         <v>42</v>
       </c>
       <c r="G227" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H227" s="12" t="s">
         <v>60</v>
@@ -9753,7 +9736,7 @@
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B228" s="8">
         <v>18.0</v>
@@ -9762,7 +9745,7 @@
         <v>61</v>
       </c>
       <c r="D228" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E228" s="12" t="s">
         <v>60</v>
@@ -9771,7 +9754,7 @@
         <v>42</v>
       </c>
       <c r="G228" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H228" s="12" t="s">
         <v>60</v>
@@ -9825,25 +9808,25 @@
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B230" s="8">
         <v>31.0</v>
       </c>
       <c r="C230" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D230" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E230" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F230" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G230" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H230" s="8" t="s">
         <v>60</v>
@@ -9869,25 +9852,25 @@
     </row>
     <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B231" s="8">
         <v>1.0</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D231" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E231" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F231" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G231" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H231" s="8" t="s">
         <v>60</v>
@@ -9941,25 +9924,25 @@
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B233" s="8">
         <v>31.0</v>
       </c>
       <c r="C233" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D233" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E233" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F233" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G233" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H233" s="8" t="s">
         <v>53</v>
@@ -9985,25 +9968,25 @@
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B234" s="8">
         <v>1.0</v>
       </c>
       <c r="C234" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D234" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E234" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F234" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G234" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H234" s="8" t="s">
         <v>53</v>
@@ -10057,7 +10040,7 @@
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B236" s="8">
         <v>2.0</v>
@@ -10066,16 +10049,16 @@
         <v>45</v>
       </c>
       <c r="D236" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E236" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F236" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G236" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="G236" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="H236" s="8" t="s">
         <v>46</v>
@@ -10101,7 +10084,7 @@
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B237" s="8">
         <v>16.0</v>
@@ -10110,16 +10093,16 @@
         <v>45</v>
       </c>
       <c r="D237" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E237" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F237" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G237" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="G237" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="H237" s="8" t="s">
         <v>46</v>
@@ -10173,7 +10156,7 @@
     </row>
     <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B239" s="8">
         <v>2.0</v>
@@ -10182,16 +10165,16 @@
         <v>9</v>
       </c>
       <c r="D239" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E239" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F239" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G239" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="G239" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="H239" s="8" t="s">
         <v>17</v>
@@ -10217,7 +10200,7 @@
     </row>
     <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B240" s="8">
         <v>16.0</v>
@@ -10226,16 +10209,16 @@
         <v>9</v>
       </c>
       <c r="D240" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E240" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F240" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G240" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="G240" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="H240" s="8" t="s">
         <v>17</v>
@@ -10261,16 +10244,16 @@
     </row>
     <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B241" s="8">
         <v>2.0</v>
       </c>
       <c r="C241" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D241" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E241" s="8" t="s">
         <v>17</v>
@@ -10279,7 +10262,7 @@
         <v>42</v>
       </c>
       <c r="G241" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H241" s="8" t="s">
         <v>17</v>
@@ -10305,16 +10288,16 @@
     </row>
     <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B242" s="8">
         <v>16.0</v>
       </c>
       <c r="C242" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D242" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E242" s="8" t="s">
         <v>17</v>
@@ -10323,7 +10306,7 @@
         <v>42</v>
       </c>
       <c r="G242" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H242" s="8" t="s">
         <v>17</v>
@@ -10377,28 +10360,28 @@
     </row>
     <row r="244" ht="15.75" customHeight="1">
       <c r="A244" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B244" s="8">
         <v>7.0</v>
       </c>
       <c r="C244" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D244" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E244" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F244" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G244" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="G244" s="8" t="s">
-        <v>114</v>
-      </c>
       <c r="H244" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I244" s="8"/>
       <c r="J244" s="8"/>
@@ -10421,28 +10404,28 @@
     </row>
     <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B245" s="8">
         <v>8.0</v>
       </c>
       <c r="C245" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D245" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E245" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F245" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G245" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="G245" s="8" t="s">
-        <v>114</v>
-      </c>
       <c r="H245" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I245" s="8"/>
       <c r="J245" s="8"/>
@@ -10493,28 +10476,28 @@
     </row>
     <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B247" s="8">
         <v>7.0</v>
       </c>
       <c r="C247" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D247" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E247" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F247" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G247" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="G247" s="8" t="s">
-        <v>114</v>
-      </c>
       <c r="H247" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I247" s="8"/>
       <c r="J247" s="8"/>
@@ -10537,28 +10520,28 @@
     </row>
     <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B248" s="8">
         <v>8.0</v>
       </c>
       <c r="C248" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D248" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E248" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F248" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G248" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="G248" s="8" t="s">
-        <v>114</v>
-      </c>
       <c r="H248" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I248" s="8"/>
       <c r="J248" s="8"/>
@@ -10609,28 +10592,28 @@
     </row>
     <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B250" s="8">
         <v>7.0</v>
       </c>
       <c r="C250" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D250" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E250" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F250" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G250" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="G250" s="8" t="s">
-        <v>114</v>
-      </c>
       <c r="H250" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I250" s="8"/>
       <c r="J250" s="8"/>
@@ -10653,28 +10636,28 @@
     </row>
     <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B251" s="8">
         <v>8.0</v>
       </c>
       <c r="C251" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D251" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E251" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F251" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G251" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="G251" s="8" t="s">
-        <v>114</v>
-      </c>
       <c r="H251" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I251" s="8"/>
       <c r="J251" s="8"/>
@@ -10725,7 +10708,7 @@
     </row>
     <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B253" s="8">
         <v>14.0</v>
@@ -10734,16 +10717,16 @@
         <v>49</v>
       </c>
       <c r="D253" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E253" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F253" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G253" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="G253" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="H253" s="8" t="s">
         <v>48</v>
@@ -10769,7 +10752,7 @@
     </row>
     <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B254" s="8">
         <v>15.0</v>
@@ -10778,16 +10761,16 @@
         <v>49</v>
       </c>
       <c r="D254" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E254" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F254" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G254" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="G254" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="H254" s="8" t="s">
         <v>48</v>
@@ -10841,7 +10824,7 @@
     </row>
     <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B256" s="8">
         <v>14.0</v>
@@ -10850,16 +10833,16 @@
         <v>43</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E256" s="8" t="s">
         <v>41</v>
       </c>
       <c r="F256" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G256" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="G256" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="H256" s="8" t="s">
         <v>41</v>
@@ -10885,7 +10868,7 @@
     </row>
     <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B257" s="8">
         <v>15.0</v>
@@ -10894,16 +10877,16 @@
         <v>43</v>
       </c>
       <c r="D257" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E257" s="8" t="s">
         <v>41</v>
       </c>
       <c r="F257" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G257" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="G257" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="H257" s="8" t="s">
         <v>41</v>
@@ -10957,7 +10940,7 @@
     </row>
     <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B259" s="8">
         <v>21.0</v>
@@ -10966,16 +10949,16 @@
         <v>50</v>
       </c>
       <c r="D259" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E259" s="8" t="s">
         <v>51</v>
       </c>
       <c r="F259" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G259" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="G259" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="H259" s="8" t="s">
         <v>51</v>
@@ -11001,7 +10984,7 @@
     </row>
     <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B260" s="8">
         <v>22.0</v>
@@ -11010,16 +10993,16 @@
         <v>50</v>
       </c>
       <c r="D260" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E260" s="8" t="s">
         <v>51</v>
       </c>
       <c r="F260" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G260" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="G260" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="H260" s="8" t="s">
         <v>51</v>
@@ -11073,7 +11056,7 @@
     </row>
     <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B262" s="8">
         <v>21.0</v>
@@ -11082,16 +11065,16 @@
         <v>26</v>
       </c>
       <c r="D262" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E262" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F262" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G262" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="G262" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="H262" s="8" t="s">
         <v>17</v>
@@ -11117,7 +11100,7 @@
     </row>
     <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B263" s="8">
         <v>22.0</v>
@@ -11126,16 +11109,16 @@
         <v>26</v>
       </c>
       <c r="D263" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E263" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F263" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G263" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="G263" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="H263" s="8" t="s">
         <v>17</v>
@@ -11189,7 +11172,7 @@
     </row>
     <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B265" s="8">
         <v>21.0</v>
@@ -11198,7 +11181,7 @@
         <v>22</v>
       </c>
       <c r="D265" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E265" s="8" t="s">
         <v>17</v>
@@ -11207,7 +11190,7 @@
         <v>42</v>
       </c>
       <c r="G265" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H265" s="8" t="s">
         <v>17</v>
@@ -11233,7 +11216,7 @@
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B266" s="8">
         <v>22.0</v>
@@ -11242,7 +11225,7 @@
         <v>22</v>
       </c>
       <c r="D266" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E266" s="8" t="s">
         <v>17</v>
@@ -11251,7 +11234,7 @@
         <v>42</v>
       </c>
       <c r="G266" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H266" s="8" t="s">
         <v>17</v>
@@ -11305,7 +11288,7 @@
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B268" s="8">
         <v>28.0</v>
@@ -11314,7 +11297,7 @@
         <v>54</v>
       </c>
       <c r="D268" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E268" s="8" t="s">
         <v>53</v>
@@ -11323,7 +11306,7 @@
         <v>42</v>
       </c>
       <c r="G268" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H268" s="8" t="s">
         <v>53</v>
@@ -11349,7 +11332,7 @@
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B269" s="8">
         <v>29.0</v>
@@ -11358,7 +11341,7 @@
         <v>54</v>
       </c>
       <c r="D269" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E269" s="8" t="s">
         <v>53</v>
@@ -11367,7 +11350,7 @@
         <v>42</v>
       </c>
       <c r="G269" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H269" s="8" t="s">
         <v>53</v>
@@ -11421,7 +11404,7 @@
     </row>
     <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B271" s="8">
         <v>28.0</v>
@@ -11430,16 +11413,16 @@
         <v>66</v>
       </c>
       <c r="D271" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E271" s="8" t="s">
         <v>64</v>
       </c>
       <c r="F271" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G271" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="G271" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="H271" s="8" t="s">
         <v>64</v>
@@ -11465,7 +11448,7 @@
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B272" s="8">
         <v>29.0</v>
@@ -11474,16 +11457,16 @@
         <v>66</v>
       </c>
       <c r="D272" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E272" s="8" t="s">
         <v>64</v>
       </c>
       <c r="F272" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G272" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="G272" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="H272" s="8" t="s">
         <v>64</v>
@@ -11509,7 +11492,7 @@
     </row>
     <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B273" s="8">
         <v>28.0</v>
@@ -11518,7 +11501,7 @@
         <v>65</v>
       </c>
       <c r="D273" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E273" s="8" t="s">
         <v>64</v>
@@ -11527,7 +11510,7 @@
         <v>42</v>
       </c>
       <c r="G273" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H273" s="8" t="s">
         <v>64</v>
@@ -11553,7 +11536,7 @@
     </row>
     <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B274" s="8">
         <v>29.0</v>
@@ -11562,7 +11545,7 @@
         <v>65</v>
       </c>
       <c r="D274" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E274" s="8" t="s">
         <v>64</v>
@@ -11571,7 +11554,7 @@
         <v>42</v>
       </c>
       <c r="G274" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H274" s="8" t="s">
         <v>64</v>
@@ -11625,7 +11608,7 @@
     </row>
     <row r="276" ht="15.75" customHeight="1">
       <c r="A276" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B276" s="8">
         <v>28.0</v>
@@ -11634,7 +11617,7 @@
         <v>61</v>
       </c>
       <c r="D276" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E276" s="8" t="s">
         <v>60</v>
@@ -11643,7 +11626,7 @@
         <v>42</v>
       </c>
       <c r="G276" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H276" s="8" t="s">
         <v>60</v>
@@ -11669,7 +11652,7 @@
     </row>
     <row r="277" ht="15.75" customHeight="1">
       <c r="A277" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B277" s="8">
         <v>29.0</v>
@@ -11678,7 +11661,7 @@
         <v>61</v>
       </c>
       <c r="D277" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E277" s="8" t="s">
         <v>60</v>
@@ -11687,7 +11670,7 @@
         <v>42</v>
       </c>
       <c r="G277" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H277" s="8" t="s">
         <v>60</v>
@@ -11741,25 +11724,25 @@
     </row>
     <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B279" s="8">
         <v>28.0</v>
       </c>
       <c r="C279" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D279" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E279" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F279" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G279" s="12" t="s">
         <v>113</v>
-      </c>
-      <c r="G279" s="12" t="s">
-        <v>114</v>
       </c>
       <c r="H279" s="8" t="s">
         <v>60</v>
@@ -11785,25 +11768,25 @@
     </row>
     <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B280" s="8">
         <v>29.0</v>
       </c>
       <c r="C280" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D280" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E280" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F280" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G280" s="12" t="s">
         <v>113</v>
-      </c>
-      <c r="G280" s="12" t="s">
-        <v>114</v>
       </c>
       <c r="H280" s="8" t="s">
         <v>60</v>
@@ -11857,25 +11840,25 @@
     </row>
     <row r="282" ht="15.75" customHeight="1">
       <c r="A282" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B282" s="8">
         <v>28.0</v>
       </c>
       <c r="C282" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D282" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E282" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F282" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G282" s="12" t="s">
         <v>113</v>
-      </c>
-      <c r="G282" s="12" t="s">
-        <v>114</v>
       </c>
       <c r="H282" s="8" t="s">
         <v>53</v>
@@ -11901,25 +11884,25 @@
     </row>
     <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B283" s="8">
         <v>29.0</v>
       </c>
       <c r="C283" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D283" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E283" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F283" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G283" s="12" t="s">
         <v>113</v>
-      </c>
-      <c r="G283" s="12" t="s">
-        <v>114</v>
       </c>
       <c r="H283" s="8" t="s">
         <v>53</v>
@@ -12001,7 +11984,7 @@
     </row>
     <row r="286" ht="15.75" customHeight="1">
       <c r="A286" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B286" s="12">
         <v>7.0</v>
@@ -12010,16 +11993,16 @@
         <v>45</v>
       </c>
       <c r="D286" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E286" s="12" t="s">
         <v>46</v>
       </c>
       <c r="F286" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G286" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G286" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H286" s="12" t="s">
         <v>46</v>
@@ -12045,7 +12028,7 @@
     </row>
     <row r="287" ht="15.75" customHeight="1">
       <c r="A287" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B287" s="12">
         <v>14.0</v>
@@ -12054,16 +12037,16 @@
         <v>45</v>
       </c>
       <c r="D287" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E287" s="12" t="s">
         <v>46</v>
       </c>
       <c r="F287" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G287" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G287" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H287" s="12" t="s">
         <v>46</v>
@@ -12117,7 +12100,7 @@
     </row>
     <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B289" s="12">
         <v>7.0</v>
@@ -12126,16 +12109,16 @@
         <v>9</v>
       </c>
       <c r="D289" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E289" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F289" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G289" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G289" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H289" s="12" t="s">
         <v>17</v>
@@ -12161,7 +12144,7 @@
     </row>
     <row r="290" ht="15.75" customHeight="1">
       <c r="A290" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B290" s="12">
         <v>14.0</v>
@@ -12170,16 +12153,16 @@
         <v>9</v>
       </c>
       <c r="D290" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E290" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F290" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G290" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G290" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H290" s="12" t="s">
         <v>17</v>
@@ -12205,16 +12188,16 @@
     </row>
     <row r="291" ht="15.75" customHeight="1">
       <c r="A291" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B291" s="12">
         <v>7.0</v>
       </c>
       <c r="C291" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D291" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E291" s="12" t="s">
         <v>17</v>
@@ -12223,7 +12206,7 @@
         <v>42</v>
       </c>
       <c r="G291" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H291" s="12" t="s">
         <v>17</v>
@@ -12249,16 +12232,16 @@
     </row>
     <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B292" s="12">
         <v>14.0</v>
       </c>
       <c r="C292" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D292" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E292" s="12" t="s">
         <v>17</v>
@@ -12267,7 +12250,7 @@
         <v>42</v>
       </c>
       <c r="G292" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H292" s="12" t="s">
         <v>17</v>
@@ -12321,28 +12304,28 @@
     </row>
     <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B294" s="8">
         <v>5.0</v>
       </c>
       <c r="C294" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D294" s="12" t="s">
         <v>32</v>
       </c>
       <c r="E294" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F294" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G294" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G294" s="12" t="s">
-        <v>121</v>
-      </c>
       <c r="H294" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I294" s="8"/>
       <c r="J294" s="8"/>
@@ -12365,28 +12348,28 @@
     </row>
     <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B295" s="8">
         <v>6.0</v>
       </c>
       <c r="C295" s="12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D295" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E295" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F295" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G295" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G295" s="12" t="s">
-        <v>121</v>
-      </c>
       <c r="H295" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I295" s="8"/>
       <c r="J295" s="8"/>
@@ -12437,28 +12420,28 @@
     </row>
     <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B297" s="8">
         <v>5.0</v>
       </c>
       <c r="C297" s="12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D297" s="12" t="s">
         <v>20</v>
       </c>
       <c r="E297" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F297" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G297" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G297" s="12" t="s">
-        <v>121</v>
-      </c>
       <c r="H297" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I297" s="8"/>
       <c r="J297" s="8"/>
@@ -12481,28 +12464,28 @@
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B298" s="8">
         <v>6.0</v>
       </c>
       <c r="C298" s="12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D298" s="12" t="s">
         <v>25</v>
       </c>
       <c r="E298" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F298" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G298" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G298" s="12" t="s">
-        <v>121</v>
-      </c>
       <c r="H298" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I298" s="8"/>
       <c r="J298" s="8"/>
@@ -12553,28 +12536,28 @@
     </row>
     <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B300" s="8">
         <v>5.0</v>
       </c>
       <c r="C300" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D300" s="12" t="s">
         <v>32</v>
       </c>
       <c r="E300" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F300" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G300" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G300" s="12" t="s">
-        <v>121</v>
-      </c>
       <c r="H300" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I300" s="8"/>
       <c r="J300" s="8"/>
@@ -12597,28 +12580,28 @@
     </row>
     <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B301" s="8">
         <v>6.0</v>
       </c>
       <c r="C301" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D301" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E301" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F301" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G301" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G301" s="12" t="s">
-        <v>121</v>
-      </c>
       <c r="H301" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I301" s="8"/>
       <c r="J301" s="8"/>
@@ -12669,7 +12652,7 @@
     </row>
     <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B303" s="8">
         <v>5.0</v>
@@ -12684,10 +12667,10 @@
         <v>51</v>
       </c>
       <c r="F303" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G303" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G303" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H303" s="8" t="s">
         <v>51</v>
@@ -12713,7 +12696,7 @@
     </row>
     <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B304" s="8">
         <v>6.0</v>
@@ -12728,10 +12711,10 @@
         <v>51</v>
       </c>
       <c r="F304" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G304" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G304" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H304" s="8" t="s">
         <v>51</v>
@@ -12785,7 +12768,7 @@
     </row>
     <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B306" s="8">
         <v>5.0</v>
@@ -12800,10 +12783,10 @@
         <v>17</v>
       </c>
       <c r="F306" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G306" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G306" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H306" s="12" t="s">
         <v>17</v>
@@ -12829,7 +12812,7 @@
     </row>
     <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B307" s="8">
         <v>6.0</v>
@@ -12844,10 +12827,10 @@
         <v>17</v>
       </c>
       <c r="F307" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G307" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G307" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H307" s="12" t="s">
         <v>17</v>
@@ -12873,7 +12856,7 @@
     </row>
     <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B308" s="8">
         <v>5.0</v>
@@ -12882,7 +12865,7 @@
         <v>22</v>
       </c>
       <c r="D308" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E308" s="12" t="s">
         <v>17</v>
@@ -12891,7 +12874,7 @@
         <v>42</v>
       </c>
       <c r="G308" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H308" s="12" t="s">
         <v>17</v>
@@ -12917,7 +12900,7 @@
     </row>
     <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B309" s="8">
         <v>6.0</v>
@@ -12926,7 +12909,7 @@
         <v>22</v>
       </c>
       <c r="D309" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E309" s="12" t="s">
         <v>17</v>
@@ -12935,7 +12918,7 @@
         <v>42</v>
       </c>
       <c r="G309" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H309" s="12" t="s">
         <v>17</v>
@@ -12989,7 +12972,7 @@
     </row>
     <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B311" s="8">
         <v>12.0</v>
@@ -13004,10 +12987,10 @@
         <v>48</v>
       </c>
       <c r="F311" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G311" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G311" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H311" s="12" t="s">
         <v>48</v>
@@ -13033,7 +13016,7 @@
     </row>
     <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B312" s="8">
         <v>13.0</v>
@@ -13048,10 +13031,10 @@
         <v>48</v>
       </c>
       <c r="F312" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G312" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G312" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H312" s="12" t="s">
         <v>48</v>
@@ -13105,7 +13088,7 @@
     </row>
     <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B314" s="8">
         <v>12.0</v>
@@ -13120,10 +13103,10 @@
         <v>41</v>
       </c>
       <c r="F314" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G314" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G314" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H314" s="8" t="s">
         <v>41</v>
@@ -13149,7 +13132,7 @@
     </row>
     <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B315" s="8">
         <v>13.0</v>
@@ -13164,10 +13147,10 @@
         <v>41</v>
       </c>
       <c r="F315" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G315" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G315" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H315" s="8" t="s">
         <v>41</v>
@@ -13221,7 +13204,7 @@
     </row>
     <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B317" s="8">
         <v>12.0</v>
@@ -13230,7 +13213,7 @@
         <v>54</v>
       </c>
       <c r="D317" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E317" s="12" t="s">
         <v>53</v>
@@ -13239,7 +13222,7 @@
         <v>42</v>
       </c>
       <c r="G317" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H317" s="12" t="s">
         <v>53</v>
@@ -13265,7 +13248,7 @@
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B318" s="8">
         <v>13.0</v>
@@ -13274,7 +13257,7 @@
         <v>54</v>
       </c>
       <c r="D318" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E318" s="12" t="s">
         <v>53</v>
@@ -13283,7 +13266,7 @@
         <v>42</v>
       </c>
       <c r="G318" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H318" s="12" t="s">
         <v>53</v>
@@ -13337,7 +13320,7 @@
     </row>
     <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B320" s="8">
         <v>12.0</v>
@@ -13352,10 +13335,10 @@
         <v>64</v>
       </c>
       <c r="F320" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G320" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G320" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H320" s="8" t="s">
         <v>64</v>
@@ -13381,7 +13364,7 @@
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B321" s="8">
         <v>13.0</v>
@@ -13396,10 +13379,10 @@
         <v>64</v>
       </c>
       <c r="F321" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G321" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G321" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H321" s="8" t="s">
         <v>64</v>
@@ -13425,7 +13408,7 @@
     </row>
     <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B322" s="8">
         <v>12.0</v>
@@ -13434,7 +13417,7 @@
         <v>65</v>
       </c>
       <c r="D322" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E322" s="8" t="s">
         <v>64</v>
@@ -13443,7 +13426,7 @@
         <v>42</v>
       </c>
       <c r="G322" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H322" s="8" t="s">
         <v>64</v>
@@ -13469,7 +13452,7 @@
     </row>
     <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B323" s="8">
         <v>13.0</v>
@@ -13478,7 +13461,7 @@
         <v>65</v>
       </c>
       <c r="D323" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E323" s="8" t="s">
         <v>64</v>
@@ -13487,7 +13470,7 @@
         <v>42</v>
       </c>
       <c r="G323" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H323" s="8" t="s">
         <v>64</v>
@@ -13541,7 +13524,7 @@
     </row>
     <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B325" s="8">
         <v>12.0</v>
@@ -13550,7 +13533,7 @@
         <v>61</v>
       </c>
       <c r="D325" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E325" s="8" t="s">
         <v>60</v>
@@ -13559,7 +13542,7 @@
         <v>42</v>
       </c>
       <c r="G325" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H325" s="8" t="s">
         <v>60</v>
@@ -13585,7 +13568,7 @@
     </row>
     <row r="326" ht="15.75" customHeight="1">
       <c r="A326" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B326" s="8">
         <v>13.0</v>
@@ -13594,7 +13577,7 @@
         <v>61</v>
       </c>
       <c r="D326" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E326" s="8" t="s">
         <v>60</v>
@@ -13603,7 +13586,7 @@
         <v>42</v>
       </c>
       <c r="G326" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H326" s="8" t="s">
         <v>60</v>
@@ -13657,25 +13640,25 @@
     </row>
     <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B328" s="12">
         <v>12.0</v>
       </c>
       <c r="C328" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D328" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E328" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F328" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G328" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G328" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H328" s="8" t="s">
         <v>60</v>
@@ -13701,25 +13684,25 @@
     </row>
     <row r="329" ht="15.75" customHeight="1">
       <c r="A329" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B329" s="12">
         <v>13.0</v>
       </c>
       <c r="C329" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D329" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E329" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F329" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G329" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G329" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H329" s="8" t="s">
         <v>60</v>
@@ -13773,25 +13756,25 @@
     </row>
     <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B331" s="12">
         <v>12.0</v>
       </c>
       <c r="C331" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D331" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E331" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F331" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G331" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G331" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H331" s="8" t="s">
         <v>53</v>
@@ -13817,25 +13800,25 @@
     </row>
     <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B332" s="12">
         <v>13.0</v>
       </c>
       <c r="C332" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D332" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E332" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F332" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G332" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G332" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H332" s="8" t="s">
         <v>53</v>

--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="124">
   <si>
     <t>MÊS</t>
   </si>
@@ -70,7 +70,7 @@
     <t xml:space="preserve">Prática Clinica        </t>
   </si>
   <si>
-    <t>PROINSU SP 2a.f. 010925</t>
+    <t>PROINSU SP 2a.f 010925</t>
   </si>
   <si>
     <t>Procedimento Injetável Estético: Toxina Botulinica - Teoria</t>
@@ -491,9 +491,6 @@
     <t>22/01/2027 a 26/01/2027</t>
   </si>
   <si>
-    <t>PROINSU SP 2a.f 010925</t>
-  </si>
-  <si>
     <t xml:space="preserve">PROINSU BA 280226 </t>
   </si>
   <si>
@@ -668,7 +665,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -699,6 +696,9 @@
     <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
     <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
@@ -722,6 +722,9 @@
     </xf>
     <xf borderId="9" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1087,7 +1090,7 @@
       <c r="B4" s="6">
         <v>6.0</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="10" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="7" t="s">
@@ -1389,7 +1392,7 @@
       <c r="B11" s="6">
         <v>20.0</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="10" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="7" t="s">
@@ -1603,7 +1606,7 @@
       <c r="B16" s="6">
         <v>3.0</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="10" t="s">
         <v>19</v>
       </c>
       <c r="D16" s="7" t="s">
@@ -1907,7 +1910,7 @@
       <c r="B23" s="6">
         <v>17.0</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="10" t="s">
         <v>19</v>
       </c>
       <c r="D23" s="7" t="s">
@@ -2172,7 +2175,7 @@
       <c r="A32" s="5"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
-      <c r="D32" s="10"/>
+      <c r="D32" s="11"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
@@ -2512,7 +2515,7 @@
       <c r="A41" s="5"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
-      <c r="D41" s="10"/>
+      <c r="D41" s="11"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
@@ -3052,7 +3055,7 @@
       <c r="A56" s="5"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
-      <c r="D56" s="10"/>
+      <c r="D56" s="11"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
@@ -3392,7 +3395,7 @@
       <c r="A65" s="5"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
-      <c r="D65" s="10"/>
+      <c r="D65" s="11"/>
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
@@ -3648,7 +3651,7 @@
       <c r="A72" s="5"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
-      <c r="D72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
       <c r="G72" s="8"/>
@@ -4074,7 +4077,7 @@
       <c r="A83" s="5"/>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
-      <c r="D83" s="10"/>
+      <c r="D83" s="11"/>
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
@@ -4448,7 +4451,7 @@
       <c r="C92" s="8"/>
       <c r="D92" s="7"/>
       <c r="E92" s="6"/>
-      <c r="F92" s="11"/>
+      <c r="F92" s="12"/>
       <c r="G92" s="6"/>
       <c r="H92" s="6"/>
       <c r="I92" s="8"/>
@@ -4476,7 +4479,7 @@
       <c r="C93" s="8"/>
       <c r="D93" s="7"/>
       <c r="E93" s="6"/>
-      <c r="F93" s="11"/>
+      <c r="F93" s="12"/>
       <c r="G93" s="6"/>
       <c r="H93" s="6"/>
       <c r="I93" s="8"/>
@@ -4502,7 +4505,7 @@
       <c r="A94" s="5"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
-      <c r="D94" s="10"/>
+      <c r="D94" s="11"/>
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
       <c r="G94" s="8"/>
@@ -5106,7 +5109,7 @@
       <c r="A109" s="5"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
-      <c r="D109" s="10"/>
+      <c r="D109" s="11"/>
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
       <c r="G109" s="8"/>
@@ -5410,7 +5413,7 @@
       <c r="A117" s="5"/>
       <c r="B117" s="8"/>
       <c r="C117" s="8"/>
-      <c r="D117" s="10"/>
+      <c r="D117" s="11"/>
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
       <c r="G117" s="8"/>
@@ -5714,7 +5717,7 @@
       <c r="A125" s="5"/>
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
-      <c r="D125" s="10"/>
+      <c r="D125" s="11"/>
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
       <c r="G125" s="8"/>
@@ -5974,7 +5977,7 @@
       <c r="A132" s="5"/>
       <c r="B132" s="6"/>
       <c r="C132" s="8"/>
-      <c r="D132" s="10"/>
+      <c r="D132" s="11"/>
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
       <c r="G132" s="8"/>
@@ -6090,7 +6093,7 @@
       <c r="A135" s="5"/>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
-      <c r="D135" s="10"/>
+      <c r="D135" s="11"/>
       <c r="E135" s="8"/>
       <c r="F135" s="8"/>
       <c r="G135" s="8"/>
@@ -6206,7 +6209,7 @@
       <c r="A138" s="5"/>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
-      <c r="D138" s="10"/>
+      <c r="D138" s="11"/>
       <c r="E138" s="8"/>
       <c r="F138" s="8"/>
       <c r="G138" s="8"/>
@@ -6234,25 +6237,25 @@
       <c r="A139" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B139" s="12">
+      <c r="B139" s="13">
         <v>7.0</v>
       </c>
-      <c r="C139" s="12" t="s">
+      <c r="C139" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D139" s="12" t="s">
+      <c r="D139" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E139" s="12" t="s">
+      <c r="E139" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="F139" s="12" t="s">
+      <c r="F139" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G139" s="12" t="s">
+      <c r="G139" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="H139" s="12" t="s">
+      <c r="H139" s="13" t="s">
         <v>46</v>
       </c>
       <c r="I139" s="8"/>
@@ -6278,25 +6281,25 @@
       <c r="A140" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B140" s="12">
+      <c r="B140" s="13">
         <v>21.0</v>
       </c>
-      <c r="C140" s="12" t="s">
+      <c r="C140" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D140" s="12" t="s">
+      <c r="D140" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E140" s="12" t="s">
+      <c r="E140" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="F140" s="12" t="s">
+      <c r="F140" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G140" s="12" t="s">
+      <c r="G140" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="H140" s="12" t="s">
+      <c r="H140" s="13" t="s">
         <v>46</v>
       </c>
       <c r="I140" s="8"/>
@@ -6322,7 +6325,7 @@
       <c r="A141" s="5"/>
       <c r="B141" s="8"/>
       <c r="C141" s="8"/>
-      <c r="D141" s="10"/>
+      <c r="D141" s="11"/>
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
       <c r="G141" s="8"/>
@@ -6350,25 +6353,25 @@
       <c r="A142" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B142" s="12">
+      <c r="B142" s="13">
         <v>7.0</v>
       </c>
-      <c r="C142" s="12" t="s">
+      <c r="C142" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D142" s="12" t="s">
+      <c r="D142" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E142" s="12" t="s">
+      <c r="E142" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F142" s="12" t="s">
+      <c r="F142" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G142" s="12" t="s">
+      <c r="G142" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="H142" s="12" t="s">
+      <c r="H142" s="13" t="s">
         <v>17</v>
       </c>
       <c r="I142" s="8"/>
@@ -6394,25 +6397,25 @@
       <c r="A143" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B143" s="12">
+      <c r="B143" s="13">
         <v>21.0</v>
       </c>
-      <c r="C143" s="12" t="s">
+      <c r="C143" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D143" s="12" t="s">
+      <c r="D143" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E143" s="12" t="s">
+      <c r="E143" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F143" s="12" t="s">
+      <c r="F143" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G143" s="12" t="s">
+      <c r="G143" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="H143" s="12" t="s">
+      <c r="H143" s="13" t="s">
         <v>17</v>
       </c>
       <c r="I143" s="8"/>
@@ -6438,25 +6441,25 @@
       <c r="A144" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B144" s="12">
+      <c r="B144" s="13">
         <v>7.0</v>
       </c>
-      <c r="C144" s="12" t="s">
+      <c r="C144" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D144" s="12" t="s">
+      <c r="D144" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E144" s="12" t="s">
+      <c r="E144" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F144" s="12" t="s">
+      <c r="F144" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G144" s="12" t="s">
+      <c r="G144" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="H144" s="12" t="s">
+      <c r="H144" s="13" t="s">
         <v>17</v>
       </c>
       <c r="I144" s="8"/>
@@ -6482,25 +6485,25 @@
       <c r="A145" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B145" s="12">
+      <c r="B145" s="13">
         <v>21.0</v>
       </c>
-      <c r="C145" s="12" t="s">
+      <c r="C145" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="D145" s="12" t="s">
+      <c r="D145" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E145" s="12" t="s">
+      <c r="E145" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F145" s="12" t="s">
+      <c r="F145" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G145" s="12" t="s">
+      <c r="G145" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="H145" s="12" t="s">
+      <c r="H145" s="13" t="s">
         <v>17</v>
       </c>
       <c r="I145" s="8"/>
@@ -6526,7 +6529,7 @@
       <c r="A146" s="5"/>
       <c r="B146" s="8"/>
       <c r="C146" s="8"/>
-      <c r="D146" s="10"/>
+      <c r="D146" s="11"/>
       <c r="E146" s="8"/>
       <c r="F146" s="8"/>
       <c r="G146" s="8"/>
@@ -6566,10 +6569,10 @@
       <c r="E147" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="F147" s="13" t="s">
+      <c r="F147" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G147" s="13" t="s">
+      <c r="G147" s="14" t="s">
         <v>69</v>
       </c>
       <c r="H147" s="8" t="s">
@@ -6610,10 +6613,10 @@
       <c r="E148" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="F148" s="13" t="s">
+      <c r="F148" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G148" s="13" t="s">
+      <c r="G148" s="14" t="s">
         <v>69</v>
       </c>
       <c r="H148" s="8" t="s">
@@ -6642,7 +6645,7 @@
       <c r="A149" s="5"/>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
-      <c r="D149" s="10"/>
+      <c r="D149" s="11"/>
       <c r="E149" s="8"/>
       <c r="F149" s="8"/>
       <c r="G149" s="8"/>
@@ -6758,7 +6761,7 @@
       <c r="A152" s="5"/>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
-      <c r="D152" s="10"/>
+      <c r="D152" s="11"/>
       <c r="E152" s="8"/>
       <c r="F152" s="8"/>
       <c r="G152" s="8"/>
@@ -6798,10 +6801,10 @@
       <c r="E153" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F153" s="13" t="s">
+      <c r="F153" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G153" s="13" t="s">
+      <c r="G153" s="14" t="s">
         <v>69</v>
       </c>
       <c r="H153" s="8" t="s">
@@ -6842,10 +6845,10 @@
       <c r="E154" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F154" s="13" t="s">
+      <c r="F154" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G154" s="13" t="s">
+      <c r="G154" s="14" t="s">
         <v>69</v>
       </c>
       <c r="H154" s="8" t="s">
@@ -6874,7 +6877,7 @@
       <c r="A155" s="5"/>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
-      <c r="D155" s="10"/>
+      <c r="D155" s="11"/>
       <c r="E155" s="8"/>
       <c r="F155" s="8"/>
       <c r="G155" s="8"/>
@@ -6908,16 +6911,16 @@
       <c r="C156" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D156" s="10" t="s">
+      <c r="D156" s="11" t="s">
         <v>86</v>
       </c>
       <c r="E156" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F156" s="13" t="s">
+      <c r="F156" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G156" s="13" t="s">
+      <c r="G156" s="14" t="s">
         <v>69</v>
       </c>
       <c r="H156" s="8" t="s">
@@ -6952,16 +6955,16 @@
       <c r="C157" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D157" s="10" t="s">
+      <c r="D157" s="11" t="s">
         <v>87</v>
       </c>
       <c r="E157" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F157" s="13" t="s">
+      <c r="F157" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G157" s="13" t="s">
+      <c r="G157" s="14" t="s">
         <v>69</v>
       </c>
       <c r="H157" s="8" t="s">
@@ -6990,7 +6993,7 @@
       <c r="A158" s="5"/>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
-      <c r="D158" s="10"/>
+      <c r="D158" s="11"/>
       <c r="E158" s="8"/>
       <c r="F158" s="8"/>
       <c r="G158" s="8"/>
@@ -7106,7 +7109,7 @@
       <c r="A161" s="5"/>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
-      <c r="D161" s="10"/>
+      <c r="D161" s="11"/>
       <c r="E161" s="8"/>
       <c r="F161" s="8"/>
       <c r="G161" s="8"/>
@@ -7222,7 +7225,7 @@
       <c r="A164" s="5"/>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
-      <c r="D164" s="10"/>
+      <c r="D164" s="11"/>
       <c r="E164" s="8"/>
       <c r="F164" s="8"/>
       <c r="G164" s="8"/>
@@ -7259,7 +7262,7 @@
       <c r="D165" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E165" s="12" t="s">
+      <c r="E165" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F165" s="8" t="s">
@@ -7303,13 +7306,13 @@
       <c r="D166" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="E166" s="12" t="s">
+      <c r="E166" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F166" s="13" t="s">
+      <c r="F166" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G166" s="13" t="s">
+      <c r="G166" s="14" t="s">
         <v>69</v>
       </c>
       <c r="H166" s="8" t="s">
@@ -7426,7 +7429,7 @@
       <c r="A169" s="5"/>
       <c r="B169" s="8"/>
       <c r="C169" s="8"/>
-      <c r="D169" s="10"/>
+      <c r="D169" s="11"/>
       <c r="E169" s="8"/>
       <c r="F169" s="8"/>
       <c r="G169" s="8"/>
@@ -7542,7 +7545,7 @@
       <c r="A172" s="5"/>
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
-      <c r="D172" s="10"/>
+      <c r="D172" s="11"/>
       <c r="E172" s="8"/>
       <c r="F172" s="8"/>
       <c r="G172" s="8"/>
@@ -7746,7 +7749,7 @@
       <c r="A177" s="5"/>
       <c r="B177" s="8"/>
       <c r="C177" s="8"/>
-      <c r="D177" s="10"/>
+      <c r="D177" s="11"/>
       <c r="E177" s="8"/>
       <c r="F177" s="8"/>
       <c r="G177" s="8"/>
@@ -7830,10 +7833,10 @@
       <c r="E179" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F179" s="13" t="s">
+      <c r="F179" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G179" s="13" t="s">
+      <c r="G179" s="14" t="s">
         <v>69</v>
       </c>
       <c r="H179" s="8" t="s">
@@ -7862,7 +7865,7 @@
       <c r="A180" s="5"/>
       <c r="B180" s="8"/>
       <c r="C180" s="8"/>
-      <c r="D180" s="10"/>
+      <c r="D180" s="11"/>
       <c r="E180" s="8"/>
       <c r="F180" s="8"/>
       <c r="G180" s="8"/>
@@ -7890,7 +7893,7 @@
       <c r="A181" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B181" s="14">
+      <c r="B181" s="15">
         <v>27.0</v>
       </c>
       <c r="C181" s="8" t="s">
@@ -7902,10 +7905,10 @@
       <c r="E181" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F181" s="13" t="s">
+      <c r="F181" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G181" s="13" t="s">
+      <c r="G181" s="14" t="s">
         <v>69</v>
       </c>
       <c r="H181" s="6" t="s">
@@ -7934,7 +7937,7 @@
       <c r="A182" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B182" s="14">
+      <c r="B182" s="15">
         <v>26.0</v>
       </c>
       <c r="C182" s="8" t="s">
@@ -7946,10 +7949,10 @@
       <c r="E182" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F182" s="13" t="s">
+      <c r="F182" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G182" s="13" t="s">
+      <c r="G182" s="14" t="s">
         <v>69</v>
       </c>
       <c r="H182" s="6" t="s">
@@ -7978,7 +7981,7 @@
       <c r="A183" s="5"/>
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
-      <c r="D183" s="10"/>
+      <c r="D183" s="11"/>
       <c r="E183" s="8"/>
       <c r="F183" s="8"/>
       <c r="G183" s="8"/>
@@ -8006,7 +8009,7 @@
       <c r="A184" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B184" s="14">
+      <c r="B184" s="15">
         <v>27.0</v>
       </c>
       <c r="C184" s="8" t="s">
@@ -8018,10 +8021,10 @@
       <c r="E184" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F184" s="13" t="s">
+      <c r="F184" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G184" s="13" t="s">
+      <c r="G184" s="14" t="s">
         <v>69</v>
       </c>
       <c r="H184" s="8" t="s">
@@ -8050,7 +8053,7 @@
       <c r="A185" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B185" s="14">
+      <c r="B185" s="15">
         <v>26.0</v>
       </c>
       <c r="C185" s="8" t="s">
@@ -8062,10 +8065,10 @@
       <c r="E185" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F185" s="13" t="s">
+      <c r="F185" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G185" s="13" t="s">
+      <c r="G185" s="14" t="s">
         <v>69</v>
       </c>
       <c r="H185" s="8" t="s">
@@ -8091,32 +8094,32 @@
       <c r="Z185" s="9"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="15"/>
-      <c r="B186" s="12"/>
-      <c r="C186" s="12"/>
-      <c r="D186" s="16"/>
-      <c r="E186" s="12"/>
-      <c r="F186" s="12"/>
-      <c r="G186" s="12"/>
-      <c r="H186" s="12"/>
-      <c r="I186" s="12"/>
-      <c r="J186" s="12"/>
-      <c r="K186" s="12"/>
-      <c r="L186" s="12"/>
-      <c r="M186" s="12"/>
-      <c r="N186" s="12"/>
-      <c r="O186" s="12"/>
-      <c r="P186" s="12"/>
-      <c r="Q186" s="12"/>
-      <c r="R186" s="12"/>
-      <c r="S186" s="12"/>
-      <c r="T186" s="12"/>
-      <c r="U186" s="12"/>
-      <c r="V186" s="12"/>
-      <c r="W186" s="12"/>
-      <c r="X186" s="12"/>
-      <c r="Y186" s="12"/>
-      <c r="Z186" s="17"/>
+      <c r="A186" s="16"/>
+      <c r="B186" s="13"/>
+      <c r="C186" s="13"/>
+      <c r="D186" s="17"/>
+      <c r="E186" s="13"/>
+      <c r="F186" s="13"/>
+      <c r="G186" s="13"/>
+      <c r="H186" s="13"/>
+      <c r="I186" s="13"/>
+      <c r="J186" s="13"/>
+      <c r="K186" s="13"/>
+      <c r="L186" s="13"/>
+      <c r="M186" s="13"/>
+      <c r="N186" s="13"/>
+      <c r="O186" s="13"/>
+      <c r="P186" s="13"/>
+      <c r="Q186" s="13"/>
+      <c r="R186" s="13"/>
+      <c r="S186" s="13"/>
+      <c r="T186" s="13"/>
+      <c r="U186" s="13"/>
+      <c r="V186" s="13"/>
+      <c r="W186" s="13"/>
+      <c r="X186" s="13"/>
+      <c r="Y186" s="13"/>
+      <c r="Z186" s="18"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="5" t="s">
@@ -8125,13 +8128,13 @@
       <c r="B187" s="8">
         <v>5.0</v>
       </c>
-      <c r="C187" s="12" t="s">
+      <c r="C187" s="13" t="s">
         <v>45</v>
       </c>
       <c r="D187" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E187" s="12" t="s">
+      <c r="E187" s="13" t="s">
         <v>46</v>
       </c>
       <c r="F187" s="8" t="s">
@@ -8140,7 +8143,7 @@
       <c r="G187" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H187" s="12" t="s">
+      <c r="H187" s="13" t="s">
         <v>46</v>
       </c>
       <c r="I187" s="8"/>
@@ -8169,13 +8172,13 @@
       <c r="B188" s="8">
         <v>19.0</v>
       </c>
-      <c r="C188" s="12" t="s">
+      <c r="C188" s="13" t="s">
         <v>45</v>
       </c>
       <c r="D188" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E188" s="12" t="s">
+      <c r="E188" s="13" t="s">
         <v>46</v>
       </c>
       <c r="F188" s="8" t="s">
@@ -8184,7 +8187,7 @@
       <c r="G188" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H188" s="12" t="s">
+      <c r="H188" s="13" t="s">
         <v>46</v>
       </c>
       <c r="I188" s="8"/>
@@ -8210,7 +8213,7 @@
       <c r="A189" s="5"/>
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
-      <c r="D189" s="10"/>
+      <c r="D189" s="11"/>
       <c r="E189" s="8"/>
       <c r="F189" s="8" t="s">
         <v>28</v>
@@ -8245,13 +8248,13 @@
       <c r="B190" s="8">
         <v>5.0</v>
       </c>
-      <c r="C190" s="12" t="s">
+      <c r="C190" s="13" t="s">
         <v>9</v>
       </c>
       <c r="D190" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E190" s="12" t="s">
+      <c r="E190" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F190" s="8" t="s">
@@ -8260,7 +8263,7 @@
       <c r="G190" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H190" s="12" t="s">
+      <c r="H190" s="13" t="s">
         <v>17</v>
       </c>
       <c r="I190" s="8"/>
@@ -8289,13 +8292,13 @@
       <c r="B191" s="8">
         <v>19.0</v>
       </c>
-      <c r="C191" s="12" t="s">
+      <c r="C191" s="13" t="s">
         <v>9</v>
       </c>
       <c r="D191" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E191" s="12" t="s">
+      <c r="E191" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F191" s="8" t="s">
@@ -8304,7 +8307,7 @@
       <c r="G191" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H191" s="12" t="s">
+      <c r="H191" s="13" t="s">
         <v>17</v>
       </c>
       <c r="I191" s="8"/>
@@ -8333,22 +8336,22 @@
       <c r="B192" s="8">
         <v>5.0</v>
       </c>
-      <c r="C192" s="12" t="s">
+      <c r="C192" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="D192" s="12" t="s">
+      <c r="D192" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E192" s="12" t="s">
+      <c r="E192" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F192" s="12" t="s">
+      <c r="F192" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G192" s="12" t="s">
+      <c r="G192" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="H192" s="12" t="s">
+      <c r="H192" s="13" t="s">
         <v>17</v>
       </c>
       <c r="I192" s="8"/>
@@ -8377,22 +8380,22 @@
       <c r="B193" s="8">
         <v>19.0</v>
       </c>
-      <c r="C193" s="12" t="s">
+      <c r="C193" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D193" s="12" t="s">
+      <c r="D193" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="E193" s="12" t="s">
+      <c r="E193" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F193" s="12" t="s">
+      <c r="F193" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G193" s="12" t="s">
+      <c r="G193" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="H193" s="12" t="s">
+      <c r="H193" s="13" t="s">
         <v>17</v>
       </c>
       <c r="I193" s="8"/>
@@ -8418,7 +8421,7 @@
       <c r="A194" s="5"/>
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
-      <c r="D194" s="10"/>
+      <c r="D194" s="11"/>
       <c r="E194" s="8"/>
       <c r="F194" s="8"/>
       <c r="G194" s="8"/>
@@ -8458,10 +8461,10 @@
       <c r="E195" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="F195" s="12" t="s">
+      <c r="F195" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G195" s="12" t="s">
+      <c r="G195" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H195" s="8" t="s">
@@ -8502,10 +8505,10 @@
       <c r="E196" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="F196" s="12" t="s">
+      <c r="F196" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G196" s="12" t="s">
+      <c r="G196" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H196" s="8" t="s">
@@ -8534,7 +8537,7 @@
       <c r="A197" s="5"/>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
-      <c r="D197" s="10"/>
+      <c r="D197" s="11"/>
       <c r="E197" s="8"/>
       <c r="F197" s="8"/>
       <c r="G197" s="8"/>
@@ -8574,10 +8577,10 @@
       <c r="E198" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F198" s="12" t="s">
+      <c r="F198" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G198" s="12" t="s">
+      <c r="G198" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H198" s="8" t="s">
@@ -8618,10 +8621,10 @@
       <c r="E199" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F199" s="12" t="s">
+      <c r="F199" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G199" s="12" t="s">
+      <c r="G199" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H199" s="8" t="s">
@@ -8650,7 +8653,7 @@
       <c r="A200" s="5"/>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
-      <c r="D200" s="10"/>
+      <c r="D200" s="11"/>
       <c r="E200" s="8"/>
       <c r="F200" s="8"/>
       <c r="G200" s="8"/>
@@ -8684,16 +8687,16 @@
       <c r="C201" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D201" s="10" t="s">
+      <c r="D201" s="11" t="s">
         <v>88</v>
       </c>
       <c r="E201" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F201" s="12" t="s">
+      <c r="F201" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G201" s="12" t="s">
+      <c r="G201" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H201" s="8" t="s">
@@ -8728,16 +8731,16 @@
       <c r="C202" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D202" s="10" t="s">
+      <c r="D202" s="11" t="s">
         <v>97</v>
       </c>
       <c r="E202" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F202" s="12" t="s">
+      <c r="F202" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G202" s="12" t="s">
+      <c r="G202" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H202" s="8" t="s">
@@ -8766,7 +8769,7 @@
       <c r="A203" s="5"/>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
-      <c r="D203" s="10"/>
+      <c r="D203" s="11"/>
       <c r="E203" s="8"/>
       <c r="F203" s="8"/>
       <c r="G203" s="8"/>
@@ -8800,16 +8803,16 @@
       <c r="C204" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D204" s="10" t="s">
+      <c r="D204" s="11" t="s">
         <v>88</v>
       </c>
       <c r="E204" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F204" s="12" t="s">
+      <c r="F204" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G204" s="12" t="s">
+      <c r="G204" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H204" s="8" t="s">
@@ -8844,16 +8847,16 @@
       <c r="C205" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D205" s="10" t="s">
+      <c r="D205" s="11" t="s">
         <v>97</v>
       </c>
       <c r="E205" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F205" s="12" t="s">
+      <c r="F205" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G205" s="12" t="s">
+      <c r="G205" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H205" s="8" t="s">
@@ -8882,7 +8885,7 @@
       <c r="A206" s="5"/>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
-      <c r="D206" s="10"/>
+      <c r="D206" s="11"/>
       <c r="E206" s="8"/>
       <c r="F206" s="8"/>
       <c r="G206" s="8"/>
@@ -8922,10 +8925,10 @@
       <c r="E207" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F207" s="12" t="s">
+      <c r="F207" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G207" s="12" t="s">
+      <c r="G207" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H207" s="8" t="s">
@@ -8966,10 +8969,10 @@
       <c r="E208" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F208" s="12" t="s">
+      <c r="F208" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G208" s="12" t="s">
+      <c r="G208" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H208" s="8" t="s">
@@ -8998,7 +9001,7 @@
       <c r="A209" s="5"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
-      <c r="D209" s="10"/>
+      <c r="D209" s="11"/>
       <c r="E209" s="8"/>
       <c r="F209" s="8"/>
       <c r="G209" s="8"/>
@@ -9038,10 +9041,10 @@
       <c r="E210" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F210" s="12" t="s">
+      <c r="F210" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G210" s="12" t="s">
+      <c r="G210" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H210" s="8" t="s">
@@ -9082,10 +9085,10 @@
       <c r="E211" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F211" s="12" t="s">
+      <c r="F211" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G211" s="12" t="s">
+      <c r="G211" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H211" s="8" t="s">
@@ -9114,7 +9117,7 @@
       <c r="A212" s="5"/>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
-      <c r="D212" s="10"/>
+      <c r="D212" s="11"/>
       <c r="E212" s="8"/>
       <c r="F212" s="8"/>
       <c r="G212" s="8"/>
@@ -9148,16 +9151,16 @@
       <c r="C213" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D213" s="10" t="s">
+      <c r="D213" s="11" t="s">
         <v>88</v>
       </c>
       <c r="E213" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F213" s="12" t="s">
+      <c r="F213" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G213" s="12" t="s">
+      <c r="G213" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H213" s="8" t="s">
@@ -9192,16 +9195,16 @@
       <c r="C214" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D214" s="10" t="s">
+      <c r="D214" s="11" t="s">
         <v>97</v>
       </c>
       <c r="E214" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F214" s="12" t="s">
+      <c r="F214" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G214" s="12" t="s">
+      <c r="G214" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H214" s="8" t="s">
@@ -9230,7 +9233,7 @@
       <c r="A215" s="5"/>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
-      <c r="D215" s="10"/>
+      <c r="D215" s="11"/>
       <c r="E215" s="8"/>
       <c r="F215" s="8"/>
       <c r="G215" s="8"/>
@@ -9346,7 +9349,7 @@
       <c r="A218" s="5"/>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
-      <c r="D218" s="10"/>
+      <c r="D218" s="11"/>
       <c r="E218" s="8"/>
       <c r="F218" s="8"/>
       <c r="G218" s="8"/>
@@ -9462,7 +9465,7 @@
       <c r="A221" s="5"/>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
-      <c r="D221" s="10"/>
+      <c r="D221" s="11"/>
       <c r="E221" s="8"/>
       <c r="F221" s="8"/>
       <c r="G221" s="8"/>
@@ -9493,7 +9496,7 @@
       <c r="B222" s="8">
         <v>17.0</v>
       </c>
-      <c r="C222" s="12" t="s">
+      <c r="C222" s="13" t="s">
         <v>66</v>
       </c>
       <c r="D222" s="8" t="s">
@@ -9502,10 +9505,10 @@
       <c r="E222" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F222" s="12" t="s">
+      <c r="F222" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G222" s="12" t="s">
+      <c r="G222" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H222" s="8" t="s">
@@ -9537,7 +9540,7 @@
       <c r="B223" s="8">
         <v>18.0</v>
       </c>
-      <c r="C223" s="12" t="s">
+      <c r="C223" s="13" t="s">
         <v>66</v>
       </c>
       <c r="D223" s="8" t="s">
@@ -9546,10 +9549,10 @@
       <c r="E223" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F223" s="12" t="s">
+      <c r="F223" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G223" s="12" t="s">
+      <c r="G223" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H223" s="8" t="s">
@@ -9581,13 +9584,13 @@
       <c r="B224" s="8">
         <v>17.0</v>
       </c>
-      <c r="C224" s="12" t="s">
+      <c r="C224" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D224" s="12" t="s">
+      <c r="D224" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="E224" s="12" t="s">
+      <c r="E224" s="13" t="s">
         <v>64</v>
       </c>
       <c r="F224" s="8" t="s">
@@ -9596,7 +9599,7 @@
       <c r="G224" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H224" s="12" t="s">
+      <c r="H224" s="13" t="s">
         <v>64</v>
       </c>
       <c r="I224" s="8"/>
@@ -9625,13 +9628,13 @@
       <c r="B225" s="8">
         <v>18.0</v>
       </c>
-      <c r="C225" s="12" t="s">
+      <c r="C225" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D225" s="12" t="s">
+      <c r="D225" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="E225" s="12" t="s">
+      <c r="E225" s="13" t="s">
         <v>64</v>
       </c>
       <c r="F225" s="8" t="s">
@@ -9640,7 +9643,7 @@
       <c r="G225" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H225" s="12" t="s">
+      <c r="H225" s="13" t="s">
         <v>64</v>
       </c>
       <c r="I225" s="8"/>
@@ -9666,7 +9669,7 @@
       <c r="A226" s="5"/>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
-      <c r="D226" s="10"/>
+      <c r="D226" s="11"/>
       <c r="E226" s="8"/>
       <c r="F226" s="8"/>
       <c r="G226" s="8"/>
@@ -9697,13 +9700,13 @@
       <c r="B227" s="8">
         <v>17.0</v>
       </c>
-      <c r="C227" s="12" t="s">
+      <c r="C227" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D227" s="12" t="s">
+      <c r="D227" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="E227" s="12" t="s">
+      <c r="E227" s="13" t="s">
         <v>60</v>
       </c>
       <c r="F227" s="8" t="s">
@@ -9712,7 +9715,7 @@
       <c r="G227" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H227" s="12" t="s">
+      <c r="H227" s="13" t="s">
         <v>60</v>
       </c>
       <c r="I227" s="8"/>
@@ -9741,13 +9744,13 @@
       <c r="B228" s="8">
         <v>18.0</v>
       </c>
-      <c r="C228" s="12" t="s">
+      <c r="C228" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D228" s="12" t="s">
+      <c r="D228" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="E228" s="12" t="s">
+      <c r="E228" s="13" t="s">
         <v>60</v>
       </c>
       <c r="F228" s="8" t="s">
@@ -9756,7 +9759,7 @@
       <c r="G228" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H228" s="12" t="s">
+      <c r="H228" s="13" t="s">
         <v>60</v>
       </c>
       <c r="I228" s="8"/>
@@ -9782,7 +9785,7 @@
       <c r="A229" s="5"/>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
-      <c r="D229" s="10"/>
+      <c r="D229" s="11"/>
       <c r="E229" s="8"/>
       <c r="F229" s="8"/>
       <c r="G229" s="8"/>
@@ -9816,16 +9819,16 @@
       <c r="C230" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="D230" s="12" t="s">
+      <c r="D230" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="E230" s="12" t="s">
+      <c r="E230" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F230" s="12" t="s">
+      <c r="F230" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G230" s="12" t="s">
+      <c r="G230" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H230" s="8" t="s">
@@ -9860,16 +9863,16 @@
       <c r="C231" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="D231" s="12" t="s">
+      <c r="D231" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="E231" s="12" t="s">
+      <c r="E231" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F231" s="12" t="s">
+      <c r="F231" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G231" s="12" t="s">
+      <c r="G231" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H231" s="8" t="s">
@@ -9898,7 +9901,7 @@
       <c r="A232" s="5"/>
       <c r="B232" s="8"/>
       <c r="C232" s="8"/>
-      <c r="D232" s="10"/>
+      <c r="D232" s="11"/>
       <c r="E232" s="8"/>
       <c r="F232" s="8"/>
       <c r="G232" s="8"/>
@@ -9932,16 +9935,16 @@
       <c r="C233" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D233" s="12" t="s">
+      <c r="D233" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="E233" s="12" t="s">
+      <c r="E233" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F233" s="12" t="s">
+      <c r="F233" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G233" s="12" t="s">
+      <c r="G233" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H233" s="8" t="s">
@@ -9976,16 +9979,16 @@
       <c r="C234" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D234" s="12" t="s">
+      <c r="D234" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="E234" s="12" t="s">
+      <c r="E234" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F234" s="12" t="s">
+      <c r="F234" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G234" s="12" t="s">
+      <c r="G234" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H234" s="8" t="s">
@@ -10011,32 +10014,32 @@
       <c r="Z234" s="9"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="15"/>
-      <c r="B235" s="12"/>
-      <c r="C235" s="12"/>
-      <c r="D235" s="16"/>
-      <c r="E235" s="12"/>
-      <c r="F235" s="12"/>
-      <c r="G235" s="12"/>
-      <c r="H235" s="12"/>
-      <c r="I235" s="12"/>
-      <c r="J235" s="12"/>
-      <c r="K235" s="12"/>
-      <c r="L235" s="12"/>
-      <c r="M235" s="12"/>
-      <c r="N235" s="12"/>
-      <c r="O235" s="12"/>
-      <c r="P235" s="12"/>
-      <c r="Q235" s="12"/>
-      <c r="R235" s="12"/>
-      <c r="S235" s="12"/>
-      <c r="T235" s="12"/>
-      <c r="U235" s="12"/>
-      <c r="V235" s="12"/>
-      <c r="W235" s="12"/>
-      <c r="X235" s="12"/>
-      <c r="Y235" s="12"/>
-      <c r="Z235" s="17"/>
+      <c r="A235" s="16"/>
+      <c r="B235" s="13"/>
+      <c r="C235" s="13"/>
+      <c r="D235" s="17"/>
+      <c r="E235" s="13"/>
+      <c r="F235" s="13"/>
+      <c r="G235" s="13"/>
+      <c r="H235" s="13"/>
+      <c r="I235" s="13"/>
+      <c r="J235" s="13"/>
+      <c r="K235" s="13"/>
+      <c r="L235" s="13"/>
+      <c r="M235" s="13"/>
+      <c r="N235" s="13"/>
+      <c r="O235" s="13"/>
+      <c r="P235" s="13"/>
+      <c r="Q235" s="13"/>
+      <c r="R235" s="13"/>
+      <c r="S235" s="13"/>
+      <c r="T235" s="13"/>
+      <c r="U235" s="13"/>
+      <c r="V235" s="13"/>
+      <c r="W235" s="13"/>
+      <c r="X235" s="13"/>
+      <c r="Y235" s="13"/>
+      <c r="Z235" s="18"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="5" t="s">
@@ -10130,7 +10133,7 @@
       <c r="A238" s="5"/>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
-      <c r="D238" s="10"/>
+      <c r="D238" s="11"/>
       <c r="E238" s="8"/>
       <c r="F238" s="8"/>
       <c r="G238" s="8"/>
@@ -10334,7 +10337,7 @@
       <c r="A243" s="5"/>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
-      <c r="D243" s="10"/>
+      <c r="D243" s="11"/>
       <c r="E243" s="8"/>
       <c r="F243" s="8"/>
       <c r="G243" s="8"/>
@@ -10450,7 +10453,7 @@
       <c r="A246" s="5"/>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
-      <c r="D246" s="10"/>
+      <c r="D246" s="11"/>
       <c r="E246" s="8"/>
       <c r="F246" s="8"/>
       <c r="G246" s="8"/>
@@ -10566,7 +10569,7 @@
       <c r="A249" s="5"/>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
-      <c r="D249" s="10"/>
+      <c r="D249" s="11"/>
       <c r="E249" s="8"/>
       <c r="F249" s="8"/>
       <c r="G249" s="8"/>
@@ -10682,7 +10685,7 @@
       <c r="A252" s="5"/>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
-      <c r="D252" s="10"/>
+      <c r="D252" s="11"/>
       <c r="E252" s="8"/>
       <c r="F252" s="8"/>
       <c r="G252" s="8"/>
@@ -10798,7 +10801,7 @@
       <c r="A255" s="5"/>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
-      <c r="D255" s="10"/>
+      <c r="D255" s="11"/>
       <c r="E255" s="8"/>
       <c r="F255" s="8"/>
       <c r="G255" s="8"/>
@@ -10914,7 +10917,7 @@
       <c r="A258" s="5"/>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
-      <c r="D258" s="10"/>
+      <c r="D258" s="11"/>
       <c r="E258" s="8"/>
       <c r="F258" s="8"/>
       <c r="G258" s="8"/>
@@ -11030,7 +11033,7 @@
       <c r="A261" s="5"/>
       <c r="B261" s="8"/>
       <c r="C261" s="8"/>
-      <c r="D261" s="10"/>
+      <c r="D261" s="11"/>
       <c r="E261" s="8"/>
       <c r="F261" s="8"/>
       <c r="G261" s="8"/>
@@ -11146,7 +11149,7 @@
       <c r="A264" s="5"/>
       <c r="B264" s="8"/>
       <c r="C264" s="8"/>
-      <c r="D264" s="10"/>
+      <c r="D264" s="11"/>
       <c r="E264" s="8"/>
       <c r="F264" s="8"/>
       <c r="G264" s="8"/>
@@ -11262,7 +11265,7 @@
       <c r="A267" s="5"/>
       <c r="B267" s="8"/>
       <c r="C267" s="8"/>
-      <c r="D267" s="10"/>
+      <c r="D267" s="11"/>
       <c r="E267" s="8"/>
       <c r="F267" s="8"/>
       <c r="G267" s="8"/>
@@ -11296,7 +11299,7 @@
       <c r="C268" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D268" s="13" t="s">
+      <c r="D268" s="14" t="s">
         <v>106</v>
       </c>
       <c r="E268" s="8" t="s">
@@ -11340,7 +11343,7 @@
       <c r="C269" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D269" s="13" t="s">
+      <c r="D269" s="14" t="s">
         <v>106</v>
       </c>
       <c r="E269" s="8" t="s">
@@ -11378,7 +11381,7 @@
       <c r="A270" s="5"/>
       <c r="B270" s="8"/>
       <c r="C270" s="8"/>
-      <c r="D270" s="10"/>
+      <c r="D270" s="11"/>
       <c r="E270" s="8"/>
       <c r="F270" s="8"/>
       <c r="G270" s="8"/>
@@ -11735,13 +11738,13 @@
       <c r="D279" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="E279" s="12" t="s">
+      <c r="E279" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F279" s="12" t="s">
+      <c r="F279" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="G279" s="12" t="s">
+      <c r="G279" s="13" t="s">
         <v>113</v>
       </c>
       <c r="H279" s="8" t="s">
@@ -11776,16 +11779,16 @@
       <c r="C280" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="D280" s="12" t="s">
+      <c r="D280" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="E280" s="12" t="s">
+      <c r="E280" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F280" s="12" t="s">
+      <c r="F280" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="G280" s="12" t="s">
+      <c r="G280" s="13" t="s">
         <v>113</v>
       </c>
       <c r="H280" s="8" t="s">
@@ -11851,13 +11854,13 @@
       <c r="D282" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="E282" s="12" t="s">
+      <c r="E282" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F282" s="12" t="s">
+      <c r="F282" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="G282" s="12" t="s">
+      <c r="G282" s="13" t="s">
         <v>113</v>
       </c>
       <c r="H282" s="8" t="s">
@@ -11892,16 +11895,16 @@
       <c r="C283" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D283" s="12" t="s">
+      <c r="D283" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="E283" s="12" t="s">
+      <c r="E283" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F283" s="12" t="s">
+      <c r="F283" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="G283" s="12" t="s">
+      <c r="G283" s="13" t="s">
         <v>113</v>
       </c>
       <c r="H283" s="8" t="s">
@@ -11927,32 +11930,32 @@
       <c r="Z283" s="9"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
-      <c r="A284" s="15"/>
-      <c r="B284" s="12"/>
-      <c r="C284" s="12"/>
-      <c r="D284" s="12"/>
-      <c r="E284" s="12"/>
-      <c r="F284" s="12"/>
-      <c r="G284" s="12"/>
-      <c r="H284" s="12"/>
-      <c r="I284" s="12"/>
-      <c r="J284" s="12"/>
-      <c r="K284" s="12"/>
-      <c r="L284" s="12"/>
-      <c r="M284" s="12"/>
-      <c r="N284" s="12"/>
-      <c r="O284" s="12"/>
-      <c r="P284" s="12"/>
-      <c r="Q284" s="12"/>
-      <c r="R284" s="12"/>
-      <c r="S284" s="12"/>
-      <c r="T284" s="12"/>
-      <c r="U284" s="12"/>
-      <c r="V284" s="12"/>
-      <c r="W284" s="12"/>
-      <c r="X284" s="12"/>
-      <c r="Y284" s="12"/>
-      <c r="Z284" s="17"/>
+      <c r="A284" s="16"/>
+      <c r="B284" s="13"/>
+      <c r="C284" s="13"/>
+      <c r="D284" s="13"/>
+      <c r="E284" s="13"/>
+      <c r="F284" s="13"/>
+      <c r="G284" s="13"/>
+      <c r="H284" s="13"/>
+      <c r="I284" s="13"/>
+      <c r="J284" s="13"/>
+      <c r="K284" s="13"/>
+      <c r="L284" s="13"/>
+      <c r="M284" s="13"/>
+      <c r="N284" s="13"/>
+      <c r="O284" s="13"/>
+      <c r="P284" s="13"/>
+      <c r="Q284" s="13"/>
+      <c r="R284" s="13"/>
+      <c r="S284" s="13"/>
+      <c r="T284" s="13"/>
+      <c r="U284" s="13"/>
+      <c r="V284" s="13"/>
+      <c r="W284" s="13"/>
+      <c r="X284" s="13"/>
+      <c r="Y284" s="13"/>
+      <c r="Z284" s="18"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
       <c r="A285" s="5"/>
@@ -11986,25 +11989,25 @@
       <c r="A286" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B286" s="12">
+      <c r="B286" s="13">
         <v>7.0</v>
       </c>
-      <c r="C286" s="12" t="s">
+      <c r="C286" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D286" s="12" t="s">
+      <c r="D286" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="E286" s="12" t="s">
+      <c r="E286" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="F286" s="12" t="s">
+      <c r="F286" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G286" s="12" t="s">
+      <c r="G286" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="H286" s="12" t="s">
+      <c r="H286" s="13" t="s">
         <v>46</v>
       </c>
       <c r="I286" s="8"/>
@@ -12030,25 +12033,25 @@
       <c r="A287" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B287" s="12">
+      <c r="B287" s="13">
         <v>14.0</v>
       </c>
-      <c r="C287" s="12" t="s">
+      <c r="C287" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D287" s="12" t="s">
+      <c r="D287" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="E287" s="12" t="s">
+      <c r="E287" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="F287" s="12" t="s">
+      <c r="F287" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G287" s="12" t="s">
+      <c r="G287" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="H287" s="12" t="s">
+      <c r="H287" s="13" t="s">
         <v>46</v>
       </c>
       <c r="I287" s="8"/>
@@ -12102,25 +12105,25 @@
       <c r="A289" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B289" s="12">
+      <c r="B289" s="13">
         <v>7.0</v>
       </c>
-      <c r="C289" s="12" t="s">
+      <c r="C289" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D289" s="12" t="s">
+      <c r="D289" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="E289" s="12" t="s">
+      <c r="E289" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F289" s="12" t="s">
+      <c r="F289" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G289" s="12" t="s">
+      <c r="G289" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="H289" s="12" t="s">
+      <c r="H289" s="13" t="s">
         <v>17</v>
       </c>
       <c r="I289" s="8"/>
@@ -12146,25 +12149,25 @@
       <c r="A290" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B290" s="12">
+      <c r="B290" s="13">
         <v>14.0</v>
       </c>
-      <c r="C290" s="12" t="s">
+      <c r="C290" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D290" s="12" t="s">
+      <c r="D290" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="E290" s="12" t="s">
+      <c r="E290" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F290" s="12" t="s">
+      <c r="F290" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G290" s="12" t="s">
+      <c r="G290" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="H290" s="12" t="s">
+      <c r="H290" s="13" t="s">
         <v>17</v>
       </c>
       <c r="I290" s="8"/>
@@ -12190,16 +12193,16 @@
       <c r="A291" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B291" s="12">
+      <c r="B291" s="13">
         <v>7.0</v>
       </c>
-      <c r="C291" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="D291" s="12" t="s">
+      <c r="C291" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D291" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="E291" s="12" t="s">
+      <c r="E291" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F291" s="8" t="s">
@@ -12208,7 +12211,7 @@
       <c r="G291" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H291" s="12" t="s">
+      <c r="H291" s="13" t="s">
         <v>17</v>
       </c>
       <c r="I291" s="8"/>
@@ -12234,16 +12237,16 @@
       <c r="A292" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B292" s="12">
+      <c r="B292" s="13">
         <v>14.0</v>
       </c>
-      <c r="C292" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="D292" s="12" t="s">
+      <c r="C292" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D292" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="E292" s="12" t="s">
+      <c r="E292" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F292" s="8" t="s">
@@ -12252,7 +12255,7 @@
       <c r="G292" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H292" s="12" t="s">
+      <c r="H292" s="13" t="s">
         <v>17</v>
       </c>
       <c r="I292" s="8"/>
@@ -12309,22 +12312,22 @@
       <c r="B294" s="8">
         <v>5.0</v>
       </c>
-      <c r="C294" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="D294" s="12" t="s">
+      <c r="C294" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D294" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E294" s="12" t="s">
+      <c r="E294" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="F294" s="12" t="s">
+      <c r="F294" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G294" s="12" t="s">
+      <c r="G294" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="H294" s="12" t="s">
+      <c r="H294" s="13" t="s">
         <v>71</v>
       </c>
       <c r="I294" s="8"/>
@@ -12353,22 +12356,22 @@
       <c r="B295" s="8">
         <v>6.0</v>
       </c>
-      <c r="C295" s="12" t="s">
+      <c r="C295" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D295" s="12" t="s">
+      <c r="D295" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E295" s="12" t="s">
+      <c r="E295" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="F295" s="12" t="s">
+      <c r="F295" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G295" s="12" t="s">
+      <c r="G295" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="H295" s="12" t="s">
+      <c r="H295" s="13" t="s">
         <v>71</v>
       </c>
       <c r="I295" s="8"/>
@@ -12425,22 +12428,22 @@
       <c r="B297" s="8">
         <v>5.0</v>
       </c>
-      <c r="C297" s="12" t="s">
+      <c r="C297" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D297" s="12" t="s">
+      <c r="D297" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E297" s="12" t="s">
+      <c r="E297" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="F297" s="12" t="s">
+      <c r="F297" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G297" s="12" t="s">
+      <c r="G297" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="H297" s="12" t="s">
+      <c r="H297" s="13" t="s">
         <v>75</v>
       </c>
       <c r="I297" s="8"/>
@@ -12469,22 +12472,22 @@
       <c r="B298" s="8">
         <v>6.0</v>
       </c>
-      <c r="C298" s="12" t="s">
+      <c r="C298" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D298" s="12" t="s">
+      <c r="D298" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E298" s="12" t="s">
+      <c r="E298" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="F298" s="12" t="s">
+      <c r="F298" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G298" s="12" t="s">
+      <c r="G298" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="H298" s="12" t="s">
+      <c r="H298" s="13" t="s">
         <v>75</v>
       </c>
       <c r="I298" s="8"/>
@@ -12544,16 +12547,16 @@
       <c r="C300" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D300" s="12" t="s">
+      <c r="D300" s="13" t="s">
         <v>32</v>
       </c>
       <c r="E300" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F300" s="12" t="s">
+      <c r="F300" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G300" s="12" t="s">
+      <c r="G300" s="13" t="s">
         <v>120</v>
       </c>
       <c r="H300" s="8" t="s">
@@ -12588,16 +12591,16 @@
       <c r="C301" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D301" s="12" t="s">
+      <c r="D301" s="13" t="s">
         <v>39</v>
       </c>
       <c r="E301" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F301" s="12" t="s">
+      <c r="F301" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G301" s="12" t="s">
+      <c r="G301" s="13" t="s">
         <v>120</v>
       </c>
       <c r="H301" s="8" t="s">
@@ -12660,16 +12663,16 @@
       <c r="C303" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D303" s="12" t="s">
+      <c r="D303" s="13" t="s">
         <v>32</v>
       </c>
       <c r="E303" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F303" s="12" t="s">
+      <c r="F303" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G303" s="12" t="s">
+      <c r="G303" s="13" t="s">
         <v>120</v>
       </c>
       <c r="H303" s="8" t="s">
@@ -12704,16 +12707,16 @@
       <c r="C304" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D304" s="12" t="s">
+      <c r="D304" s="13" t="s">
         <v>39</v>
       </c>
       <c r="E304" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F304" s="12" t="s">
+      <c r="F304" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G304" s="12" t="s">
+      <c r="G304" s="13" t="s">
         <v>120</v>
       </c>
       <c r="H304" s="8" t="s">
@@ -12776,19 +12779,19 @@
       <c r="C306" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D306" s="12" t="s">
+      <c r="D306" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E306" s="12" t="s">
+      <c r="E306" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F306" s="12" t="s">
+      <c r="F306" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G306" s="12" t="s">
+      <c r="G306" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="H306" s="12" t="s">
+      <c r="H306" s="13" t="s">
         <v>17</v>
       </c>
       <c r="I306" s="8"/>
@@ -12820,19 +12823,19 @@
       <c r="C307" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D307" s="12" t="s">
+      <c r="D307" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E307" s="12" t="s">
+      <c r="E307" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F307" s="12" t="s">
+      <c r="F307" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G307" s="12" t="s">
+      <c r="G307" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="H307" s="12" t="s">
+      <c r="H307" s="13" t="s">
         <v>17</v>
       </c>
       <c r="I307" s="8"/>
@@ -12861,13 +12864,13 @@
       <c r="B308" s="8">
         <v>5.0</v>
       </c>
-      <c r="C308" s="12" t="s">
+      <c r="C308" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D308" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E308" s="12" t="s">
+      <c r="D308" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E308" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F308" s="8" t="s">
@@ -12876,7 +12879,7 @@
       <c r="G308" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H308" s="12" t="s">
+      <c r="H308" s="13" t="s">
         <v>17</v>
       </c>
       <c r="I308" s="8"/>
@@ -12905,13 +12908,13 @@
       <c r="B309" s="8">
         <v>6.0</v>
       </c>
-      <c r="C309" s="12" t="s">
+      <c r="C309" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D309" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E309" s="12" t="s">
+      <c r="D309" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E309" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F309" s="8" t="s">
@@ -12920,7 +12923,7 @@
       <c r="G309" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H309" s="12" t="s">
+      <c r="H309" s="13" t="s">
         <v>17</v>
       </c>
       <c r="I309" s="8"/>
@@ -12977,22 +12980,22 @@
       <c r="B311" s="8">
         <v>12.0</v>
       </c>
-      <c r="C311" s="12" t="s">
+      <c r="C311" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D311" s="12" t="s">
+      <c r="D311" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E311" s="12" t="s">
+      <c r="E311" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F311" s="12" t="s">
+      <c r="F311" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G311" s="12" t="s">
+      <c r="G311" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="H311" s="12" t="s">
+      <c r="H311" s="13" t="s">
         <v>48</v>
       </c>
       <c r="I311" s="8"/>
@@ -13021,22 +13024,22 @@
       <c r="B312" s="8">
         <v>13.0</v>
       </c>
-      <c r="C312" s="12" t="s">
+      <c r="C312" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D312" s="12" t="s">
+      <c r="D312" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E312" s="12" t="s">
+      <c r="E312" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F312" s="12" t="s">
+      <c r="F312" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G312" s="12" t="s">
+      <c r="G312" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="H312" s="12" t="s">
+      <c r="H312" s="13" t="s">
         <v>48</v>
       </c>
       <c r="I312" s="8"/>
@@ -13093,19 +13096,19 @@
       <c r="B314" s="8">
         <v>12.0</v>
       </c>
-      <c r="C314" s="12" t="s">
+      <c r="C314" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D314" s="12" t="s">
+      <c r="D314" s="13" t="s">
         <v>32</v>
       </c>
       <c r="E314" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F314" s="12" t="s">
+      <c r="F314" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G314" s="12" t="s">
+      <c r="G314" s="13" t="s">
         <v>120</v>
       </c>
       <c r="H314" s="8" t="s">
@@ -13137,19 +13140,19 @@
       <c r="B315" s="8">
         <v>13.0</v>
       </c>
-      <c r="C315" s="12" t="s">
+      <c r="C315" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D315" s="12" t="s">
+      <c r="D315" s="13" t="s">
         <v>39</v>
       </c>
       <c r="E315" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F315" s="12" t="s">
+      <c r="F315" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G315" s="12" t="s">
+      <c r="G315" s="13" t="s">
         <v>120</v>
       </c>
       <c r="H315" s="8" t="s">
@@ -13209,13 +13212,13 @@
       <c r="B317" s="8">
         <v>12.0</v>
       </c>
-      <c r="C317" s="12" t="s">
+      <c r="C317" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D317" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="E317" s="12" t="s">
+      <c r="D317" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E317" s="13" t="s">
         <v>53</v>
       </c>
       <c r="F317" s="8" t="s">
@@ -13224,7 +13227,7 @@
       <c r="G317" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H317" s="12" t="s">
+      <c r="H317" s="13" t="s">
         <v>53</v>
       </c>
       <c r="I317" s="8"/>
@@ -13253,13 +13256,13 @@
       <c r="B318" s="8">
         <v>13.0</v>
       </c>
-      <c r="C318" s="12" t="s">
+      <c r="C318" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D318" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="E318" s="12" t="s">
+      <c r="D318" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E318" s="13" t="s">
         <v>53</v>
       </c>
       <c r="F318" s="8" t="s">
@@ -13268,7 +13271,7 @@
       <c r="G318" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H318" s="12" t="s">
+      <c r="H318" s="13" t="s">
         <v>53</v>
       </c>
       <c r="I318" s="8"/>
@@ -13328,16 +13331,16 @@
       <c r="C320" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D320" s="12" t="s">
+      <c r="D320" s="13" t="s">
         <v>32</v>
       </c>
       <c r="E320" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F320" s="12" t="s">
+      <c r="F320" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G320" s="12" t="s">
+      <c r="G320" s="13" t="s">
         <v>120</v>
       </c>
       <c r="H320" s="8" t="s">
@@ -13372,16 +13375,16 @@
       <c r="C321" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D321" s="12" t="s">
+      <c r="D321" s="13" t="s">
         <v>39</v>
       </c>
       <c r="E321" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F321" s="12" t="s">
+      <c r="F321" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G321" s="12" t="s">
+      <c r="G321" s="13" t="s">
         <v>120</v>
       </c>
       <c r="H321" s="8" t="s">
@@ -13416,8 +13419,8 @@
       <c r="C322" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D322" s="12" t="s">
-        <v>123</v>
+      <c r="D322" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="E322" s="8" t="s">
         <v>64</v>
@@ -13460,8 +13463,8 @@
       <c r="C323" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D323" s="12" t="s">
-        <v>123</v>
+      <c r="D323" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="E323" s="8" t="s">
         <v>64</v>
@@ -13533,7 +13536,7 @@
         <v>61</v>
       </c>
       <c r="D325" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E325" s="8" t="s">
         <v>60</v>
@@ -13577,7 +13580,7 @@
         <v>61</v>
       </c>
       <c r="D326" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E326" s="8" t="s">
         <v>60</v>
@@ -13642,22 +13645,22 @@
       <c r="A328" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B328" s="12">
+      <c r="B328" s="13">
         <v>12.0</v>
       </c>
       <c r="C328" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="D328" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E328" s="12" t="s">
+      <c r="D328" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E328" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F328" s="12" t="s">
+      <c r="F328" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G328" s="12" t="s">
+      <c r="G328" s="13" t="s">
         <v>120</v>
       </c>
       <c r="H328" s="8" t="s">
@@ -13686,22 +13689,22 @@
       <c r="A329" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B329" s="12">
+      <c r="B329" s="13">
         <v>13.0</v>
       </c>
       <c r="C329" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="D329" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="E329" s="12" t="s">
+      <c r="D329" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E329" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F329" s="12" t="s">
+      <c r="F329" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G329" s="12" t="s">
+      <c r="G329" s="13" t="s">
         <v>120</v>
       </c>
       <c r="H329" s="8" t="s">
@@ -13758,22 +13761,22 @@
       <c r="A331" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B331" s="12">
+      <c r="B331" s="13">
         <v>12.0</v>
       </c>
       <c r="C331" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D331" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E331" s="12" t="s">
+      <c r="D331" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E331" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F331" s="12" t="s">
+      <c r="F331" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G331" s="12" t="s">
+      <c r="G331" s="13" t="s">
         <v>120</v>
       </c>
       <c r="H331" s="8" t="s">
@@ -13802,22 +13805,22 @@
       <c r="A332" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B332" s="12">
+      <c r="B332" s="13">
         <v>13.0</v>
       </c>
       <c r="C332" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D332" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="E332" s="12" t="s">
+      <c r="D332" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E332" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F332" s="12" t="s">
+      <c r="F332" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G332" s="12" t="s">
+      <c r="G332" s="13" t="s">
         <v>120</v>
       </c>
       <c r="H332" s="8" t="s">

--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="124">
   <si>
     <t>MÊS</t>
   </si>
@@ -217,12 +217,6 @@
     <t xml:space="preserve">Tricologia e Terapia Capilares Avançadas - Prática </t>
   </si>
   <si>
-    <t>02/10/2026 a 06/10/2026</t>
-  </si>
-  <si>
-    <t>16/10/2026 a 20/10/2026</t>
-  </si>
-  <si>
     <t>PROINSU BA 220225</t>
   </si>
   <si>
@@ -263,6 +257,12 @@
   </si>
   <si>
     <t>Setembro</t>
+  </si>
+  <si>
+    <t>02/10/2026 a 06/10/2026</t>
+  </si>
+  <si>
+    <t>16/10/2026 a 20/10/2026</t>
   </si>
   <si>
     <r>
@@ -4990,30 +4990,14 @@
       <c r="Z105" s="9"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B106" s="6">
-        <v>26.0</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D106" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E106" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F106" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G106" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>64</v>
-      </c>
+      <c r="A106" s="5"/>
+      <c r="B106" s="6"/>
+      <c r="C106" s="6"/>
+      <c r="D106" s="7"/>
+      <c r="E106" s="6"/>
+      <c r="F106" s="6"/>
+      <c r="G106" s="6"/>
+      <c r="H106" s="6"/>
       <c r="I106" s="8"/>
       <c r="J106" s="8"/>
       <c r="K106" s="8"/>
@@ -5062,30 +5046,14 @@
       <c r="Z107" s="9"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B108" s="6">
-        <v>27.0</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D108" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G108" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>64</v>
-      </c>
+      <c r="A108" s="5"/>
+      <c r="B108" s="6"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="7"/>
+      <c r="E108" s="6"/>
+      <c r="F108" s="6"/>
+      <c r="G108" s="6"/>
+      <c r="H108" s="6"/>
       <c r="I108" s="8"/>
       <c r="J108" s="8"/>
       <c r="K108" s="8"/>
@@ -5141,22 +5109,22 @@
         <v>4.0</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D110" s="7" t="s">
         <v>31</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I110" s="8"/>
       <c r="J110" s="8"/>
@@ -5185,7 +5153,7 @@
         <v>25.0</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D111" s="7" t="s">
         <v>56</v>
@@ -5197,10 +5165,10 @@
         <v>42</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I111" s="8"/>
       <c r="J111" s="8"/>
@@ -5229,7 +5197,7 @@
         <v>26.0</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D112" s="7" t="s">
         <v>29</v>
@@ -5241,10 +5209,10 @@
         <v>28</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I112" s="8"/>
       <c r="J112" s="8"/>
@@ -5273,13 +5241,13 @@
         <v>1.0</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D113" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F113" s="6" t="s">
         <v>44</v>
@@ -5288,7 +5256,7 @@
         <v>35</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I113" s="8"/>
       <c r="J113" s="8"/>
@@ -5317,13 +5285,13 @@
         <v>2.0</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D114" s="7" t="s">
         <v>37</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>44</v>
@@ -5332,7 +5300,7 @@
         <v>35</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I114" s="8"/>
       <c r="J114" s="8"/>
@@ -5445,22 +5413,22 @@
         <v>4.0</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D118" s="7" t="s">
         <v>16</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I118" s="8"/>
       <c r="J118" s="8"/>
@@ -5489,7 +5457,7 @@
         <v>25.0</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D119" s="7" t="s">
         <v>56</v>
@@ -5501,10 +5469,10 @@
         <v>28</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I119" s="8"/>
       <c r="J119" s="8"/>
@@ -5533,7 +5501,7 @@
         <v>26.0</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D120" s="7" t="s">
         <v>29</v>
@@ -5545,10 +5513,10 @@
         <v>28</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I120" s="8"/>
       <c r="J120" s="8"/>
@@ -5577,13 +5545,13 @@
         <v>1.0</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D121" s="7" t="s">
         <v>37</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F121" s="6" t="s">
         <v>44</v>
@@ -5592,7 +5560,7 @@
         <v>35</v>
       </c>
       <c r="H121" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I121" s="8"/>
       <c r="J121" s="8"/>
@@ -5621,13 +5589,13 @@
         <v>2.0</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D122" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>44</v>
@@ -5636,7 +5604,7 @@
         <v>35</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I122" s="8"/>
       <c r="J122" s="8"/>
@@ -5749,7 +5717,7 @@
         <v>25.0</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D126" s="7" t="s">
         <v>56</v>
@@ -5764,7 +5732,7 @@
         <v>35</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I126" s="8"/>
       <c r="J126" s="8"/>
@@ -5793,7 +5761,7 @@
         <v>26.0</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D127" s="7" t="s">
         <v>29</v>
@@ -5808,7 +5776,7 @@
         <v>35</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I127" s="8"/>
       <c r="J127" s="8"/>
@@ -5837,13 +5805,13 @@
         <v>1.0</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D128" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>44</v>
@@ -5852,7 +5820,7 @@
         <v>35</v>
       </c>
       <c r="H128" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I128" s="8"/>
       <c r="J128" s="8"/>
@@ -5881,13 +5849,13 @@
         <v>2.0</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D129" s="7" t="s">
         <v>37</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F129" s="6" t="s">
         <v>44</v>
@@ -5896,7 +5864,7 @@
         <v>35</v>
       </c>
       <c r="H129" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I129" s="8"/>
       <c r="J129" s="8"/>
@@ -6009,10 +5977,10 @@
         <v>22.0</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E133" s="6" t="s">
         <v>11</v>
@@ -6053,10 +6021,10 @@
         <v>23.0</v>
       </c>
       <c r="C134" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D134" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>11</v>
@@ -6125,10 +6093,10 @@
         <v>22.0</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>11</v>
@@ -6169,10 +6137,10 @@
         <v>23.0</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E137" s="6" t="s">
         <v>11</v>
@@ -6235,7 +6203,7 @@
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B139" s="13">
         <v>7.0</v>
@@ -6250,10 +6218,10 @@
         <v>46</v>
       </c>
       <c r="F139" s="13" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G139" s="13" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H139" s="13" t="s">
         <v>46</v>
@@ -6279,7 +6247,7 @@
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B140" s="13">
         <v>21.0</v>
@@ -6294,10 +6262,10 @@
         <v>46</v>
       </c>
       <c r="F140" s="13" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G140" s="13" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H140" s="13" t="s">
         <v>46</v>
@@ -6351,7 +6319,7 @@
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B142" s="13">
         <v>7.0</v>
@@ -6366,10 +6334,10 @@
         <v>17</v>
       </c>
       <c r="F142" s="13" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G142" s="13" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H142" s="13" t="s">
         <v>17</v>
@@ -6395,7 +6363,7 @@
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B143" s="13">
         <v>21.0</v>
@@ -6410,10 +6378,10 @@
         <v>17</v>
       </c>
       <c r="F143" s="13" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G143" s="13" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H143" s="13" t="s">
         <v>17</v>
@@ -6439,7 +6407,7 @@
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B144" s="13">
         <v>7.0</v>
@@ -6454,10 +6422,10 @@
         <v>17</v>
       </c>
       <c r="F144" s="13" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G144" s="13" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H144" s="13" t="s">
         <v>17</v>
@@ -6483,7 +6451,7 @@
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B145" s="13">
         <v>21.0</v>
@@ -6498,10 +6466,10 @@
         <v>17</v>
       </c>
       <c r="F145" s="13" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G145" s="13" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H145" s="13" t="s">
         <v>17</v>
@@ -6555,28 +6523,28 @@
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B147" s="8">
         <v>5.0</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D147" s="8" t="s">
         <v>86</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F147" s="14" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G147" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H147" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="H147" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="I147" s="8"/>
       <c r="J147" s="8"/>
@@ -6599,28 +6567,28 @@
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B148" s="8">
         <v>6.0</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D148" s="8" t="s">
         <v>87</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F148" s="14" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G148" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H148" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="H148" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="I148" s="8"/>
       <c r="J148" s="8"/>
@@ -6671,28 +6639,28 @@
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B150" s="8">
         <v>5.0</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D150" s="8" t="s">
         <v>88</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G150" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H150" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I150" s="8"/>
       <c r="J150" s="8"/>
@@ -6715,28 +6683,28 @@
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B151" s="8">
         <v>6.0</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D151" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H151" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I151" s="8"/>
       <c r="J151" s="8"/>
@@ -6787,7 +6755,7 @@
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B153" s="8">
         <v>5.0</v>
@@ -6799,16 +6767,16 @@
         <v>86</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F153" s="14" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G153" s="14" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H153" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I153" s="8"/>
       <c r="J153" s="8"/>
@@ -6831,7 +6799,7 @@
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B154" s="8">
         <v>6.0</v>
@@ -6843,16 +6811,16 @@
         <v>87</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F154" s="14" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G154" s="14" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H154" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I154" s="8"/>
       <c r="J154" s="8"/>
@@ -6903,7 +6871,7 @@
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B156" s="8">
         <v>12.0</v>
@@ -6918,10 +6886,10 @@
         <v>48</v>
       </c>
       <c r="F156" s="14" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G156" s="14" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H156" s="8" t="s">
         <v>28</v>
@@ -6947,7 +6915,7 @@
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B157" s="8">
         <v>13.0</v>
@@ -6962,10 +6930,10 @@
         <v>48</v>
       </c>
       <c r="F157" s="14" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G157" s="14" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H157" s="8" t="s">
         <v>28</v>
@@ -7019,7 +6987,7 @@
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B159" s="8">
         <v>12.0</v>
@@ -7037,7 +7005,7 @@
         <v>28</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H159" s="8" t="s">
         <v>41</v>
@@ -7063,7 +7031,7 @@
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B160" s="8">
         <v>13.0</v>
@@ -7081,7 +7049,7 @@
         <v>28</v>
       </c>
       <c r="G160" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H160" s="8" t="s">
         <v>41</v>
@@ -7135,7 +7103,7 @@
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B162" s="8">
         <v>19.0</v>
@@ -7153,7 +7121,7 @@
         <v>28</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H162" s="8" t="s">
         <v>51</v>
@@ -7179,7 +7147,7 @@
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B163" s="8">
         <v>20.0</v>
@@ -7197,7 +7165,7 @@
         <v>28</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H163" s="8" t="s">
         <v>51</v>
@@ -7251,7 +7219,7 @@
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B165" s="8">
         <v>19.0</v>
@@ -7269,7 +7237,7 @@
         <v>28</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H165" s="8" t="s">
         <v>17</v>
@@ -7295,7 +7263,7 @@
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B166" s="8">
         <v>20.0</v>
@@ -7310,10 +7278,10 @@
         <v>17</v>
       </c>
       <c r="F166" s="14" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G166" s="14" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H166" s="8" t="s">
         <v>17</v>
@@ -7339,7 +7307,7 @@
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B167" s="8">
         <v>19.0</v>
@@ -7354,10 +7322,10 @@
         <v>17</v>
       </c>
       <c r="F167" s="8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G167" s="8" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H167" s="8" t="s">
         <v>17</v>
@@ -7383,7 +7351,7 @@
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B168" s="8">
         <v>20.0</v>
@@ -7398,10 +7366,10 @@
         <v>17</v>
       </c>
       <c r="F168" s="8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H168" s="8" t="s">
         <v>17</v>
@@ -7455,7 +7423,7 @@
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B170" s="8">
         <v>26.0</v>
@@ -7470,10 +7438,10 @@
         <v>53</v>
       </c>
       <c r="F170" s="8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H170" s="8" t="s">
         <v>53</v>
@@ -7499,7 +7467,7 @@
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B171" s="8">
         <v>27.0</v>
@@ -7514,10 +7482,10 @@
         <v>53</v>
       </c>
       <c r="F171" s="8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G171" s="8" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H171" s="8" t="s">
         <v>53</v>
@@ -7571,7 +7539,7 @@
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B173" s="8">
         <v>26.0</v>
@@ -7589,7 +7557,7 @@
         <v>28</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H173" s="8" t="s">
         <v>64</v>
@@ -7615,7 +7583,7 @@
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B174" s="8">
         <v>27.0</v>
@@ -7633,7 +7601,7 @@
         <v>28</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H174" s="8" t="s">
         <v>64</v>
@@ -7659,7 +7627,7 @@
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B175" s="8">
         <v>26.0</v>
@@ -7674,10 +7642,10 @@
         <v>64</v>
       </c>
       <c r="F175" s="8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G175" s="8" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H175" s="8" t="s">
         <v>64</v>
@@ -7703,7 +7671,7 @@
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B176" s="8">
         <v>27.0</v>
@@ -7718,10 +7686,10 @@
         <v>64</v>
       </c>
       <c r="F176" s="8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G176" s="8" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H176" s="8" t="s">
         <v>64</v>
@@ -7775,7 +7743,7 @@
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B178" s="8">
         <v>26.0</v>
@@ -7790,10 +7758,10 @@
         <v>60</v>
       </c>
       <c r="F178" s="8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G178" s="8" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H178" s="8" t="s">
         <v>60</v>
@@ -7819,7 +7787,7 @@
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B179" s="8">
         <v>27.0</v>
@@ -7834,10 +7802,10 @@
         <v>60</v>
       </c>
       <c r="F179" s="14" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G179" s="14" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H179" s="8" t="s">
         <v>60</v>
@@ -7891,7 +7859,7 @@
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B181" s="15">
         <v>27.0</v>
@@ -7906,10 +7874,10 @@
         <v>11</v>
       </c>
       <c r="F181" s="14" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G181" s="14" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H181" s="6" t="s">
         <v>53</v>
@@ -7935,13 +7903,13 @@
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B182" s="15">
         <v>26.0</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D182" s="8" t="s">
         <v>95</v>
@@ -7950,10 +7918,10 @@
         <v>11</v>
       </c>
       <c r="F182" s="14" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G182" s="14" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H182" s="6" t="s">
         <v>53</v>
@@ -8007,13 +7975,13 @@
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B184" s="15">
         <v>27.0</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D184" s="8" t="s">
         <v>94</v>
@@ -8022,10 +7990,10 @@
         <v>11</v>
       </c>
       <c r="F184" s="14" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G184" s="14" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H184" s="8" t="s">
         <v>60</v>
@@ -8051,13 +8019,13 @@
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B185" s="15">
         <v>26.0</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D185" s="8" t="s">
         <v>95</v>
@@ -8066,10 +8034,10 @@
         <v>11</v>
       </c>
       <c r="F185" s="14" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G185" s="14" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H185" s="8" t="s">
         <v>60</v>
@@ -8141,7 +8109,7 @@
         <v>28</v>
       </c>
       <c r="G187" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H187" s="13" t="s">
         <v>46</v>
@@ -8185,7 +8153,7 @@
         <v>28</v>
       </c>
       <c r="G188" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H188" s="13" t="s">
         <v>46</v>
@@ -8219,7 +8187,7 @@
         <v>28</v>
       </c>
       <c r="G189" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H189" s="8"/>
       <c r="I189" s="8"/>
@@ -8261,7 +8229,7 @@
         <v>28</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H190" s="13" t="s">
         <v>17</v>
@@ -8305,7 +8273,7 @@
         <v>28</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H191" s="13" t="s">
         <v>17</v>
@@ -8453,13 +8421,13 @@
         <v>10.0</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D195" s="8" t="s">
         <v>88</v>
       </c>
       <c r="E195" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F195" s="13" t="s">
         <v>100</v>
@@ -8468,7 +8436,7 @@
         <v>101</v>
       </c>
       <c r="H195" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I195" s="8"/>
       <c r="J195" s="8"/>
@@ -8497,13 +8465,13 @@
         <v>11.0</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D196" s="8" t="s">
         <v>103</v>
       </c>
       <c r="E196" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F196" s="13" t="s">
         <v>100</v>
@@ -8512,7 +8480,7 @@
         <v>101</v>
       </c>
       <c r="H196" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I196" s="8"/>
       <c r="J196" s="8"/>
@@ -8569,13 +8537,13 @@
         <v>10.0</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D198" s="8" t="s">
         <v>104</v>
       </c>
       <c r="E198" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F198" s="13" t="s">
         <v>100</v>
@@ -8584,7 +8552,7 @@
         <v>101</v>
       </c>
       <c r="H198" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I198" s="8"/>
       <c r="J198" s="8"/>
@@ -8613,13 +8581,13 @@
         <v>11.0</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D199" s="8" t="s">
         <v>105</v>
       </c>
       <c r="E199" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F199" s="13" t="s">
         <v>100</v>
@@ -8628,7 +8596,7 @@
         <v>101</v>
       </c>
       <c r="H199" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I199" s="8"/>
       <c r="J199" s="8"/>
@@ -8691,7 +8659,7 @@
         <v>88</v>
       </c>
       <c r="E201" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F201" s="13" t="s">
         <v>100</v>
@@ -8700,7 +8668,7 @@
         <v>101</v>
       </c>
       <c r="H201" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I201" s="8"/>
       <c r="J201" s="8"/>
@@ -8735,7 +8703,7 @@
         <v>97</v>
       </c>
       <c r="E202" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F202" s="13" t="s">
         <v>100</v>
@@ -8744,7 +8712,7 @@
         <v>101</v>
       </c>
       <c r="H202" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I202" s="8"/>
       <c r="J202" s="8"/>
@@ -9277,7 +9245,7 @@
         <v>42</v>
       </c>
       <c r="G216" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H216" s="8" t="s">
         <v>17</v>
@@ -9321,7 +9289,7 @@
         <v>42</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H217" s="8" t="s">
         <v>17</v>
@@ -9393,7 +9361,7 @@
         <v>28</v>
       </c>
       <c r="G219" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H219" s="8" t="s">
         <v>53</v>
@@ -9437,7 +9405,7 @@
         <v>28</v>
       </c>
       <c r="G220" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H220" s="8" t="s">
         <v>53</v>
@@ -9597,7 +9565,7 @@
         <v>42</v>
       </c>
       <c r="G224" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H224" s="13" t="s">
         <v>64</v>
@@ -9641,7 +9609,7 @@
         <v>42</v>
       </c>
       <c r="G225" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H225" s="13" t="s">
         <v>64</v>
@@ -9713,7 +9681,7 @@
         <v>42</v>
       </c>
       <c r="G227" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H227" s="13" t="s">
         <v>60</v>
@@ -9757,7 +9725,7 @@
         <v>42</v>
       </c>
       <c r="G228" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H228" s="13" t="s">
         <v>60</v>
@@ -9817,7 +9785,7 @@
         <v>31.0</v>
       </c>
       <c r="C230" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D230" s="13" t="s">
         <v>108</v>
@@ -9861,7 +9829,7 @@
         <v>1.0</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D231" s="13" t="s">
         <v>110</v>
@@ -9977,7 +9945,7 @@
         <v>1.0</v>
       </c>
       <c r="C234" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D234" s="13" t="s">
         <v>110</v>
@@ -10265,7 +10233,7 @@
         <v>42</v>
       </c>
       <c r="G241" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H241" s="8" t="s">
         <v>17</v>
@@ -10309,7 +10277,7 @@
         <v>42</v>
       </c>
       <c r="G242" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H242" s="8" t="s">
         <v>17</v>
@@ -10369,13 +10337,13 @@
         <v>7.0</v>
       </c>
       <c r="C244" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D244" s="8" t="s">
         <v>104</v>
       </c>
       <c r="E244" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F244" s="8" t="s">
         <v>112</v>
@@ -10384,7 +10352,7 @@
         <v>113</v>
       </c>
       <c r="H244" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I244" s="8"/>
       <c r="J244" s="8"/>
@@ -10413,13 +10381,13 @@
         <v>8.0</v>
       </c>
       <c r="C245" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D245" s="8" t="s">
         <v>105</v>
       </c>
       <c r="E245" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F245" s="8" t="s">
         <v>112</v>
@@ -10428,7 +10396,7 @@
         <v>113</v>
       </c>
       <c r="H245" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I245" s="8"/>
       <c r="J245" s="8"/>
@@ -10485,13 +10453,13 @@
         <v>7.0</v>
       </c>
       <c r="C247" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D247" s="8" t="s">
         <v>86</v>
       </c>
       <c r="E247" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F247" s="8" t="s">
         <v>112</v>
@@ -10500,7 +10468,7 @@
         <v>113</v>
       </c>
       <c r="H247" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I247" s="8"/>
       <c r="J247" s="8"/>
@@ -10529,13 +10497,13 @@
         <v>8.0</v>
       </c>
       <c r="C248" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D248" s="8" t="s">
         <v>87</v>
       </c>
       <c r="E248" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F248" s="8" t="s">
         <v>112</v>
@@ -10544,7 +10512,7 @@
         <v>113</v>
       </c>
       <c r="H248" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I248" s="8"/>
       <c r="J248" s="8"/>
@@ -10607,7 +10575,7 @@
         <v>104</v>
       </c>
       <c r="E250" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F250" s="8" t="s">
         <v>112</v>
@@ -10616,7 +10584,7 @@
         <v>113</v>
       </c>
       <c r="H250" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I250" s="8"/>
       <c r="J250" s="8"/>
@@ -10651,7 +10619,7 @@
         <v>105</v>
       </c>
       <c r="E251" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F251" s="8" t="s">
         <v>112</v>
@@ -10660,7 +10628,7 @@
         <v>113</v>
       </c>
       <c r="H251" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I251" s="8"/>
       <c r="J251" s="8"/>
@@ -11193,7 +11161,7 @@
         <v>42</v>
       </c>
       <c r="G265" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H265" s="8" t="s">
         <v>17</v>
@@ -11237,7 +11205,7 @@
         <v>42</v>
       </c>
       <c r="G266" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H266" s="8" t="s">
         <v>17</v>
@@ -11309,7 +11277,7 @@
         <v>42</v>
       </c>
       <c r="G268" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H268" s="8" t="s">
         <v>53</v>
@@ -11353,7 +11321,7 @@
         <v>42</v>
       </c>
       <c r="G269" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H269" s="8" t="s">
         <v>53</v>
@@ -11513,7 +11481,7 @@
         <v>42</v>
       </c>
       <c r="G273" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H273" s="8" t="s">
         <v>64</v>
@@ -11557,7 +11525,7 @@
         <v>42</v>
       </c>
       <c r="G274" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H274" s="8" t="s">
         <v>64</v>
@@ -11629,7 +11597,7 @@
         <v>42</v>
       </c>
       <c r="G276" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H276" s="8" t="s">
         <v>60</v>
@@ -11673,7 +11641,7 @@
         <v>42</v>
       </c>
       <c r="G277" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H277" s="8" t="s">
         <v>60</v>
@@ -11733,7 +11701,7 @@
         <v>28.0</v>
       </c>
       <c r="C279" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D279" s="8" t="s">
         <v>116</v>
@@ -11777,7 +11745,7 @@
         <v>29.0</v>
       </c>
       <c r="C280" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D280" s="13" t="s">
         <v>117</v>
@@ -11893,7 +11861,7 @@
         <v>29.0</v>
       </c>
       <c r="C283" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D283" s="13" t="s">
         <v>117</v>
@@ -12209,7 +12177,7 @@
         <v>42</v>
       </c>
       <c r="G291" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H291" s="13" t="s">
         <v>17</v>
@@ -12253,7 +12221,7 @@
         <v>42</v>
       </c>
       <c r="G292" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H292" s="13" t="s">
         <v>17</v>
@@ -12319,7 +12287,7 @@
         <v>32</v>
       </c>
       <c r="E294" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F294" s="13" t="s">
         <v>119</v>
@@ -12328,7 +12296,7 @@
         <v>120</v>
       </c>
       <c r="H294" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I294" s="8"/>
       <c r="J294" s="8"/>
@@ -12357,13 +12325,13 @@
         <v>6.0</v>
       </c>
       <c r="C295" s="13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D295" s="13" t="s">
         <v>39</v>
       </c>
       <c r="E295" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F295" s="13" t="s">
         <v>119</v>
@@ -12372,7 +12340,7 @@
         <v>120</v>
       </c>
       <c r="H295" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I295" s="8"/>
       <c r="J295" s="8"/>
@@ -12429,13 +12397,13 @@
         <v>5.0</v>
       </c>
       <c r="C297" s="13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D297" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E297" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F297" s="13" t="s">
         <v>119</v>
@@ -12444,7 +12412,7 @@
         <v>120</v>
       </c>
       <c r="H297" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I297" s="8"/>
       <c r="J297" s="8"/>
@@ -12473,13 +12441,13 @@
         <v>6.0</v>
       </c>
       <c r="C298" s="13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D298" s="13" t="s">
         <v>25</v>
       </c>
       <c r="E298" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F298" s="13" t="s">
         <v>119</v>
@@ -12488,7 +12456,7 @@
         <v>120</v>
       </c>
       <c r="H298" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I298" s="8"/>
       <c r="J298" s="8"/>
@@ -12551,7 +12519,7 @@
         <v>32</v>
       </c>
       <c r="E300" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F300" s="13" t="s">
         <v>119</v>
@@ -12560,7 +12528,7 @@
         <v>120</v>
       </c>
       <c r="H300" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I300" s="8"/>
       <c r="J300" s="8"/>
@@ -12595,7 +12563,7 @@
         <v>39</v>
       </c>
       <c r="E301" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F301" s="13" t="s">
         <v>119</v>
@@ -12604,7 +12572,7 @@
         <v>120</v>
       </c>
       <c r="H301" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I301" s="8"/>
       <c r="J301" s="8"/>
@@ -12877,7 +12845,7 @@
         <v>42</v>
       </c>
       <c r="G308" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H308" s="13" t="s">
         <v>17</v>
@@ -12921,7 +12889,7 @@
         <v>42</v>
       </c>
       <c r="G309" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H309" s="13" t="s">
         <v>17</v>
@@ -13225,7 +13193,7 @@
         <v>42</v>
       </c>
       <c r="G317" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H317" s="13" t="s">
         <v>53</v>
@@ -13269,7 +13237,7 @@
         <v>42</v>
       </c>
       <c r="G318" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H318" s="13" t="s">
         <v>53</v>
@@ -13429,7 +13397,7 @@
         <v>42</v>
       </c>
       <c r="G322" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H322" s="8" t="s">
         <v>64</v>
@@ -13473,7 +13441,7 @@
         <v>42</v>
       </c>
       <c r="G323" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H323" s="8" t="s">
         <v>64</v>
@@ -13545,7 +13513,7 @@
         <v>42</v>
       </c>
       <c r="G325" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H325" s="8" t="s">
         <v>60</v>
@@ -13589,7 +13557,7 @@
         <v>42</v>
       </c>
       <c r="G326" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H326" s="8" t="s">
         <v>60</v>
@@ -13649,7 +13617,7 @@
         <v>12.0</v>
       </c>
       <c r="C328" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D328" s="15" t="s">
         <v>10</v>
@@ -13693,7 +13661,7 @@
         <v>13.0</v>
       </c>
       <c r="C329" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D329" s="19" t="s">
         <v>10</v>
@@ -13809,7 +13777,7 @@
         <v>13.0</v>
       </c>
       <c r="C332" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D332" s="19" t="s">
         <v>10</v>
